--- a/spreadsheets/2026 Fin Inst Database.xlsx
+++ b/spreadsheets/2026 Fin Inst Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-projects\trading\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76AAD86-4675-49CF-8963-BD52559C3EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01521718-1AF2-4498-A6A9-DE37FFC557D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31560" yWindow="1185" windowWidth="20265" windowHeight="10515" tabRatio="763" activeTab="3" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="763" activeTab="2" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="31" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2664" uniqueCount="393">
   <si>
     <t>comm_type</t>
   </si>
@@ -1206,6 +1206,18 @@
   </si>
   <si>
     <t>exclusion</t>
+  </si>
+  <si>
+    <t>biotech</t>
+  </si>
+  <si>
+    <t>IBB</t>
+  </si>
+  <si>
+    <t>aerospace</t>
+  </si>
+  <si>
+    <t>ITA</t>
   </si>
 </sst>
 </file>
@@ -1499,7 +1511,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1889,6 +1901,12 @@
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2138,6 +2156,475 @@
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.000000_);_(&quot;$&quot;* \(#,##0.000000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.000000_);_(&quot;$&quot;* \(#,##0.000000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
       </font>
     </dxf>
     <dxf>
@@ -2996,475 +3483,6 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.000000_);_(&quot;$&quot;* \(#,##0.000000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.000000_);_(&quot;$&quot;* \(#,##0.000000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3479,35 +3497,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}" name="static_data_table" displayName="static_data_table" ref="A1:P166" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65" headerRowCellStyle="Comma" dataCellStyle="Comma">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}" name="static_data_table" displayName="static_data_table" ref="A1:P166" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89" headerRowCellStyle="Comma" dataCellStyle="Comma">
   <autoFilter ref="A1:P166" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A118:O164">
     <sortCondition ref="B1:B166"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="19" xr3:uid="{1221CC04-A25D-42E0-9BD3-B46333797DBE}" name="vpn" dataDxfId="64" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{BED55A9A-3E28-4A17-AA02-2381DB89A658}" name="group" dataDxfId="63" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{F9B08B7F-16AE-460B-BDFB-B2726D177E92}" name="sector" dataDxfId="62" dataCellStyle="Comma"/>
-    <tableColumn id="1" xr3:uid="{8C59AB6B-6EBF-48B8-9D8A-4E9EFB96C425}" name="my_prod_type" dataDxfId="61"/>
-    <tableColumn id="18" xr3:uid="{D3CEE51C-FF16-474C-AC93-30CEB3E7D375}" name="my_fi_name" dataDxfId="60" dataCellStyle="Comma"/>
-    <tableColumn id="22" xr3:uid="{51F924B8-25BB-4080-AD58-7509A60E27B0}" name="my_pf_name" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{A13A7736-F17C-4146-B643-6EF65FC4B25C}" name="pf_locator" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{211C7B2F-2849-4B0F-B281-BF0424C5B57F}" name="top_currency" dataDxfId="57" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{46C5F41D-D64D-4F76-9E5D-390D6FE03BE6}" name="base_currency" dataDxfId="56" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{E2441BE5-ABB7-40CB-848F-02508F05A37C}" name="comm_type" dataDxfId="55" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{16FCE019-989B-4467-A8B9-96A8E58B2A2A}" name="comm_maker" dataDxfId="54" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{0E805949-D535-4626-85EB-FA3727E7DAF4}" name="comm_taker" dataDxfId="53" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{5709324A-7C63-43F4-AF59-F119177A7972}" name="comm_misc" dataDxfId="52" dataCellStyle="Comma"/>
-    <tableColumn id="8" xr3:uid="{32E47B88-05FD-48EE-97A0-59BC78476043}" name="comm_update" dataDxfId="51" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{B6578BCD-793E-47C9-99CF-D01D02E8D922}" name="mkt_data_stream" dataDxfId="50" dataCellStyle="Comma"/>
-    <tableColumn id="13" xr3:uid="{F138DC7A-FBFD-4726-8F8E-B333700760C4}" name="exclusion" dataDxfId="49" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{1221CC04-A25D-42E0-9BD3-B46333797DBE}" name="vpn" dataDxfId="88" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{BED55A9A-3E28-4A17-AA02-2381DB89A658}" name="group" dataDxfId="87" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{F9B08B7F-16AE-460B-BDFB-B2726D177E92}" name="sector" dataDxfId="86" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{8C59AB6B-6EBF-48B8-9D8A-4E9EFB96C425}" name="my_prod_type" dataDxfId="85"/>
+    <tableColumn id="18" xr3:uid="{D3CEE51C-FF16-474C-AC93-30CEB3E7D375}" name="my_fi_name" dataDxfId="84" dataCellStyle="Comma"/>
+    <tableColumn id="22" xr3:uid="{51F924B8-25BB-4080-AD58-7509A60E27B0}" name="my_pf_name" dataDxfId="83"/>
+    <tableColumn id="2" xr3:uid="{A13A7736-F17C-4146-B643-6EF65FC4B25C}" name="pf_locator" dataDxfId="82"/>
+    <tableColumn id="4" xr3:uid="{211C7B2F-2849-4B0F-B281-BF0424C5B57F}" name="top_currency" dataDxfId="81" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{46C5F41D-D64D-4F76-9E5D-390D6FE03BE6}" name="base_currency" dataDxfId="80" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{E2441BE5-ABB7-40CB-848F-02508F05A37C}" name="comm_type" dataDxfId="79" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{16FCE019-989B-4467-A8B9-96A8E58B2A2A}" name="comm_maker" dataDxfId="78" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{0E805949-D535-4626-85EB-FA3727E7DAF4}" name="comm_taker" dataDxfId="77" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{5709324A-7C63-43F4-AF59-F119177A7972}" name="comm_misc" dataDxfId="76" dataCellStyle="Comma"/>
+    <tableColumn id="8" xr3:uid="{32E47B88-05FD-48EE-97A0-59BC78476043}" name="comm_update" dataDxfId="75" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{B6578BCD-793E-47C9-99CF-D01D02E8D922}" name="mkt_data_stream" dataDxfId="74" dataCellStyle="Comma"/>
+    <tableColumn id="13" xr3:uid="{F138DC7A-FBFD-4726-8F8E-B333700760C4}" name="exclusion" dataDxfId="73" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}" name="btc_to_do" displayName="btc_to_do" ref="A171:AA224" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}" name="btc_to_do" displayName="btc_to_do" ref="A171:AA224" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
   <autoFilter ref="A171:AA224" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}">
     <filterColumn colId="1">
       <filters>
@@ -3516,71 +3534,71 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{73FD62E2-E8FE-4C00-9C3C-F3122EB55D0D}" name="Column1" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{F8F856BF-80BD-4398-8276-448953D1A283}" name="Column2" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{859FF76C-0D7F-496C-B885-2DE680F3F916}" name="Column7" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{EFE5B159-5688-4C13-A02D-A6C704275E2E}" name="Column4" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{69D00D15-DF82-46C9-9945-107A85371A6F}" name="Column5" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{F10DE59E-3B92-4DD0-8A04-FAE76E9F8BB9}" name="Column6" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{2D949549-0F5C-4A89-B8F7-72304B9A24F1}" name="Column8" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{C42826CE-029E-4945-8434-CBC9F4DAA57F}" name="Column9" dataDxfId="39" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{F0789B57-A27F-47CD-94AE-4F6B71344DB9}" name="Column92" dataDxfId="38" dataCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{84F8B5AD-93FB-4C3E-8E09-FB358E10FC62}" name="Column93" dataDxfId="37" dataCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{DA8CB162-5C11-45A4-93E0-E0C45C3ED3D0}" name="Column94" dataDxfId="36" dataCellStyle="Comma"/>
-    <tableColumn id="27" xr3:uid="{100A9F62-6915-49BB-B014-4D0BC03BB553}" name="Column95" dataDxfId="35" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{5B60D48A-2B91-4E81-AD9D-2709C1335F32}" name="Column10" dataDxfId="34" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{E1B16D3B-DEA4-44A7-8DE4-CA3F41D77B2B}" name="Column11" dataDxfId="33" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{793817C6-38BE-49BA-A9A6-4F96D87310D9}" name="Column12" dataDxfId="32" dataCellStyle="Comma"/>
-    <tableColumn id="15" xr3:uid="{2AFA675A-D2B0-476D-A865-BB72634DC6DA}" name="Column15" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{B5249436-7148-4EBF-B8E6-5226AA101320}" name="Column16" dataDxfId="30" dataCellStyle="Currency"/>
-    <tableColumn id="17" xr3:uid="{22140E2C-B2EC-4771-8D39-0E8FE9F80B88}" name="Column17" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{AC423A03-E794-4524-9C7D-D02B01892118}" name="Column18" dataDxfId="28" dataCellStyle="Comma"/>
-    <tableColumn id="19" xr3:uid="{F73A917A-F13B-4BB9-8524-E34E6050878C}" name="Column19" dataDxfId="27" dataCellStyle="Comma"/>
-    <tableColumn id="20" xr3:uid="{4A9B484B-EBD7-41D1-8470-161DB87D7FB2}" name="Column20" dataDxfId="26" dataCellStyle="Comma"/>
-    <tableColumn id="21" xr3:uid="{D03D1805-69BB-4D67-B61E-961F2E625E81}" name="Column21" dataDxfId="25"/>
-    <tableColumn id="22" xr3:uid="{66E8E4D1-FF14-404F-8354-025C93AED5CB}" name="Column22" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{9540F131-1C8F-4F4F-8796-92F1AFD57E03}" name="Column23" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{B7156378-CEA1-4808-9801-4E93C755FE92}" name="Column24" dataDxfId="22"/>
-    <tableColumn id="25" xr3:uid="{6908C233-AA1B-4818-BF8F-36FC13C53D09}" name="Column25" dataDxfId="21"/>
-    <tableColumn id="26" xr3:uid="{104781D6-1EEE-4947-A424-3CE3DCADF4CF}" name="Column26" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{73FD62E2-E8FE-4C00-9C3C-F3122EB55D0D}" name="Column1" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{F8F856BF-80BD-4398-8276-448953D1A283}" name="Column2" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{859FF76C-0D7F-496C-B885-2DE680F3F916}" name="Column7" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{EFE5B159-5688-4C13-A02D-A6C704275E2E}" name="Column4" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{69D00D15-DF82-46C9-9945-107A85371A6F}" name="Column5" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{F10DE59E-3B92-4DD0-8A04-FAE76E9F8BB9}" name="Column6" dataDxfId="65"/>
+    <tableColumn id="8" xr3:uid="{2D949549-0F5C-4A89-B8F7-72304B9A24F1}" name="Column8" dataDxfId="64"/>
+    <tableColumn id="9" xr3:uid="{C42826CE-029E-4945-8434-CBC9F4DAA57F}" name="Column9" dataDxfId="63" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{F0789B57-A27F-47CD-94AE-4F6B71344DB9}" name="Column92" dataDxfId="62" dataCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{84F8B5AD-93FB-4C3E-8E09-FB358E10FC62}" name="Column93" dataDxfId="61" dataCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{DA8CB162-5C11-45A4-93E0-E0C45C3ED3D0}" name="Column94" dataDxfId="60" dataCellStyle="Comma"/>
+    <tableColumn id="27" xr3:uid="{100A9F62-6915-49BB-B014-4D0BC03BB553}" name="Column95" dataDxfId="59" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{5B60D48A-2B91-4E81-AD9D-2709C1335F32}" name="Column10" dataDxfId="58" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{E1B16D3B-DEA4-44A7-8DE4-CA3F41D77B2B}" name="Column11" dataDxfId="57" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{793817C6-38BE-49BA-A9A6-4F96D87310D9}" name="Column12" dataDxfId="56" dataCellStyle="Comma"/>
+    <tableColumn id="15" xr3:uid="{2AFA675A-D2B0-476D-A865-BB72634DC6DA}" name="Column15" dataDxfId="55"/>
+    <tableColumn id="16" xr3:uid="{B5249436-7148-4EBF-B8E6-5226AA101320}" name="Column16" dataDxfId="54" dataCellStyle="Currency"/>
+    <tableColumn id="17" xr3:uid="{22140E2C-B2EC-4771-8D39-0E8FE9F80B88}" name="Column17" dataDxfId="53"/>
+    <tableColumn id="18" xr3:uid="{AC423A03-E794-4524-9C7D-D02B01892118}" name="Column18" dataDxfId="52" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{F73A917A-F13B-4BB9-8524-E34E6050878C}" name="Column19" dataDxfId="51" dataCellStyle="Comma"/>
+    <tableColumn id="20" xr3:uid="{4A9B484B-EBD7-41D1-8470-161DB87D7FB2}" name="Column20" dataDxfId="50" dataCellStyle="Comma"/>
+    <tableColumn id="21" xr3:uid="{D03D1805-69BB-4D67-B61E-961F2E625E81}" name="Column21" dataDxfId="49"/>
+    <tableColumn id="22" xr3:uid="{66E8E4D1-FF14-404F-8354-025C93AED5CB}" name="Column22" dataDxfId="48"/>
+    <tableColumn id="23" xr3:uid="{9540F131-1C8F-4F4F-8796-92F1AFD57E03}" name="Column23" dataDxfId="47"/>
+    <tableColumn id="24" xr3:uid="{B7156378-CEA1-4808-9801-4E93C755FE92}" name="Column24" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{6908C233-AA1B-4818-BF8F-36FC13C53D09}" name="Column25" dataDxfId="45"/>
+    <tableColumn id="26" xr3:uid="{104781D6-1EEE-4947-A424-3CE3DCADF4CF}" name="Column26" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4BF31094-215C-402D-8B13-3705F7FDAA90}" name="scalar_inputs_table" displayName="scalar_inputs_table" ref="A1:Z89" totalsRowShown="0">
-  <autoFilter ref="A1:Z89" xr:uid="{09E497BC-17A6-470C-8E05-7E807D85C061}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z77">
-    <sortCondition ref="D1:D77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4BF31094-215C-402D-8B13-3705F7FDAA90}" name="scalar_inputs_table" displayName="scalar_inputs_table" ref="A1:Z91" totalsRowShown="0">
+  <autoFilter ref="A1:Z91" xr:uid="{09E497BC-17A6-470C-8E05-7E807D85C061}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z79">
+    <sortCondition ref="D1:D79"/>
   </sortState>
   <tableColumns count="26">
     <tableColumn id="8" xr3:uid="{8CAFE9A2-351C-491C-8F0E-A191FB5F62F1}" name="group"/>
     <tableColumn id="7" xr3:uid="{05D8AE13-6024-4F28-BE04-4F5644C5B73A}" name="sector"/>
-    <tableColumn id="1" xr3:uid="{AFA57C80-2B2F-4727-B322-33373A15C9AE}" name="symbol" dataDxfId="90"/>
-    <tableColumn id="18" xr3:uid="{26F4ADAE-9F47-4523-899C-9F45673EC02E}" name="etf family" dataDxfId="89" dataCellStyle="Comma"/>
-    <tableColumn id="2" xr3:uid="{8D355E55-9FB0-4524-AED7-63AB9F6D6462}" name="etf fee" dataDxfId="88" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{FCA124B1-94D2-4B56-BB90-0F7311223FEE}" name="div 2026-09" dataDxfId="87" dataCellStyle="Currency"/>
-    <tableColumn id="16" xr3:uid="{BFBF1D57-673D-4449-B2FA-6EED3331C484}" name="div 2026-09 ex-date" dataDxfId="86" dataCellStyle="Percent"/>
-    <tableColumn id="13" xr3:uid="{F669470C-F245-4562-8E25-5953F248B91F}" name="div 2026-08" dataDxfId="85" dataCellStyle="Currency"/>
-    <tableColumn id="23" xr3:uid="{9D2DF049-DA5F-4A77-8D33-ABB58A4438DC}" name="div 2026-08 ex-date" dataDxfId="84" dataCellStyle="Percent"/>
-    <tableColumn id="11" xr3:uid="{BBCBF25D-DDD4-4D61-8E1E-077BE62554AC}" name="div 2026-07" dataDxfId="83" dataCellStyle="Currency"/>
-    <tableColumn id="22" xr3:uid="{9B510A38-BDAA-4C83-A0BA-CBA8258D1B5A}" name="div 2026-07 ex-date" dataDxfId="82" dataCellStyle="Percent"/>
-    <tableColumn id="14" xr3:uid="{D76D35EB-1AB6-4DE5-8C1C-3111406F2F72}" name="div 2026-06" dataDxfId="81" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{2101D0BE-AB56-44C4-AFF7-91BBB1013C9C}" name="div 2026-06 ex-date" dataDxfId="80" dataCellStyle="Percent"/>
-    <tableColumn id="21" xr3:uid="{82A49A8D-4D68-4D59-B5F9-F90A5262424F}" name="div 2026-05" dataDxfId="79" dataCellStyle="Currency"/>
-    <tableColumn id="24" xr3:uid="{2182D668-9AC5-4102-8F80-1187AFD225B7}" name="div 2026-05 ex-date" dataDxfId="78" dataCellStyle="Percent"/>
-    <tableColumn id="20" xr3:uid="{852173F6-72F7-4C68-BCA3-F7246A86D135}" name="div 2026-04" dataDxfId="77" dataCellStyle="Currency"/>
-    <tableColumn id="25" xr3:uid="{B8A617CB-C02A-4BAC-8397-105FB69C924D}" name="div 2026-04 ex-date" dataDxfId="76" dataCellStyle="Percent"/>
-    <tableColumn id="12" xr3:uid="{9BD4CA41-7A1D-40D5-86AC-FF1C5FE693FF}" name="div 2026-03" dataDxfId="75" dataCellStyle="Currency"/>
-    <tableColumn id="15" xr3:uid="{EE81E628-1DED-4A9A-B38F-77C889074F27}" name="div 2026-03 ex-date" dataDxfId="74" dataCellStyle="Percent"/>
-    <tableColumn id="19" xr3:uid="{3AD8B9FD-8C84-4949-A894-23543B2F48F6}" name="div 2026-02" dataDxfId="73" dataCellStyle="Currency"/>
-    <tableColumn id="26" xr3:uid="{B1AEFFE4-8EA5-4C45-A401-AE133D518FD2}" name="div 2026-02 ex-date" dataDxfId="72" dataCellStyle="Percent"/>
-    <tableColumn id="17" xr3:uid="{A1681DB9-E7FD-4AAD-BF01-80B2684F4CDF}" name="div 2026-01" dataDxfId="71" dataCellStyle="Currency"/>
-    <tableColumn id="27" xr3:uid="{576627EC-6EAC-4067-956A-DF67926726DC}" name="div 2026-01 ex-date" dataDxfId="70" dataCellStyle="Percent"/>
-    <tableColumn id="5" xr3:uid="{6C9795AF-4493-4D80-8BB1-FF32A4E90439}" name=" div 2025-12" dataDxfId="69" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{D716E943-B958-4884-BE63-A9B80B433F62}" name="div 2025-12 ex-date" dataDxfId="68" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{9FCCF7D4-0FBF-4FEE-86E1-9320D1C3E195}" name="comment" dataDxfId="67" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{AFA57C80-2B2F-4727-B322-33373A15C9AE}" name="symbol" dataDxfId="43"/>
+    <tableColumn id="18" xr3:uid="{26F4ADAE-9F47-4523-899C-9F45673EC02E}" name="etf family" dataDxfId="42" dataCellStyle="Comma"/>
+    <tableColumn id="2" xr3:uid="{8D355E55-9FB0-4524-AED7-63AB9F6D6462}" name="etf fee" dataDxfId="41" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{FCA124B1-94D2-4B56-BB90-0F7311223FEE}" name="div 2026-09" dataDxfId="40" dataCellStyle="Currency"/>
+    <tableColumn id="16" xr3:uid="{BFBF1D57-673D-4449-B2FA-6EED3331C484}" name="div 2026-09 ex-date" dataDxfId="39" dataCellStyle="Percent"/>
+    <tableColumn id="13" xr3:uid="{F669470C-F245-4562-8E25-5953F248B91F}" name="div 2026-08" dataDxfId="38" dataCellStyle="Currency"/>
+    <tableColumn id="23" xr3:uid="{9D2DF049-DA5F-4A77-8D33-ABB58A4438DC}" name="div 2026-08 ex-date" dataDxfId="37" dataCellStyle="Percent"/>
+    <tableColumn id="11" xr3:uid="{BBCBF25D-DDD4-4D61-8E1E-077BE62554AC}" name="div 2026-07" dataDxfId="36" dataCellStyle="Currency"/>
+    <tableColumn id="22" xr3:uid="{9B510A38-BDAA-4C83-A0BA-CBA8258D1B5A}" name="div 2026-07 ex-date" dataDxfId="35" dataCellStyle="Percent"/>
+    <tableColumn id="14" xr3:uid="{D76D35EB-1AB6-4DE5-8C1C-3111406F2F72}" name="div 2026-06" dataDxfId="34" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{2101D0BE-AB56-44C4-AFF7-91BBB1013C9C}" name="div 2026-06 ex-date" dataDxfId="33" dataCellStyle="Percent"/>
+    <tableColumn id="21" xr3:uid="{82A49A8D-4D68-4D59-B5F9-F90A5262424F}" name="div 2026-05" dataDxfId="32" dataCellStyle="Currency"/>
+    <tableColumn id="24" xr3:uid="{2182D668-9AC5-4102-8F80-1187AFD225B7}" name="div 2026-05 ex-date" dataDxfId="31" dataCellStyle="Percent"/>
+    <tableColumn id="20" xr3:uid="{852173F6-72F7-4C68-BCA3-F7246A86D135}" name="div 2026-04" dataDxfId="30" dataCellStyle="Currency"/>
+    <tableColumn id="25" xr3:uid="{B8A617CB-C02A-4BAC-8397-105FB69C924D}" name="div 2026-04 ex-date" dataDxfId="29" dataCellStyle="Percent"/>
+    <tableColumn id="12" xr3:uid="{9BD4CA41-7A1D-40D5-86AC-FF1C5FE693FF}" name="div 2026-03" dataDxfId="28" dataCellStyle="Currency"/>
+    <tableColumn id="15" xr3:uid="{EE81E628-1DED-4A9A-B38F-77C889074F27}" name="div 2026-03 ex-date" dataDxfId="27" dataCellStyle="Percent"/>
+    <tableColumn id="19" xr3:uid="{3AD8B9FD-8C84-4949-A894-23543B2F48F6}" name="div 2026-02" dataDxfId="26" dataCellStyle="Currency"/>
+    <tableColumn id="26" xr3:uid="{B1AEFFE4-8EA5-4C45-A401-AE133D518FD2}" name="div 2026-02 ex-date" dataDxfId="25" dataCellStyle="Percent"/>
+    <tableColumn id="17" xr3:uid="{A1681DB9-E7FD-4AAD-BF01-80B2684F4CDF}" name="div 2026-01" dataDxfId="24" dataCellStyle="Currency"/>
+    <tableColumn id="27" xr3:uid="{576627EC-6EAC-4067-956A-DF67926726DC}" name="div 2026-01 ex-date" dataDxfId="23" dataCellStyle="Percent"/>
+    <tableColumn id="5" xr3:uid="{6C9795AF-4493-4D80-8BB1-FF32A4E90439}" name=" div 2025-12" dataDxfId="22" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{D716E943-B958-4884-BE63-A9B80B433F62}" name="div 2025-12 ex-date" dataDxfId="21" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{9FCCF7D4-0FBF-4FEE-86E1-9320D1C3E195}" name="comment" dataDxfId="20" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15140,7 +15158,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E7D6F9-8EEF-4AEB-9A0C-4C38E8E5BED4}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AB370"/>
+  <dimension ref="A1:AB372"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -15271,10 +15289,10 @@
       <c r="E2" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F2" s="138">
-        <v>0</v>
-      </c>
-      <c r="G2" s="128">
+      <c r="F2" s="151">
+        <v>0.2</v>
+      </c>
+      <c r="G2" s="152">
         <v>46283</v>
       </c>
       <c r="H2" s="138">
@@ -15349,10 +15367,10 @@
       <c r="E3" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F3" s="138">
-        <v>0</v>
-      </c>
-      <c r="G3" s="128">
+      <c r="F3" s="151">
+        <v>0.31</v>
+      </c>
+      <c r="G3" s="152">
         <v>46283</v>
       </c>
       <c r="H3" s="138">
@@ -15427,10 +15445,10 @@
       <c r="E4" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F4" s="138">
-        <v>0</v>
-      </c>
-      <c r="G4" s="128">
+      <c r="F4" s="151">
+        <v>0.254</v>
+      </c>
+      <c r="G4" s="152">
         <v>46283</v>
       </c>
       <c r="H4" s="138">
@@ -15505,10 +15523,10 @@
       <c r="E5" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F5" s="138">
-        <v>0</v>
-      </c>
-      <c r="G5" s="128">
+      <c r="F5" s="151">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="G5" s="152">
         <v>46283</v>
       </c>
       <c r="H5" s="138">
@@ -15583,10 +15601,10 @@
       <c r="E6" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F6" s="138">
-        <v>0</v>
-      </c>
-      <c r="G6" s="128">
+      <c r="F6" s="151">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="G6" s="152">
         <v>46283</v>
       </c>
       <c r="H6" s="138">
@@ -15661,10 +15679,10 @@
       <c r="E7" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F7" s="138">
-        <v>0</v>
-      </c>
-      <c r="G7" s="128">
+      <c r="F7" s="149">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="G7" s="150">
         <v>46283</v>
       </c>
       <c r="H7" s="138">
@@ -15739,10 +15757,10 @@
       <c r="E8" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F8" s="138">
-        <v>0</v>
-      </c>
-      <c r="G8" s="128">
+      <c r="F8" s="151">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="G8" s="152">
         <v>46283</v>
       </c>
       <c r="H8" s="138">
@@ -15817,10 +15835,10 @@
       <c r="E9" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F9" s="138">
-        <v>0</v>
-      </c>
-      <c r="G9" s="128">
+      <c r="F9" s="151">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="G9" s="152">
         <v>46283</v>
       </c>
       <c r="H9" s="138">
@@ -15895,10 +15913,10 @@
       <c r="E10" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F10" s="138">
-        <v>0</v>
-      </c>
-      <c r="G10" s="128">
+      <c r="F10" s="151">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="G10" s="152">
         <v>46283</v>
       </c>
       <c r="H10" s="138">
@@ -17118,20 +17136,20 @@
       <c r="A26" t="s">
         <v>315</v>
       </c>
-      <c r="B26" s="106" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="105" t="s">
-        <v>285</v>
+      <c r="B26" t="s">
+        <v>389</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>390</v>
       </c>
       <c r="D26" s="110" t="s">
         <v>273</v>
       </c>
       <c r="E26" s="111">
-        <v>3.7000000000000002E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="F26" s="149">
-        <v>0.39350299999999999</v>
+        <v>1.1194000000000001E-2</v>
       </c>
       <c r="G26" s="150">
         <v>46280</v>
@@ -17149,7 +17167,7 @@
         <v>85</v>
       </c>
       <c r="L26" s="138">
-        <v>0.30908999999999998</v>
+        <v>2.3774E-2</v>
       </c>
       <c r="M26" s="128">
         <v>46188</v>
@@ -17167,7 +17185,7 @@
         <v>85</v>
       </c>
       <c r="R26" s="138">
-        <v>0.30672700000000003</v>
+        <v>0.121818</v>
       </c>
       <c r="S26" s="127">
         <v>46098</v>
@@ -17185,7 +17203,7 @@
         <v>85</v>
       </c>
       <c r="X26" s="138">
-        <v>0.34088200000000002</v>
+        <v>0.18309900000000001</v>
       </c>
       <c r="Y26" s="128">
         <v>46007</v>
@@ -17196,20 +17214,20 @@
       <c r="A27" t="s">
         <v>315</v>
       </c>
-      <c r="B27" s="106" t="s">
-        <v>357</v>
-      </c>
-      <c r="C27" s="105" t="s">
-        <v>289</v>
+      <c r="B27" t="s">
+        <v>391</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>392</v>
       </c>
       <c r="D27" s="110" t="s">
         <v>273</v>
       </c>
       <c r="E27" s="111">
-        <v>3.7000000000000002E-3</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="F27" s="149">
-        <v>0.41789900000000002</v>
+        <v>0.25052000000000002</v>
       </c>
       <c r="G27" s="150">
         <v>46280</v>
@@ -17227,7 +17245,7 @@
         <v>85</v>
       </c>
       <c r="L27" s="138">
-        <v>0.38038300000000003</v>
+        <v>0.16358</v>
       </c>
       <c r="M27" s="128">
         <v>46188</v>
@@ -17245,7 +17263,7 @@
         <v>85</v>
       </c>
       <c r="R27" s="138">
-        <v>0.57623199999999997</v>
+        <v>0.15132499999999999</v>
       </c>
       <c r="S27" s="127">
         <v>46098</v>
@@ -17263,7 +17281,7 @@
         <v>85</v>
       </c>
       <c r="X27" s="138">
-        <v>0.57199199999999994</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="128">
         <v>46007</v>
@@ -17275,10 +17293,10 @@
         <v>315</v>
       </c>
       <c r="B28" s="106" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C28" s="105" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D28" s="110" t="s">
         <v>273</v>
@@ -17287,7 +17305,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="F28" s="149">
-        <v>0.190827</v>
+        <v>0.39350299999999999</v>
       </c>
       <c r="G28" s="150">
         <v>46280</v>
@@ -17305,7 +17323,7 @@
         <v>85</v>
       </c>
       <c r="L28" s="138">
-        <v>0.16336000000000001</v>
+        <v>0.30908999999999998</v>
       </c>
       <c r="M28" s="128">
         <v>46188</v>
@@ -17323,7 +17341,7 @@
         <v>85</v>
       </c>
       <c r="R28" s="138">
-        <v>0.19481999999999999</v>
+        <v>0.30672700000000003</v>
       </c>
       <c r="S28" s="127">
         <v>46098</v>
@@ -17341,7 +17359,7 @@
         <v>85</v>
       </c>
       <c r="X28" s="138">
-        <v>0.249694</v>
+        <v>0.34088200000000002</v>
       </c>
       <c r="Y28" s="128">
         <v>46007</v>
@@ -17353,10 +17371,10 @@
         <v>315</v>
       </c>
       <c r="B29" s="106" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C29" s="105" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D29" s="110" t="s">
         <v>273</v>
@@ -17365,7 +17383,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="F29" s="149">
-        <v>0.30100700000000002</v>
+        <v>0.41789900000000002</v>
       </c>
       <c r="G29" s="150">
         <v>46280</v>
@@ -17383,7 +17401,7 @@
         <v>85</v>
       </c>
       <c r="L29" s="138">
-        <v>0.262299</v>
+        <v>0.38038300000000003</v>
       </c>
       <c r="M29" s="128">
         <v>46188</v>
@@ -17401,7 +17419,7 @@
         <v>85</v>
       </c>
       <c r="R29" s="138">
-        <v>0.27506799999999998</v>
+        <v>0.57623199999999997</v>
       </c>
       <c r="S29" s="127">
         <v>46098</v>
@@ -17419,7 +17437,7 @@
         <v>85</v>
       </c>
       <c r="X29" s="138">
-        <v>0.26978000000000002</v>
+        <v>0.57199199999999994</v>
       </c>
       <c r="Y29" s="128">
         <v>46007</v>
@@ -17431,10 +17449,10 @@
         <v>315</v>
       </c>
       <c r="B30" s="106" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C30" s="105" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D30" s="110" t="s">
         <v>273</v>
@@ -17443,7 +17461,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="F30" s="149">
-        <v>0.73818700000000004</v>
+        <v>0.190827</v>
       </c>
       <c r="G30" s="150">
         <v>46280</v>
@@ -17461,7 +17479,7 @@
         <v>85</v>
       </c>
       <c r="L30" s="138">
-        <v>0.51000999999999996</v>
+        <v>0.16336000000000001</v>
       </c>
       <c r="M30" s="128">
         <v>46188</v>
@@ -17479,7 +17497,7 @@
         <v>85</v>
       </c>
       <c r="R30" s="138">
-        <v>0.27537</v>
+        <v>0.19481999999999999</v>
       </c>
       <c r="S30" s="127">
         <v>46098</v>
@@ -17497,7 +17515,7 @@
         <v>85</v>
       </c>
       <c r="X30" s="138">
-        <v>0.86209499999999994</v>
+        <v>0.249694</v>
       </c>
       <c r="Y30" s="128">
         <v>46007</v>
@@ -17509,10 +17527,10 @@
         <v>315</v>
       </c>
       <c r="B31" s="106" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="C31" s="105" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D31" s="110" t="s">
         <v>273</v>
@@ -17521,7 +17539,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="F31" s="149">
-        <v>0.43650299999999997</v>
+        <v>0.30100700000000002</v>
       </c>
       <c r="G31" s="150">
         <v>46280</v>
@@ -17539,7 +17557,7 @@
         <v>85</v>
       </c>
       <c r="L31" s="138">
-        <v>0.40746500000000002</v>
+        <v>0.262299</v>
       </c>
       <c r="M31" s="128">
         <v>46188</v>
@@ -17557,7 +17575,7 @@
         <v>85</v>
       </c>
       <c r="R31" s="138">
-        <v>0.28752899999999998</v>
+        <v>0.27506799999999998</v>
       </c>
       <c r="S31" s="127">
         <v>46098</v>
@@ -17575,7 +17593,7 @@
         <v>85</v>
       </c>
       <c r="X31" s="138">
-        <v>0.69611699999999999</v>
+        <v>0.26978000000000002</v>
       </c>
       <c r="Y31" s="128">
         <v>46007</v>
@@ -17587,10 +17605,10 @@
         <v>315</v>
       </c>
       <c r="B32" s="106" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C32" s="105" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D32" s="110" t="s">
         <v>273</v>
@@ -17599,7 +17617,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="F32" s="149">
-        <v>4.9132000000000002E-2</v>
+        <v>0.73818700000000004</v>
       </c>
       <c r="G32" s="150">
         <v>46280</v>
@@ -17617,7 +17635,7 @@
         <v>85</v>
       </c>
       <c r="L32" s="138">
-        <v>7.1818999999999994E-2</v>
+        <v>0.51000999999999996</v>
       </c>
       <c r="M32" s="128">
         <v>46188</v>
@@ -17635,7 +17653,7 @@
         <v>85</v>
       </c>
       <c r="R32" s="138">
-        <v>6.9825999999999999E-2</v>
+        <v>0.27537</v>
       </c>
       <c r="S32" s="127">
         <v>46098</v>
@@ -17653,7 +17671,7 @@
         <v>85</v>
       </c>
       <c r="X32" s="138">
-        <v>5.5414999999999999E-2</v>
+        <v>0.86209499999999994</v>
       </c>
       <c r="Y32" s="128">
         <v>46007</v>
@@ -17665,10 +17683,10 @@
         <v>315</v>
       </c>
       <c r="B33" s="106" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C33" s="105" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="D33" s="110" t="s">
         <v>273</v>
@@ -17677,7 +17695,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="F33" s="149">
-        <v>0.64697700000000002</v>
+        <v>0.43650299999999997</v>
       </c>
       <c r="G33" s="150">
         <v>46280</v>
@@ -17695,7 +17713,7 @@
         <v>85</v>
       </c>
       <c r="L33" s="138">
-        <v>0.63148800000000005</v>
+        <v>0.40746500000000002</v>
       </c>
       <c r="M33" s="128">
         <v>46188</v>
@@ -17713,7 +17731,7 @@
         <v>85</v>
       </c>
       <c r="R33" s="138">
-        <v>0.62162899999999999</v>
+        <v>0.28752899999999998</v>
       </c>
       <c r="S33" s="127">
         <v>46098</v>
@@ -17731,7 +17749,7 @@
         <v>85</v>
       </c>
       <c r="X33" s="138">
-        <v>0.67869000000000002</v>
+        <v>0.69611699999999999</v>
       </c>
       <c r="Y33" s="128">
         <v>46007</v>
@@ -17743,10 +17761,10 @@
         <v>315</v>
       </c>
       <c r="B34" s="106" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="C34" s="105" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="D34" s="110" t="s">
         <v>273</v>
@@ -17755,7 +17773,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="F34" s="149">
-        <v>0.150284</v>
+        <v>4.9132000000000002E-2</v>
       </c>
       <c r="G34" s="150">
         <v>46280</v>
@@ -17773,7 +17791,7 @@
         <v>85</v>
       </c>
       <c r="L34" s="138">
-        <v>0.14061399999999999</v>
+        <v>7.1818999999999994E-2</v>
       </c>
       <c r="M34" s="128">
         <v>46188</v>
@@ -17791,9 +17809,9 @@
         <v>85</v>
       </c>
       <c r="R34" s="138">
-        <v>0.12673200000000001</v>
-      </c>
-      <c r="S34" s="128">
+        <v>6.9825999999999999E-2</v>
+      </c>
+      <c r="S34" s="127">
         <v>46098</v>
       </c>
       <c r="T34" s="138">
@@ -17809,7 +17827,7 @@
         <v>85</v>
       </c>
       <c r="X34" s="138">
-        <v>0.108711</v>
+        <v>5.5414999999999999E-2</v>
       </c>
       <c r="Y34" s="128">
         <v>46007</v>
@@ -17818,218 +17836,220 @@
     </row>
     <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>335</v>
-      </c>
-      <c r="B35" t="s">
-        <v>341</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="D35" s="92" t="s">
-        <v>264</v>
-      </c>
-      <c r="E35" s="108">
-        <v>2E-3</v>
-      </c>
-      <c r="F35" s="137">
-        <v>0.39</v>
-      </c>
-      <c r="G35" s="127">
-        <v>46266</v>
-      </c>
-      <c r="H35" s="137">
-        <v>0.43</v>
-      </c>
-      <c r="I35" s="127">
-        <v>46237</v>
-      </c>
-      <c r="J35" s="137">
-        <v>0.41</v>
-      </c>
-      <c r="K35" s="127">
-        <v>46204</v>
-      </c>
-      <c r="L35" s="137">
-        <v>0.41</v>
-      </c>
-      <c r="M35" s="127">
-        <v>46174</v>
-      </c>
-      <c r="N35" s="137">
-        <v>0.4</v>
-      </c>
-      <c r="O35" s="127">
-        <v>46143</v>
-      </c>
-      <c r="P35" s="137">
-        <v>0.37</v>
-      </c>
-      <c r="Q35" s="127">
-        <v>46113</v>
-      </c>
-      <c r="R35" s="137">
-        <v>0.38</v>
+        <v>315</v>
+      </c>
+      <c r="B35" s="106" t="s">
+        <v>356</v>
+      </c>
+      <c r="C35" s="105" t="s">
+        <v>309</v>
+      </c>
+      <c r="D35" s="110" t="s">
+        <v>273</v>
+      </c>
+      <c r="E35" s="111">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="F35" s="149">
+        <v>0.64697700000000002</v>
+      </c>
+      <c r="G35" s="150">
+        <v>46280</v>
+      </c>
+      <c r="H35" s="138">
+        <v>0</v>
+      </c>
+      <c r="I35" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="J35" s="138">
+        <v>0</v>
+      </c>
+      <c r="K35" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="L35" s="138">
+        <v>0.63148800000000005</v>
+      </c>
+      <c r="M35" s="128">
+        <v>46188</v>
+      </c>
+      <c r="N35" s="138">
+        <v>0</v>
+      </c>
+      <c r="O35" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="P35" s="138">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="R35" s="138">
+        <v>0.62162899999999999</v>
       </c>
       <c r="S35" s="127">
-        <v>46083</v>
-      </c>
-      <c r="T35" s="137">
-        <v>0.37</v>
-      </c>
-      <c r="U35" s="127">
-        <v>46055</v>
-      </c>
-      <c r="V35" s="137">
+        <v>46098</v>
+      </c>
+      <c r="T35" s="138">
+        <v>0</v>
+      </c>
+      <c r="U35" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="V35" s="138">
         <v>0</v>
       </c>
       <c r="W35" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="X35" s="137">
-        <v>0.42</v>
-      </c>
-      <c r="Y35" s="127">
-        <v>46022</v>
-      </c>
+      <c r="X35" s="138">
+        <v>0.67869000000000002</v>
+      </c>
+      <c r="Y35" s="128">
+        <v>46007</v>
+      </c>
+      <c r="Z35" s="96"/>
     </row>
     <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>335</v>
-      </c>
-      <c r="B36" t="s">
-        <v>336</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="D36" s="92" t="s">
-        <v>267</v>
-      </c>
-      <c r="E36" s="94">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="F36" s="137">
-        <v>7.6600000000000001E-2</v>
-      </c>
-      <c r="G36" s="127">
-        <v>46266</v>
-      </c>
-      <c r="H36" s="137">
-        <v>8.7999999999999995E-2</v>
-      </c>
-      <c r="I36" s="127">
-        <v>46237</v>
-      </c>
-      <c r="J36" s="137">
-        <v>0.08</v>
-      </c>
-      <c r="K36" s="127">
-        <v>46204</v>
-      </c>
-      <c r="L36" s="137">
-        <v>8.09E-2</v>
-      </c>
-      <c r="M36" s="127">
-        <v>46174</v>
-      </c>
-      <c r="N36" s="137">
-        <v>7.8700000000000006E-2</v>
-      </c>
-      <c r="O36" s="127">
-        <v>46143</v>
-      </c>
-      <c r="P36" s="137">
-        <v>7.85E-2</v>
-      </c>
-      <c r="Q36" s="127">
-        <v>46113</v>
-      </c>
-      <c r="R36" s="137">
-        <v>7.7200000000000005E-2</v>
-      </c>
-      <c r="S36" s="127">
-        <v>46083</v>
-      </c>
-      <c r="T36" s="137">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="U36" s="127">
-        <v>46055</v>
-      </c>
-      <c r="V36" s="137">
+        <v>315</v>
+      </c>
+      <c r="B36" s="106" t="s">
+        <v>371</v>
+      </c>
+      <c r="C36" s="105" t="s">
+        <v>276</v>
+      </c>
+      <c r="D36" s="110" t="s">
+        <v>273</v>
+      </c>
+      <c r="E36" s="111">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="F36" s="149">
+        <v>0.150284</v>
+      </c>
+      <c r="G36" s="150">
+        <v>46280</v>
+      </c>
+      <c r="H36" s="138">
+        <v>0</v>
+      </c>
+      <c r="I36" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="J36" s="138">
+        <v>0</v>
+      </c>
+      <c r="K36" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="L36" s="138">
+        <v>0.14061399999999999</v>
+      </c>
+      <c r="M36" s="128">
+        <v>46188</v>
+      </c>
+      <c r="N36" s="138">
+        <v>0</v>
+      </c>
+      <c r="O36" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="P36" s="138">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="R36" s="138">
+        <v>0.12673200000000001</v>
+      </c>
+      <c r="S36" s="128">
+        <v>46098</v>
+      </c>
+      <c r="T36" s="138">
+        <v>0</v>
+      </c>
+      <c r="U36" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="V36" s="138">
         <v>0</v>
       </c>
       <c r="W36" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="X36" s="137">
-        <v>7.6999999999999999E-2</v>
-      </c>
-      <c r="Y36" s="127">
-        <v>46010</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" s="64" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X36" s="138">
+        <v>0.108711</v>
+      </c>
+      <c r="Y36" s="128">
+        <v>46007</v>
+      </c>
+      <c r="Z36" s="96"/>
+    </row>
+    <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>335</v>
       </c>
       <c r="B37" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D37" s="92" t="s">
-        <v>267</v>
-      </c>
-      <c r="E37" s="94">
-        <v>2.9999999999999997E-4</v>
+        <v>264</v>
+      </c>
+      <c r="E37" s="108">
+        <v>2E-3</v>
       </c>
       <c r="F37" s="137">
-        <v>0.1396</v>
+        <v>0.39</v>
       </c>
       <c r="G37" s="127">
         <v>46266</v>
       </c>
       <c r="H37" s="137">
-        <v>0.1547</v>
+        <v>0.43</v>
       </c>
       <c r="I37" s="127">
         <v>46237</v>
       </c>
       <c r="J37" s="137">
-        <v>0.1487</v>
+        <v>0.41</v>
       </c>
       <c r="K37" s="127">
         <v>46204</v>
       </c>
       <c r="L37" s="137">
-        <v>0.14960000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="M37" s="127">
         <v>46174</v>
       </c>
       <c r="N37" s="137">
-        <v>0.1449</v>
+        <v>0.4</v>
       </c>
       <c r="O37" s="127">
         <v>46143</v>
       </c>
       <c r="P37" s="137">
-        <v>0.1537</v>
+        <v>0.37</v>
       </c>
       <c r="Q37" s="127">
         <v>46113</v>
       </c>
       <c r="R37" s="137">
-        <v>0.1449</v>
+        <v>0.38</v>
       </c>
       <c r="S37" s="127">
         <v>46083</v>
       </c>
       <c r="T37" s="137">
-        <v>0.15579999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="U37" s="127">
         <v>46055</v>
@@ -18041,22 +18061,21 @@
         <v>85</v>
       </c>
       <c r="X37" s="137">
-        <v>0.14810000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="Y37" s="127">
-        <v>46010</v>
-      </c>
-      <c r="Z37"/>
+        <v>46022</v>
+      </c>
     </row>
     <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>335</v>
       </c>
       <c r="B38" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="D38" s="92" t="s">
         <v>267</v>
@@ -18065,49 +18084,49 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F38" s="137">
-        <v>0.10929999999999999</v>
+        <v>7.6600000000000001E-2</v>
       </c>
       <c r="G38" s="127">
         <v>46266</v>
       </c>
       <c r="H38" s="137">
-        <v>0.127</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="I38" s="127">
         <v>46237</v>
       </c>
       <c r="J38" s="137">
-        <v>0.1085</v>
+        <v>0.08</v>
       </c>
       <c r="K38" s="127">
         <v>46204</v>
       </c>
       <c r="L38" s="137">
-        <v>0.14960000000000001</v>
+        <v>8.09E-2</v>
       </c>
       <c r="M38" s="127">
         <v>46174</v>
       </c>
       <c r="N38" s="137">
-        <v>0.1168</v>
+        <v>7.8700000000000006E-2</v>
       </c>
       <c r="O38" s="127">
         <v>46143</v>
       </c>
       <c r="P38" s="137">
-        <v>0.12770000000000001</v>
+        <v>7.85E-2</v>
       </c>
       <c r="Q38" s="127">
         <v>46113</v>
       </c>
       <c r="R38" s="137">
-        <v>0.1066</v>
+        <v>7.7200000000000005E-2</v>
       </c>
       <c r="S38" s="127">
         <v>46083</v>
       </c>
       <c r="T38" s="137">
-        <v>0.14799999999999999</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="U38" s="127">
         <v>46055</v>
@@ -18119,72 +18138,72 @@
         <v>85</v>
       </c>
       <c r="X38" s="137">
-        <v>0.127</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="Y38" s="127">
         <v>46010</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" s="64" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>335</v>
       </c>
       <c r="B39" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D39" s="92" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E39" s="94">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F39" s="137">
-        <v>8.9305999999999996E-2</v>
+        <v>0.1396</v>
       </c>
       <c r="G39" s="127">
         <v>46266</v>
       </c>
       <c r="H39" s="137">
-        <v>8.8980000000000004E-2</v>
+        <v>0.1547</v>
       </c>
       <c r="I39" s="127">
         <v>46237</v>
       </c>
       <c r="J39" s="137">
-        <v>8.7480000000000002E-2</v>
+        <v>0.1487</v>
       </c>
       <c r="K39" s="127">
         <v>46204</v>
       </c>
       <c r="L39" s="137">
-        <v>8.7929999999999994E-2</v>
+        <v>0.14960000000000001</v>
       </c>
       <c r="M39" s="127">
         <v>46174</v>
       </c>
       <c r="N39" s="137">
-        <v>8.6389999999999995E-2</v>
+        <v>0.1449</v>
       </c>
       <c r="O39" s="127">
         <v>46143</v>
       </c>
       <c r="P39" s="137">
-        <v>8.7540000000000007E-2</v>
+        <v>0.1537</v>
       </c>
       <c r="Q39" s="127">
         <v>46113</v>
       </c>
       <c r="R39" s="137">
-        <v>8.3150000000000002E-2</v>
+        <v>0.1449</v>
       </c>
       <c r="S39" s="127">
         <v>46083</v>
       </c>
       <c r="T39" s="137">
-        <v>8.1979999999999997E-2</v>
+        <v>0.15579999999999999</v>
       </c>
       <c r="U39" s="127">
         <v>46055</v>
@@ -18196,72 +18215,73 @@
         <v>85</v>
       </c>
       <c r="X39" s="137">
-        <v>9.1097999999999998E-2</v>
+        <v>0.14810000000000001</v>
       </c>
       <c r="Y39" s="127">
-        <v>46009</v>
-      </c>
+        <v>46010</v>
+      </c>
+      <c r="Z39"/>
     </row>
     <row r="40" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>335</v>
       </c>
       <c r="B40" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D40" s="92" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E40" s="94">
-        <v>4.0000000000000001E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F40" s="137">
-        <v>0.154807</v>
+        <v>0.10929999999999999</v>
       </c>
       <c r="G40" s="127">
         <v>46266</v>
       </c>
       <c r="H40" s="137">
-        <v>0.21054</v>
+        <v>0.127</v>
       </c>
       <c r="I40" s="127">
         <v>46237</v>
       </c>
       <c r="J40" s="137">
-        <v>9.1050000000000006E-2</v>
+        <v>0.1085</v>
       </c>
       <c r="K40" s="127">
         <v>46204</v>
       </c>
       <c r="L40" s="137">
-        <v>0.15523000000000001</v>
+        <v>0.14960000000000001</v>
       </c>
       <c r="M40" s="127">
         <v>46174</v>
       </c>
       <c r="N40" s="137">
-        <v>0.12466000000000001</v>
+        <v>0.1168</v>
       </c>
       <c r="O40" s="127">
         <v>46143</v>
       </c>
       <c r="P40" s="137">
-        <v>0.10198</v>
+        <v>0.12770000000000001</v>
       </c>
       <c r="Q40" s="127">
         <v>46113</v>
       </c>
       <c r="R40" s="137">
-        <v>0.14646999999999999</v>
+        <v>0.1066</v>
       </c>
       <c r="S40" s="127">
         <v>46083</v>
       </c>
       <c r="T40" s="137">
-        <v>8.6249999999999993E-2</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="U40" s="127">
         <v>46055</v>
@@ -18273,10 +18293,10 @@
         <v>85</v>
       </c>
       <c r="X40" s="137">
-        <v>0.16361100000000001</v>
+        <v>0.127</v>
       </c>
       <c r="Y40" s="127">
-        <v>46009</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="41" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18284,10 +18304,10 @@
         <v>335</v>
       </c>
       <c r="B41" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D41" s="92" t="s">
         <v>274</v>
@@ -18296,49 +18316,49 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F41" s="137">
-        <v>0.123783</v>
+        <v>8.9305999999999996E-2</v>
       </c>
       <c r="G41" s="127">
         <v>46266</v>
       </c>
       <c r="H41" s="137">
-        <v>0.12334000000000001</v>
+        <v>8.8980000000000004E-2</v>
       </c>
       <c r="I41" s="127">
         <v>46237</v>
       </c>
       <c r="J41" s="137">
-        <v>0.12291000000000001</v>
+        <v>8.7480000000000002E-2</v>
       </c>
       <c r="K41" s="127">
         <v>46204</v>
       </c>
       <c r="L41" s="137">
-        <v>0.12291000000000001</v>
+        <v>8.7929999999999994E-2</v>
       </c>
       <c r="M41" s="127">
         <v>46174</v>
       </c>
       <c r="N41" s="137">
-        <v>0.12257</v>
+        <v>8.6389999999999995E-2</v>
       </c>
       <c r="O41" s="127">
         <v>46143</v>
       </c>
       <c r="P41" s="137">
-        <v>0.12262000000000001</v>
+        <v>8.7540000000000007E-2</v>
       </c>
       <c r="Q41" s="127">
         <v>46113</v>
       </c>
       <c r="R41" s="137">
-        <v>0.12246</v>
+        <v>8.3150000000000002E-2</v>
       </c>
       <c r="S41" s="127">
         <v>46083</v>
       </c>
       <c r="T41" s="137">
-        <v>0.12303</v>
+        <v>8.1979999999999997E-2</v>
       </c>
       <c r="U41" s="127">
         <v>46055</v>
@@ -18350,7 +18370,7 @@
         <v>85</v>
       </c>
       <c r="X41" s="137">
-        <v>0.122505</v>
+        <v>9.1097999999999998E-2</v>
       </c>
       <c r="Y41" s="127">
         <v>46009</v>
@@ -18361,10 +18381,10 @@
         <v>335</v>
       </c>
       <c r="B42" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="D42" s="92" t="s">
         <v>274</v>
@@ -18373,49 +18393,49 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="F42" s="137">
-        <v>0.53229499999999996</v>
+        <v>0.154807</v>
       </c>
       <c r="G42" s="127">
         <v>46266</v>
       </c>
       <c r="H42" s="137">
-        <v>0.52717999999999998</v>
+        <v>0.21054</v>
       </c>
       <c r="I42" s="127">
         <v>46237</v>
       </c>
       <c r="J42" s="137">
-        <v>0.53078000000000003</v>
+        <v>9.1050000000000006E-2</v>
       </c>
       <c r="K42" s="127">
         <v>46204</v>
       </c>
       <c r="L42" s="137">
-        <v>0.52310000000000001</v>
+        <v>0.15523000000000001</v>
       </c>
       <c r="M42" s="127">
         <v>46174</v>
       </c>
       <c r="N42" s="137">
-        <v>0.52693999999999996</v>
+        <v>0.12466000000000001</v>
       </c>
       <c r="O42" s="127">
         <v>46143</v>
       </c>
       <c r="P42" s="137">
-        <v>0.52478000000000002</v>
+        <v>0.10198</v>
       </c>
       <c r="Q42" s="127">
         <v>46113</v>
       </c>
       <c r="R42" s="137">
-        <v>0.52456999999999998</v>
+        <v>0.14646999999999999</v>
       </c>
       <c r="S42" s="127">
         <v>46083</v>
       </c>
       <c r="T42" s="137">
-        <v>0.56008999999999998</v>
+        <v>8.6249999999999993E-2</v>
       </c>
       <c r="U42" s="127">
         <v>46055</v>
@@ -18427,7 +18447,7 @@
         <v>85</v>
       </c>
       <c r="X42" s="137">
-        <v>0.49054799999999998</v>
+        <v>0.16361100000000001</v>
       </c>
       <c r="Y42" s="127">
         <v>46009</v>
@@ -18438,61 +18458,61 @@
         <v>335</v>
       </c>
       <c r="B43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D43" s="92" t="s">
         <v>274</v>
       </c>
       <c r="E43" s="94">
-        <v>5.0000000000000001E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F43" s="137">
-        <v>0.14036100000000001</v>
+        <v>0.123783</v>
       </c>
       <c r="G43" s="127">
         <v>46266</v>
       </c>
       <c r="H43" s="137">
-        <v>0.13564999999999999</v>
+        <v>0.12334000000000001</v>
       </c>
       <c r="I43" s="127">
         <v>46237</v>
       </c>
       <c r="J43" s="137">
-        <v>0.13818</v>
+        <v>0.12291000000000001</v>
       </c>
       <c r="K43" s="127">
         <v>46204</v>
       </c>
       <c r="L43" s="137">
-        <v>0.13750999999999999</v>
+        <v>0.12291000000000001</v>
       </c>
       <c r="M43" s="127">
         <v>46174</v>
       </c>
       <c r="N43" s="137">
-        <v>0.13657</v>
+        <v>0.12257</v>
       </c>
       <c r="O43" s="127">
         <v>46143</v>
       </c>
       <c r="P43" s="137">
-        <v>0.13836000000000001</v>
+        <v>0.12262000000000001</v>
       </c>
       <c r="Q43" s="127">
         <v>46113</v>
       </c>
       <c r="R43" s="137">
-        <v>0.13963999999999999</v>
+        <v>0.12246</v>
       </c>
       <c r="S43" s="127">
         <v>46083</v>
       </c>
       <c r="T43" s="137">
-        <v>0.13791</v>
+        <v>0.12303</v>
       </c>
       <c r="U43" s="127">
         <v>46055</v>
@@ -18504,7 +18524,7 @@
         <v>85</v>
       </c>
       <c r="X43" s="137">
-        <v>0.140677</v>
+        <v>0.122505</v>
       </c>
       <c r="Y43" s="127">
         <v>46009</v>
@@ -18515,61 +18535,61 @@
         <v>335</v>
       </c>
       <c r="B44" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D44" s="92" t="s">
         <v>274</v>
       </c>
       <c r="E44" s="94">
-        <v>3.5000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="F44" s="137">
-        <v>4.4215999999999998E-2</v>
+        <v>0.53229499999999996</v>
       </c>
       <c r="G44" s="127">
         <v>46266</v>
       </c>
       <c r="H44" s="137">
-        <v>4.546E-2</v>
+        <v>0.52717999999999998</v>
       </c>
       <c r="I44" s="127">
         <v>46237</v>
       </c>
       <c r="J44" s="137">
-        <v>4.4130000000000003E-2</v>
+        <v>0.53078000000000003</v>
       </c>
       <c r="K44" s="127">
         <v>46204</v>
       </c>
       <c r="L44" s="137">
-        <v>4.5019999999999998E-2</v>
+        <v>0.52310000000000001</v>
       </c>
       <c r="M44" s="127">
         <v>46174</v>
       </c>
       <c r="N44" s="137">
-        <v>4.3720000000000002E-2</v>
+        <v>0.52693999999999996</v>
       </c>
       <c r="O44" s="127">
         <v>46143</v>
       </c>
       <c r="P44" s="137">
-        <v>4.5359999999999998E-2</v>
+        <v>0.52478000000000002</v>
       </c>
       <c r="Q44" s="127">
         <v>46113</v>
       </c>
       <c r="R44" s="137">
-        <v>4.0980000000000003E-2</v>
+        <v>0.52456999999999998</v>
       </c>
       <c r="S44" s="127">
         <v>46083</v>
       </c>
       <c r="T44" s="137">
-        <v>3.8260000000000002E-2</v>
+        <v>0.56008999999999998</v>
       </c>
       <c r="U44" s="127">
         <v>46055</v>
@@ -18581,7 +18601,7 @@
         <v>85</v>
       </c>
       <c r="X44" s="137">
-        <v>0</v>
+        <v>0.49054799999999998</v>
       </c>
       <c r="Y44" s="127">
         <v>46009</v>
@@ -18592,61 +18612,61 @@
         <v>335</v>
       </c>
       <c r="B45" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="D45" s="92" t="s">
         <v>274</v>
       </c>
       <c r="E45" s="94">
-        <v>4.0000000000000002E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F45" s="137">
-        <v>0.10195799999999999</v>
+        <v>0.14036100000000001</v>
       </c>
       <c r="G45" s="127">
         <v>46266</v>
       </c>
       <c r="H45" s="137">
-        <v>0.10152</v>
+        <v>0.13564999999999999</v>
       </c>
       <c r="I45" s="127">
         <v>46237</v>
       </c>
       <c r="J45" s="137">
-        <v>0.10116</v>
+        <v>0.13818</v>
       </c>
       <c r="K45" s="127">
         <v>46204</v>
       </c>
       <c r="L45" s="137">
-        <v>0.10147</v>
+        <v>0.13750999999999999</v>
       </c>
       <c r="M45" s="127">
         <v>46174</v>
       </c>
       <c r="N45" s="137">
-        <v>0.10135</v>
+        <v>0.13657</v>
       </c>
       <c r="O45" s="127">
         <v>46143</v>
       </c>
       <c r="P45" s="137">
-        <v>0.10022</v>
+        <v>0.13836000000000001</v>
       </c>
       <c r="Q45" s="127">
         <v>46113</v>
       </c>
       <c r="R45" s="137">
-        <v>0.10045999999999999</v>
+        <v>0.13963999999999999</v>
       </c>
       <c r="S45" s="127">
         <v>46083</v>
       </c>
       <c r="T45" s="137">
-        <v>0.10298</v>
+        <v>0.13791</v>
       </c>
       <c r="U45" s="127">
         <v>46055</v>
@@ -18658,7 +18678,7 @@
         <v>85</v>
       </c>
       <c r="X45" s="137">
-        <v>9.6627000000000005E-2</v>
+        <v>0.140677</v>
       </c>
       <c r="Y45" s="127">
         <v>46009</v>
@@ -18669,61 +18689,61 @@
         <v>335</v>
       </c>
       <c r="B46" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="D46" s="92" t="s">
         <v>274</v>
       </c>
       <c r="E46" s="94">
-        <v>2.9999999999999997E-4</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="F46" s="137">
-        <v>9.3530000000000002E-2</v>
+        <v>4.4215999999999998E-2</v>
       </c>
       <c r="G46" s="127">
         <v>46266</v>
       </c>
       <c r="H46" s="137">
-        <v>9.3149999999999997E-2</v>
+        <v>4.546E-2</v>
       </c>
       <c r="I46" s="127">
         <v>46237</v>
       </c>
       <c r="J46" s="137">
-        <v>8.9810000000000001E-2</v>
+        <v>4.4130000000000003E-2</v>
       </c>
       <c r="K46" s="127">
         <v>46204</v>
       </c>
       <c r="L46" s="137">
-        <v>9.2770000000000005E-2</v>
+        <v>4.5019999999999998E-2</v>
       </c>
       <c r="M46" s="127">
         <v>46174</v>
       </c>
       <c r="N46" s="137">
-        <v>9.0139999999999998E-2</v>
+        <v>4.3720000000000002E-2</v>
       </c>
       <c r="O46" s="127">
         <v>46143</v>
       </c>
       <c r="P46" s="137">
-        <v>9.3600000000000003E-2</v>
+        <v>4.5359999999999998E-2</v>
       </c>
       <c r="Q46" s="127">
         <v>46113</v>
       </c>
       <c r="R46" s="137">
-        <v>8.3930000000000005E-2</v>
+        <v>4.0980000000000003E-2</v>
       </c>
       <c r="S46" s="127">
         <v>46083</v>
       </c>
       <c r="T46" s="137">
-        <v>9.2689999999999995E-2</v>
+        <v>3.8260000000000002E-2</v>
       </c>
       <c r="U46" s="127">
         <v>46055</v>
@@ -18735,7 +18755,7 @@
         <v>85</v>
       </c>
       <c r="X46" s="137">
-        <v>9.2302999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="127">
         <v>46009</v>
@@ -18746,10 +18766,10 @@
         <v>335</v>
       </c>
       <c r="B47" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D47" s="92" t="s">
         <v>274</v>
@@ -18758,49 +18778,49 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="F47" s="137">
-        <v>7.1248000000000006E-2</v>
+        <v>0.10195799999999999</v>
       </c>
       <c r="G47" s="127">
         <v>46266</v>
       </c>
       <c r="H47" s="137">
-        <v>7.1599999999999997E-2</v>
+        <v>0.10152</v>
       </c>
       <c r="I47" s="127">
         <v>46237</v>
       </c>
       <c r="J47" s="137">
-        <v>7.0730000000000001E-2</v>
+        <v>0.10116</v>
       </c>
       <c r="K47" s="127">
         <v>46204</v>
       </c>
       <c r="L47" s="137">
-        <v>7.0120000000000002E-2</v>
+        <v>0.10147</v>
       </c>
       <c r="M47" s="127">
         <v>46174</v>
       </c>
       <c r="N47" s="137">
-        <v>6.9989999999999997E-2</v>
+        <v>0.10135</v>
       </c>
       <c r="O47" s="127">
         <v>46143</v>
       </c>
       <c r="P47" s="137">
-        <v>7.0129999999999998E-2</v>
+        <v>0.10022</v>
       </c>
       <c r="Q47" s="127">
         <v>46113</v>
       </c>
       <c r="R47" s="137">
-        <v>6.9449999999999998E-2</v>
+        <v>0.10045999999999999</v>
       </c>
       <c r="S47" s="127">
         <v>46083</v>
       </c>
       <c r="T47" s="137">
-        <v>7.1540000000000006E-2</v>
+        <v>0.10298</v>
       </c>
       <c r="U47" s="127">
         <v>46055</v>
@@ -18812,7 +18832,7 @@
         <v>85</v>
       </c>
       <c r="X47" s="137">
-        <v>0.14300099999999999</v>
+        <v>9.6627000000000005E-2</v>
       </c>
       <c r="Y47" s="127">
         <v>46009</v>
@@ -18823,10 +18843,10 @@
         <v>335</v>
       </c>
       <c r="B48" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D48" s="92" t="s">
         <v>274</v>
@@ -18835,49 +18855,49 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F48" s="137">
-        <v>0.13560700000000001</v>
+        <v>9.3530000000000002E-2</v>
       </c>
       <c r="G48" s="127">
         <v>46266</v>
       </c>
       <c r="H48" s="137">
-        <v>0.1351</v>
+        <v>9.3149999999999997E-2</v>
       </c>
       <c r="I48" s="127">
         <v>46237</v>
       </c>
       <c r="J48" s="137">
-        <v>0.13542999999999999</v>
+        <v>8.9810000000000001E-2</v>
       </c>
       <c r="K48" s="127">
         <v>46204</v>
       </c>
       <c r="L48" s="137">
-        <v>0.13396</v>
+        <v>9.2770000000000005E-2</v>
       </c>
       <c r="M48" s="127">
         <v>46174</v>
       </c>
       <c r="N48" s="137">
-        <v>0.13463</v>
+        <v>9.0139999999999998E-2</v>
       </c>
       <c r="O48" s="127">
         <v>46143</v>
       </c>
       <c r="P48" s="137">
-        <v>0.13347000000000001</v>
+        <v>9.3600000000000003E-2</v>
       </c>
       <c r="Q48" s="127">
         <v>46113</v>
       </c>
       <c r="R48" s="137">
-        <v>0.13635</v>
+        <v>8.3930000000000005E-2</v>
       </c>
       <c r="S48" s="127">
         <v>46083</v>
       </c>
       <c r="T48" s="137">
-        <v>0.13150000000000001</v>
+        <v>9.2689999999999995E-2</v>
       </c>
       <c r="U48" s="127">
         <v>46055</v>
@@ -18889,7 +18909,7 @@
         <v>85</v>
       </c>
       <c r="X48" s="137">
-        <v>0.13450899999999999</v>
+        <v>9.2302999999999996E-2</v>
       </c>
       <c r="Y48" s="127">
         <v>46009</v>
@@ -18897,169 +18917,167 @@
     </row>
     <row r="49" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>315</v>
-      </c>
-      <c r="B49" s="106" t="s">
-        <v>351</v>
-      </c>
-      <c r="C49" s="105" t="s">
-        <v>286</v>
-      </c>
-      <c r="D49" s="110" t="s">
+        <v>335</v>
+      </c>
+      <c r="B49" t="s">
+        <v>347</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D49" s="92" t="s">
         <v>274</v>
       </c>
-      <c r="E49" s="111">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="F49" s="138">
-        <v>0</v>
-      </c>
-      <c r="G49" s="128">
-        <v>46286</v>
-      </c>
-      <c r="H49" s="138">
-        <v>0</v>
-      </c>
-      <c r="I49" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="J49" s="138">
-        <v>0</v>
-      </c>
-      <c r="K49" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="L49" s="138">
-        <v>0.38488</v>
-      </c>
-      <c r="M49" s="128">
-        <v>46195</v>
-      </c>
-      <c r="N49" s="138">
-        <v>0</v>
-      </c>
-      <c r="O49" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="P49" s="138">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="R49" s="138">
-        <v>0.38518000000000002</v>
+      <c r="E49" s="94">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F49" s="137">
+        <v>7.1248000000000006E-2</v>
+      </c>
+      <c r="G49" s="127">
+        <v>46266</v>
+      </c>
+      <c r="H49" s="137">
+        <v>7.1599999999999997E-2</v>
+      </c>
+      <c r="I49" s="127">
+        <v>46237</v>
+      </c>
+      <c r="J49" s="137">
+        <v>7.0730000000000001E-2</v>
+      </c>
+      <c r="K49" s="127">
+        <v>46204</v>
+      </c>
+      <c r="L49" s="137">
+        <v>7.0120000000000002E-2</v>
+      </c>
+      <c r="M49" s="127">
+        <v>46174</v>
+      </c>
+      <c r="N49" s="137">
+        <v>6.9989999999999997E-2</v>
+      </c>
+      <c r="O49" s="127">
+        <v>46143</v>
+      </c>
+      <c r="P49" s="137">
+        <v>7.0129999999999998E-2</v>
+      </c>
+      <c r="Q49" s="127">
+        <v>46113</v>
+      </c>
+      <c r="R49" s="137">
+        <v>6.9449999999999998E-2</v>
       </c>
       <c r="S49" s="127">
-        <v>46104</v>
-      </c>
-      <c r="T49" s="138">
-        <v>0</v>
-      </c>
-      <c r="U49" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="V49" s="138">
+        <v>46083</v>
+      </c>
+      <c r="T49" s="137">
+        <v>7.1540000000000006E-2</v>
+      </c>
+      <c r="U49" s="127">
+        <v>46055</v>
+      </c>
+      <c r="V49" s="137">
         <v>0</v>
       </c>
       <c r="W49" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="X49" s="138">
-        <v>0.37302000000000002</v>
-      </c>
-      <c r="Y49" s="128">
-        <v>46013</v>
-      </c>
-      <c r="Z49" s="96"/>
+      <c r="X49" s="137">
+        <v>0.14300099999999999</v>
+      </c>
+      <c r="Y49" s="127">
+        <v>46009</v>
+      </c>
     </row>
     <row r="50" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>315</v>
-      </c>
-      <c r="B50" s="106" t="s">
-        <v>357</v>
-      </c>
-      <c r="C50" s="105" t="s">
-        <v>290</v>
-      </c>
-      <c r="D50" s="110" t="s">
+        <v>335</v>
+      </c>
+      <c r="B50" t="s">
+        <v>348</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D50" s="92" t="s">
         <v>274</v>
       </c>
-      <c r="E50" s="111">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="F50" s="138">
-        <v>0</v>
-      </c>
-      <c r="G50" s="128">
-        <v>46286</v>
-      </c>
-      <c r="H50" s="138">
-        <v>0</v>
-      </c>
-      <c r="I50" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="J50" s="138">
-        <v>0</v>
-      </c>
-      <c r="K50" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="L50" s="138">
-        <v>0.18708</v>
-      </c>
-      <c r="M50" s="128">
-        <v>46195</v>
-      </c>
-      <c r="N50" s="138">
-        <v>0</v>
-      </c>
-      <c r="O50" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="P50" s="138">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="R50" s="138">
-        <v>0.25148999999999999</v>
+      <c r="E50" s="94">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F50" s="137">
+        <v>0.13560700000000001</v>
+      </c>
+      <c r="G50" s="127">
+        <v>46266</v>
+      </c>
+      <c r="H50" s="137">
+        <v>0.1351</v>
+      </c>
+      <c r="I50" s="127">
+        <v>46237</v>
+      </c>
+      <c r="J50" s="137">
+        <v>0.13542999999999999</v>
+      </c>
+      <c r="K50" s="127">
+        <v>46204</v>
+      </c>
+      <c r="L50" s="137">
+        <v>0.13396</v>
+      </c>
+      <c r="M50" s="127">
+        <v>46174</v>
+      </c>
+      <c r="N50" s="137">
+        <v>0.13463</v>
+      </c>
+      <c r="O50" s="127">
+        <v>46143</v>
+      </c>
+      <c r="P50" s="137">
+        <v>0.13347000000000001</v>
+      </c>
+      <c r="Q50" s="127">
+        <v>46113</v>
+      </c>
+      <c r="R50" s="137">
+        <v>0.13635</v>
       </c>
       <c r="S50" s="127">
-        <v>46104</v>
-      </c>
-      <c r="T50" s="138">
-        <v>0</v>
-      </c>
-      <c r="U50" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="V50" s="138">
+        <v>46083</v>
+      </c>
+      <c r="T50" s="137">
+        <v>0.13150000000000001</v>
+      </c>
+      <c r="U50" s="127">
+        <v>46055</v>
+      </c>
+      <c r="V50" s="137">
         <v>0</v>
       </c>
       <c r="W50" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="X50" s="138">
-        <v>0.19077</v>
-      </c>
-      <c r="Y50" s="128">
-        <v>46013</v>
-      </c>
-      <c r="Z50" s="96"/>
+      <c r="X50" s="137">
+        <v>0.13450899999999999</v>
+      </c>
+      <c r="Y50" s="127">
+        <v>46009</v>
+      </c>
     </row>
     <row r="51" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>315</v>
       </c>
       <c r="B51" s="106" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C51" s="105" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D51" s="110" t="s">
         <v>274</v>
@@ -19067,10 +19085,10 @@
       <c r="E51" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F51" s="138">
-        <v>0</v>
-      </c>
-      <c r="G51" s="128">
+      <c r="F51" s="151">
+        <v>0</v>
+      </c>
+      <c r="G51" s="152">
         <v>46286</v>
       </c>
       <c r="H51" s="138">
@@ -19086,7 +19104,7 @@
         <v>85</v>
       </c>
       <c r="L51" s="138">
-        <v>0.65625</v>
+        <v>0.38488</v>
       </c>
       <c r="M51" s="128">
         <v>46195</v>
@@ -19104,7 +19122,7 @@
         <v>85</v>
       </c>
       <c r="R51" s="138">
-        <v>0.59467999999999999</v>
+        <v>0.38518000000000002</v>
       </c>
       <c r="S51" s="127">
         <v>46104</v>
@@ -19122,7 +19140,7 @@
         <v>85</v>
       </c>
       <c r="X51" s="138">
-        <v>0.65681999999999996</v>
+        <v>0.37302000000000002</v>
       </c>
       <c r="Y51" s="128">
         <v>46013</v>
@@ -19134,10 +19152,10 @@
         <v>315</v>
       </c>
       <c r="B52" s="106" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C52" s="105" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D52" s="110" t="s">
         <v>274</v>
@@ -19145,10 +19163,10 @@
       <c r="E52" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F52" s="138">
-        <v>0</v>
-      </c>
-      <c r="G52" s="128">
+      <c r="F52" s="151">
+        <v>0</v>
+      </c>
+      <c r="G52" s="152">
         <v>46286</v>
       </c>
       <c r="H52" s="138">
@@ -19164,7 +19182,7 @@
         <v>85</v>
       </c>
       <c r="L52" s="138">
-        <v>0.44408999999999998</v>
+        <v>0.18708</v>
       </c>
       <c r="M52" s="128">
         <v>46195</v>
@@ -19182,7 +19200,7 @@
         <v>85</v>
       </c>
       <c r="R52" s="138">
-        <v>0.45321</v>
+        <v>0.25148999999999999</v>
       </c>
       <c r="S52" s="127">
         <v>46104</v>
@@ -19200,7 +19218,7 @@
         <v>85</v>
       </c>
       <c r="X52" s="138">
-        <v>0.53159999999999996</v>
+        <v>0.19077</v>
       </c>
       <c r="Y52" s="128">
         <v>46013</v>
@@ -19212,10 +19230,10 @@
         <v>315</v>
       </c>
       <c r="B53" s="106" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C53" s="105" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D53" s="110" t="s">
         <v>274</v>
@@ -19223,10 +19241,10 @@
       <c r="E53" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F53" s="138">
-        <v>0</v>
-      </c>
-      <c r="G53" s="128">
+      <c r="F53" s="151">
+        <v>0</v>
+      </c>
+      <c r="G53" s="152">
         <v>46286</v>
       </c>
       <c r="H53" s="138">
@@ -19242,7 +19260,7 @@
         <v>85</v>
       </c>
       <c r="L53" s="138">
-        <v>0.38114999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="M53" s="128">
         <v>46195</v>
@@ -19260,7 +19278,7 @@
         <v>85</v>
       </c>
       <c r="R53" s="138">
-        <v>0.27106000000000002</v>
+        <v>0.59467999999999999</v>
       </c>
       <c r="S53" s="127">
         <v>46104</v>
@@ -19278,7 +19296,7 @@
         <v>85</v>
       </c>
       <c r="X53" s="138">
-        <v>0.43611</v>
+        <v>0.65681999999999996</v>
       </c>
       <c r="Y53" s="128">
         <v>46013</v>
@@ -19290,10 +19308,10 @@
         <v>315</v>
       </c>
       <c r="B54" s="106" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="C54" s="105" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="D54" s="110" t="s">
         <v>274</v>
@@ -19301,10 +19319,10 @@
       <c r="E54" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F54" s="138">
-        <v>0</v>
-      </c>
-      <c r="G54" s="128">
+      <c r="F54" s="151">
+        <v>0</v>
+      </c>
+      <c r="G54" s="152">
         <v>46286</v>
       </c>
       <c r="H54" s="138">
@@ -19320,7 +19338,7 @@
         <v>85</v>
       </c>
       <c r="L54" s="138">
-        <v>0.57418999999999998</v>
+        <v>0.44408999999999998</v>
       </c>
       <c r="M54" s="128">
         <v>46195</v>
@@ -19338,7 +19356,7 @@
         <v>85</v>
       </c>
       <c r="R54" s="138">
-        <v>0.45490000000000003</v>
+        <v>0.45321</v>
       </c>
       <c r="S54" s="127">
         <v>46104</v>
@@ -19356,7 +19374,7 @@
         <v>85</v>
       </c>
       <c r="X54" s="138">
-        <v>0.62697000000000003</v>
+        <v>0.53159999999999996</v>
       </c>
       <c r="Y54" s="128">
         <v>46013</v>
@@ -19368,10 +19386,10 @@
         <v>315</v>
       </c>
       <c r="B55" s="106" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C55" s="105" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D55" s="110" t="s">
         <v>274</v>
@@ -19379,10 +19397,10 @@
       <c r="E55" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F55" s="138">
-        <v>0</v>
-      </c>
-      <c r="G55" s="128">
+      <c r="F55" s="151">
+        <v>0</v>
+      </c>
+      <c r="G55" s="152">
         <v>46286</v>
       </c>
       <c r="H55" s="138">
@@ -19398,7 +19416,7 @@
         <v>85</v>
       </c>
       <c r="L55" s="138">
-        <v>0.22792000000000001</v>
+        <v>0.38114999999999999</v>
       </c>
       <c r="M55" s="128">
         <v>46195</v>
@@ -19416,7 +19434,7 @@
         <v>85</v>
       </c>
       <c r="R55" s="138">
-        <v>0.16750999999999999</v>
+        <v>0.27106000000000002</v>
       </c>
       <c r="S55" s="127">
         <v>46104</v>
@@ -19434,7 +19452,7 @@
         <v>85</v>
       </c>
       <c r="X55" s="138">
-        <v>0.21883</v>
+        <v>0.43611</v>
       </c>
       <c r="Y55" s="128">
         <v>46013</v>
@@ -19446,10 +19464,10 @@
         <v>315</v>
       </c>
       <c r="B56" s="106" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C56" s="105" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="D56" s="110" t="s">
         <v>274</v>
@@ -19457,10 +19475,10 @@
       <c r="E56" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F56" s="138">
-        <v>0</v>
-      </c>
-      <c r="G56" s="128">
+      <c r="F56" s="151">
+        <v>0</v>
+      </c>
+      <c r="G56" s="152">
         <v>46286</v>
       </c>
       <c r="H56" s="138">
@@ -19476,7 +19494,7 @@
         <v>85</v>
       </c>
       <c r="L56" s="138">
-        <v>0.28442000000000001</v>
+        <v>0.57418999999999998</v>
       </c>
       <c r="M56" s="128">
         <v>46195</v>
@@ -19494,7 +19512,7 @@
         <v>85</v>
       </c>
       <c r="R56" s="138">
-        <v>0.30993999999999999</v>
+        <v>0.45490000000000003</v>
       </c>
       <c r="S56" s="127">
         <v>46104</v>
@@ -19512,7 +19530,7 @@
         <v>85</v>
       </c>
       <c r="X56" s="138">
-        <v>0.31720999999999999</v>
+        <v>0.62697000000000003</v>
       </c>
       <c r="Y56" s="128">
         <v>46013</v>
@@ -19524,10 +19542,10 @@
         <v>315</v>
       </c>
       <c r="B57" s="106" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="C57" s="105" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="D57" s="110" t="s">
         <v>274</v>
@@ -19535,10 +19553,10 @@
       <c r="E57" s="111">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F57" s="138">
-        <v>0</v>
-      </c>
-      <c r="G57" s="128">
+      <c r="F57" s="151">
+        <v>0</v>
+      </c>
+      <c r="G57" s="152">
         <v>46286</v>
       </c>
       <c r="H57" s="138">
@@ -19554,7 +19572,7 @@
         <v>85</v>
       </c>
       <c r="L57" s="138">
-        <v>0.23322000000000001</v>
+        <v>0.22792000000000001</v>
       </c>
       <c r="M57" s="128">
         <v>46195</v>
@@ -19572,7 +19590,7 @@
         <v>85</v>
       </c>
       <c r="R57" s="138">
-        <v>0.21562300000000001</v>
+        <v>0.16750999999999999</v>
       </c>
       <c r="S57" s="127">
         <v>46104</v>
@@ -19590,7 +19608,7 @@
         <v>85</v>
       </c>
       <c r="X57" s="138">
-        <v>0.24084800000000001</v>
+        <v>0.21883</v>
       </c>
       <c r="Y57" s="128">
         <v>46013</v>
@@ -19599,218 +19617,220 @@
     </row>
     <row r="58" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>335</v>
-      </c>
-      <c r="B58" t="s">
-        <v>337</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D58" s="92" t="s">
-        <v>262</v>
-      </c>
-      <c r="E58" s="94">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="F58" s="137">
-        <v>0.159</v>
-      </c>
-      <c r="G58" s="127">
-        <v>46266</v>
-      </c>
-      <c r="H58" s="137">
-        <v>0.16839999999999999</v>
-      </c>
-      <c r="I58" s="127">
-        <v>46237</v>
-      </c>
-      <c r="J58" s="137">
-        <v>0.17100000000000001</v>
-      </c>
-      <c r="K58" s="127">
-        <v>46204</v>
-      </c>
-      <c r="L58" s="137">
-        <v>0.1535</v>
-      </c>
-      <c r="M58" s="127">
-        <v>46174</v>
-      </c>
-      <c r="N58" s="137">
-        <v>0.15629999999999999</v>
-      </c>
-      <c r="O58" s="127">
-        <v>46143</v>
-      </c>
-      <c r="P58" s="137">
-        <v>0.17449999999999999</v>
-      </c>
-      <c r="Q58" s="127">
-        <v>46113</v>
-      </c>
-      <c r="R58" s="137">
-        <v>0.14050000000000001</v>
+        <v>315</v>
+      </c>
+      <c r="B58" s="106" t="s">
+        <v>356</v>
+      </c>
+      <c r="C58" s="105" t="s">
+        <v>310</v>
+      </c>
+      <c r="D58" s="110" t="s">
+        <v>274</v>
+      </c>
+      <c r="E58" s="111">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F58" s="151">
+        <v>0</v>
+      </c>
+      <c r="G58" s="152">
+        <v>46286</v>
+      </c>
+      <c r="H58" s="138">
+        <v>0</v>
+      </c>
+      <c r="I58" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="J58" s="138">
+        <v>0</v>
+      </c>
+      <c r="K58" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="L58" s="138">
+        <v>0.28442000000000001</v>
+      </c>
+      <c r="M58" s="128">
+        <v>46195</v>
+      </c>
+      <c r="N58" s="138">
+        <v>0</v>
+      </c>
+      <c r="O58" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="P58" s="138">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="R58" s="138">
+        <v>0.30993999999999999</v>
       </c>
       <c r="S58" s="127">
-        <v>46083</v>
-      </c>
-      <c r="T58" s="137">
-        <v>0.15909999999999999</v>
-      </c>
-      <c r="U58" s="127">
-        <v>46055</v>
-      </c>
-      <c r="V58" s="137">
+        <v>46104</v>
+      </c>
+      <c r="T58" s="138">
+        <v>0</v>
+      </c>
+      <c r="U58" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="V58" s="138">
         <v>0</v>
       </c>
       <c r="W58" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="X58" s="137">
-        <v>0.15989999999999999</v>
-      </c>
-      <c r="Y58" s="127">
-        <v>46020</v>
-      </c>
+      <c r="X58" s="138">
+        <v>0.31720999999999999</v>
+      </c>
+      <c r="Y58" s="128">
+        <v>46013</v>
+      </c>
+      <c r="Z58" s="96"/>
     </row>
     <row r="59" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>335</v>
-      </c>
-      <c r="B59" t="s">
-        <v>336</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="D59" s="92" t="s">
-        <v>263</v>
-      </c>
-      <c r="E59" s="94">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="F59" s="137">
-        <v>0.252886</v>
-      </c>
-      <c r="G59" s="127">
-        <v>46266</v>
-      </c>
-      <c r="H59" s="137">
-        <v>0.25155</v>
-      </c>
-      <c r="I59" s="127">
-        <v>46237</v>
-      </c>
-      <c r="J59" s="137">
-        <v>0.24446999999999999</v>
-      </c>
-      <c r="K59" s="127">
-        <v>46204</v>
-      </c>
-      <c r="L59" s="137">
-        <v>0.24726000000000001</v>
-      </c>
-      <c r="M59" s="127">
-        <v>46174</v>
-      </c>
-      <c r="N59" s="137">
-        <v>0.24171300000000001</v>
-      </c>
-      <c r="O59" s="127">
-        <v>46143</v>
-      </c>
-      <c r="P59" s="137">
-        <v>0.25001600000000002</v>
-      </c>
-      <c r="Q59" s="127">
-        <v>46113</v>
-      </c>
-      <c r="R59" s="137">
-        <v>0.227824</v>
+        <v>315</v>
+      </c>
+      <c r="B59" s="106" t="s">
+        <v>371</v>
+      </c>
+      <c r="C59" s="105" t="s">
+        <v>277</v>
+      </c>
+      <c r="D59" s="110" t="s">
+        <v>274</v>
+      </c>
+      <c r="E59" s="111">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F59" s="151">
+        <v>0</v>
+      </c>
+      <c r="G59" s="152">
+        <v>46286</v>
+      </c>
+      <c r="H59" s="138">
+        <v>0</v>
+      </c>
+      <c r="I59" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="J59" s="138">
+        <v>0</v>
+      </c>
+      <c r="K59" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="L59" s="138">
+        <v>0.23322000000000001</v>
+      </c>
+      <c r="M59" s="128">
+        <v>46195</v>
+      </c>
+      <c r="N59" s="138">
+        <v>0</v>
+      </c>
+      <c r="O59" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="P59" s="138">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="R59" s="138">
+        <v>0.21562300000000001</v>
       </c>
       <c r="S59" s="127">
-        <v>46083</v>
-      </c>
-      <c r="T59" s="137">
-        <v>0.24546999999999999</v>
-      </c>
-      <c r="U59" s="127">
-        <v>46055</v>
-      </c>
-      <c r="V59" s="137">
+        <v>46104</v>
+      </c>
+      <c r="T59" s="138">
+        <v>0</v>
+      </c>
+      <c r="U59" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="V59" s="138">
         <v>0</v>
       </c>
       <c r="W59" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="X59" s="137">
-        <v>0.246638</v>
-      </c>
-      <c r="Y59" s="127">
-        <v>46009</v>
-      </c>
+      <c r="X59" s="138">
+        <v>0.24084800000000001</v>
+      </c>
+      <c r="Y59" s="128">
+        <v>46013</v>
+      </c>
+      <c r="Z59" s="96"/>
     </row>
     <row r="60" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>335</v>
       </c>
       <c r="B60" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>257</v>
+        <v>191</v>
       </c>
       <c r="D60" s="92" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E60" s="94">
-        <v>5.9999999999999995E-4</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="F60" s="137">
-        <v>0.26019999999999999</v>
+        <v>0.159</v>
       </c>
       <c r="G60" s="127">
         <v>46266</v>
       </c>
       <c r="H60" s="137">
-        <v>0.25640000000000002</v>
+        <v>0.16839999999999999</v>
       </c>
       <c r="I60" s="127">
         <v>46237</v>
       </c>
       <c r="J60" s="137">
-        <v>0.26240000000000002</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="K60" s="127">
         <v>46204</v>
       </c>
       <c r="L60" s="137">
-        <v>0.25750000000000001</v>
+        <v>0.1535</v>
       </c>
       <c r="M60" s="127">
         <v>46174</v>
       </c>
       <c r="N60" s="137">
-        <v>0.26029999999999998</v>
+        <v>0.15629999999999999</v>
       </c>
       <c r="O60" s="127">
         <v>46143</v>
       </c>
       <c r="P60" s="137">
-        <v>0.25819999999999999</v>
+        <v>0.17449999999999999</v>
       </c>
       <c r="Q60" s="127">
         <v>46113</v>
       </c>
       <c r="R60" s="137">
-        <v>0.25669999999999998</v>
+        <v>0.14050000000000001</v>
       </c>
       <c r="S60" s="127">
         <v>46083</v>
       </c>
       <c r="T60" s="137">
-        <v>0.25080000000000002</v>
+        <v>0.15909999999999999</v>
       </c>
       <c r="U60" s="127">
         <v>46055</v>
@@ -19822,10 +19842,10 @@
         <v>85</v>
       </c>
       <c r="X60" s="137">
-        <v>0.2626</v>
+        <v>0.15989999999999999</v>
       </c>
       <c r="Y60" s="127">
-        <v>46015</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="61" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19833,10 +19853,10 @@
         <v>335</v>
       </c>
       <c r="B61" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="D61" s="92" t="s">
         <v>263</v>
@@ -19845,49 +19865,49 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F61" s="137">
-        <v>0.32729999999999998</v>
+        <v>0.252886</v>
       </c>
       <c r="G61" s="127">
         <v>46266</v>
       </c>
       <c r="H61" s="137">
-        <v>0.32619999999999999</v>
+        <v>0.25155</v>
       </c>
       <c r="I61" s="127">
         <v>46237</v>
       </c>
       <c r="J61" s="137">
-        <v>0.316</v>
+        <v>0.24446999999999999</v>
       </c>
       <c r="K61" s="127">
         <v>46204</v>
       </c>
       <c r="L61" s="137">
-        <v>0.31900000000000001</v>
+        <v>0.24726000000000001</v>
       </c>
       <c r="M61" s="127">
         <v>46174</v>
       </c>
       <c r="N61" s="137">
-        <v>0.31409999999999999</v>
+        <v>0.24171300000000001</v>
       </c>
       <c r="O61" s="127">
         <v>46143</v>
       </c>
       <c r="P61" s="137">
-        <v>0.32269999999999999</v>
+        <v>0.25001600000000002</v>
       </c>
       <c r="Q61" s="127">
         <v>46113</v>
       </c>
       <c r="R61" s="137">
-        <v>0.2913</v>
+        <v>0.227824</v>
       </c>
       <c r="S61" s="127">
         <v>46083</v>
       </c>
       <c r="T61" s="137">
-        <v>0.32369999999999999</v>
+        <v>0.24546999999999999</v>
       </c>
       <c r="U61" s="127">
         <v>46055</v>
@@ -19899,7 +19919,7 @@
         <v>85</v>
       </c>
       <c r="X61" s="137">
-        <v>0.3105</v>
+        <v>0.246638</v>
       </c>
       <c r="Y61" s="127">
         <v>46009</v>
@@ -19910,61 +19930,61 @@
         <v>335</v>
       </c>
       <c r="B62" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D62" s="92" t="s">
         <v>263</v>
       </c>
       <c r="E62" s="94">
-        <v>1.5E-3</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="F62" s="137">
-        <v>0.32069999999999999</v>
+        <v>0.26019999999999999</v>
       </c>
       <c r="G62" s="127">
         <v>46266</v>
       </c>
       <c r="H62" s="137">
-        <v>0.34660000000000002</v>
+        <v>0.25640000000000002</v>
       </c>
       <c r="I62" s="127">
         <v>46237</v>
       </c>
       <c r="J62" s="137">
-        <v>0.31369999999999998</v>
+        <v>0.26240000000000002</v>
       </c>
       <c r="K62" s="127">
         <v>46204</v>
       </c>
       <c r="L62" s="137">
-        <v>0.31890000000000002</v>
+        <v>0.25750000000000001</v>
       </c>
       <c r="M62" s="127">
         <v>46174</v>
       </c>
       <c r="N62" s="137">
-        <v>0.318</v>
+        <v>0.26029999999999998</v>
       </c>
       <c r="O62" s="127">
         <v>46143</v>
       </c>
       <c r="P62" s="137">
-        <v>0.32879999999999998</v>
+        <v>0.25819999999999999</v>
       </c>
       <c r="Q62" s="127">
         <v>46113</v>
       </c>
       <c r="R62" s="137">
-        <v>0.3196</v>
+        <v>0.25669999999999998</v>
       </c>
       <c r="S62" s="127">
         <v>46083</v>
       </c>
       <c r="T62" s="137">
-        <v>0.33960000000000001</v>
+        <v>0.25080000000000002</v>
       </c>
       <c r="U62" s="127">
         <v>46055</v>
@@ -19976,10 +19996,10 @@
         <v>85</v>
       </c>
       <c r="X62" s="137">
-        <v>0.31519999999999998</v>
+        <v>0.2626</v>
       </c>
       <c r="Y62" s="127">
-        <v>46009</v>
+        <v>46015</v>
       </c>
     </row>
     <row r="63" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19987,61 +20007,61 @@
         <v>335</v>
       </c>
       <c r="B63" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D63" s="92" t="s">
         <v>263</v>
       </c>
       <c r="E63" s="94">
-        <v>6.9999999999999999E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F63" s="137">
-        <v>0.1206</v>
+        <v>0.32729999999999998</v>
       </c>
       <c r="G63" s="127">
         <v>46266</v>
       </c>
       <c r="H63" s="137">
-        <v>0.11849999999999999</v>
+        <v>0.32619999999999999</v>
       </c>
       <c r="I63" s="127">
         <v>46237</v>
       </c>
       <c r="J63" s="137">
-        <v>0.11119999999999999</v>
+        <v>0.316</v>
       </c>
       <c r="K63" s="127">
         <v>46204</v>
       </c>
       <c r="L63" s="137">
-        <v>0.11409999999999999</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="M63" s="127">
         <v>46174</v>
       </c>
       <c r="N63" s="137">
-        <v>0.11260000000000001</v>
+        <v>0.31409999999999999</v>
       </c>
       <c r="O63" s="127">
         <v>46143</v>
       </c>
       <c r="P63" s="137">
-        <v>0.11169999999999999</v>
+        <v>0.32269999999999999</v>
       </c>
       <c r="Q63" s="127">
         <v>46113</v>
       </c>
       <c r="R63" s="137">
-        <v>9.98E-2</v>
+        <v>0.2913</v>
       </c>
       <c r="S63" s="127">
         <v>46083</v>
       </c>
       <c r="T63" s="137">
-        <v>0.1124</v>
+        <v>0.32369999999999999</v>
       </c>
       <c r="U63" s="127">
         <v>46055</v>
@@ -20053,7 +20073,7 @@
         <v>85</v>
       </c>
       <c r="X63" s="137">
-        <v>0.96860000000000002</v>
+        <v>0.3105</v>
       </c>
       <c r="Y63" s="127">
         <v>46009</v>
@@ -20064,61 +20084,61 @@
         <v>335</v>
       </c>
       <c r="B64" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="D64" s="92" t="s">
         <v>263</v>
       </c>
       <c r="E64" s="94">
-        <v>2.9999999999999997E-4</v>
+        <v>1.5E-3</v>
       </c>
       <c r="F64" s="137">
-        <v>0.36149999999999999</v>
+        <v>0.32069999999999999</v>
       </c>
       <c r="G64" s="127">
         <v>46266</v>
       </c>
       <c r="H64" s="137">
-        <v>0.35020000000000001</v>
+        <v>0.34660000000000002</v>
       </c>
       <c r="I64" s="127">
         <v>46237</v>
       </c>
       <c r="J64" s="137">
-        <v>0.3422</v>
+        <v>0.31369999999999998</v>
       </c>
       <c r="K64" s="127">
         <v>46204</v>
       </c>
       <c r="L64" s="137">
-        <v>0.35510000000000003</v>
+        <v>0.31890000000000002</v>
       </c>
       <c r="M64" s="127">
         <v>46174</v>
       </c>
       <c r="N64" s="137">
-        <v>0.32740000000000002</v>
+        <v>0.318</v>
       </c>
       <c r="O64" s="127">
         <v>46143</v>
       </c>
       <c r="P64" s="137">
-        <v>0.35610000000000003</v>
+        <v>0.32879999999999998</v>
       </c>
       <c r="Q64" s="127">
         <v>46113</v>
       </c>
       <c r="R64" s="137">
-        <v>0.31809999999999999</v>
+        <v>0.3196</v>
       </c>
       <c r="S64" s="127">
         <v>46083</v>
       </c>
       <c r="T64" s="137">
-        <v>0.34560000000000002</v>
+        <v>0.33960000000000001</v>
       </c>
       <c r="U64" s="127">
         <v>46055</v>
@@ -20130,7 +20150,7 @@
         <v>85</v>
       </c>
       <c r="X64" s="137">
-        <v>0.34920000000000001</v>
+        <v>0.31519999999999998</v>
       </c>
       <c r="Y64" s="127">
         <v>46009</v>
@@ -20141,61 +20161,61 @@
         <v>335</v>
       </c>
       <c r="B65" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>205</v>
+        <v>247</v>
       </c>
       <c r="D65" s="92" t="s">
         <v>263</v>
       </c>
       <c r="E65" s="94">
-        <v>2.9999999999999997E-4</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="F65" s="137">
-        <v>0.21529999999999999</v>
+        <v>0.1206</v>
       </c>
       <c r="G65" s="127">
         <v>46266</v>
       </c>
       <c r="H65" s="137">
-        <v>0.2145</v>
+        <v>0.11849999999999999</v>
       </c>
       <c r="I65" s="127">
         <v>46237</v>
       </c>
       <c r="J65" s="137">
-        <v>0.20760000000000001</v>
+        <v>0.11119999999999999</v>
       </c>
       <c r="K65" s="127">
         <v>46204</v>
       </c>
       <c r="L65" s="137">
-        <v>0.21410000000000001</v>
+        <v>0.11409999999999999</v>
       </c>
       <c r="M65" s="127">
         <v>46174</v>
       </c>
       <c r="N65" s="137">
-        <v>0.2099</v>
+        <v>0.11260000000000001</v>
       </c>
       <c r="O65" s="127">
         <v>46143</v>
       </c>
       <c r="P65" s="137">
-        <v>0.2258</v>
+        <v>0.11169999999999999</v>
       </c>
       <c r="Q65" s="127">
         <v>46113</v>
       </c>
       <c r="R65" s="137">
-        <v>0.18740000000000001</v>
+        <v>9.98E-2</v>
       </c>
       <c r="S65" s="127">
         <v>46083</v>
       </c>
       <c r="T65" s="137">
-        <v>0.2145</v>
+        <v>0.1124</v>
       </c>
       <c r="U65" s="127">
         <v>46055</v>
@@ -20207,7 +20227,7 @@
         <v>85</v>
       </c>
       <c r="X65" s="137">
-        <v>0.214</v>
+        <v>0.96860000000000002</v>
       </c>
       <c r="Y65" s="127">
         <v>46009</v>
@@ -20218,10 +20238,10 @@
         <v>335</v>
       </c>
       <c r="B66" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D66" s="92" t="s">
         <v>263</v>
@@ -20230,49 +20250,49 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F66" s="137">
-        <v>0.1666</v>
+        <v>0.36149999999999999</v>
       </c>
       <c r="G66" s="127">
         <v>46266</v>
       </c>
       <c r="H66" s="137">
-        <v>0.16800000000000001</v>
+        <v>0.35020000000000001</v>
       </c>
       <c r="I66" s="127">
         <v>46237</v>
       </c>
       <c r="J66" s="137">
-        <v>0.16450000000000001</v>
+        <v>0.3422</v>
       </c>
       <c r="K66" s="127">
         <v>46204</v>
       </c>
       <c r="L66" s="137">
-        <v>0.16339999999999999</v>
+        <v>0.35510000000000003</v>
       </c>
       <c r="M66" s="127">
         <v>46174</v>
       </c>
       <c r="N66" s="137">
-        <v>0.16089999999999999</v>
+        <v>0.32740000000000002</v>
       </c>
       <c r="O66" s="127">
         <v>46143</v>
       </c>
       <c r="P66" s="137">
-        <v>0.16170000000000001</v>
+        <v>0.35610000000000003</v>
       </c>
       <c r="Q66" s="127">
         <v>46113</v>
       </c>
       <c r="R66" s="137">
-        <v>0.16089999999999999</v>
+        <v>0.31809999999999999</v>
       </c>
       <c r="S66" s="127">
         <v>46083</v>
       </c>
       <c r="T66" s="137">
-        <v>0.16450000000000001</v>
+        <v>0.34560000000000002</v>
       </c>
       <c r="U66" s="127">
         <v>46055</v>
@@ -20284,7 +20304,7 @@
         <v>85</v>
       </c>
       <c r="X66" s="137">
-        <v>0.15989999999999999</v>
+        <v>0.34920000000000001</v>
       </c>
       <c r="Y66" s="127">
         <v>46009</v>
@@ -20295,10 +20315,10 @@
         <v>335</v>
       </c>
       <c r="B67" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D67" s="92" t="s">
         <v>263</v>
@@ -20307,49 +20327,49 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F67" s="137">
-        <v>0.1434</v>
+        <v>0.21529999999999999</v>
       </c>
       <c r="G67" s="127">
         <v>46266</v>
       </c>
       <c r="H67" s="137">
-        <v>0.14149999999999999</v>
+        <v>0.2145</v>
       </c>
       <c r="I67" s="127">
         <v>46237</v>
       </c>
       <c r="J67" s="137">
-        <v>0.14199999999999999</v>
+        <v>0.20760000000000001</v>
       </c>
       <c r="K67" s="127">
         <v>46204</v>
       </c>
       <c r="L67" s="137">
-        <v>0.1381</v>
+        <v>0.21410000000000001</v>
       </c>
       <c r="M67" s="127">
         <v>46174</v>
       </c>
       <c r="N67" s="137">
-        <v>0.14230000000000001</v>
+        <v>0.2099</v>
       </c>
       <c r="O67" s="127">
         <v>46143</v>
       </c>
       <c r="P67" s="137">
-        <v>0.14149999999999999</v>
+        <v>0.2258</v>
       </c>
       <c r="Q67" s="127">
         <v>46113</v>
       </c>
       <c r="R67" s="137">
-        <v>0.1487</v>
+        <v>0.18740000000000001</v>
       </c>
       <c r="S67" s="127">
         <v>46083</v>
       </c>
       <c r="T67" s="137">
-        <v>0.13980000000000001</v>
+        <v>0.2145</v>
       </c>
       <c r="U67" s="127">
         <v>46055</v>
@@ -20361,7 +20381,7 @@
         <v>85</v>
       </c>
       <c r="X67" s="137">
-        <v>0.14169999999999999</v>
+        <v>0.214</v>
       </c>
       <c r="Y67" s="127">
         <v>46009</v>
@@ -20369,169 +20389,167 @@
     </row>
     <row r="68" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>315</v>
-      </c>
-      <c r="B68" s="106" t="s">
-        <v>351</v>
-      </c>
-      <c r="C68" s="105" t="s">
-        <v>287</v>
-      </c>
-      <c r="D68" s="110" t="s">
+        <v>335</v>
+      </c>
+      <c r="B68" t="s">
+        <v>347</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D68" s="92" t="s">
         <v>263</v>
       </c>
-      <c r="E68" s="111">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="F68" s="138">
-        <v>0</v>
-      </c>
-      <c r="G68" s="128">
-        <v>46288</v>
-      </c>
-      <c r="H68" s="138">
-        <v>0</v>
-      </c>
-      <c r="I68" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="J68" s="138">
-        <v>0</v>
-      </c>
-      <c r="K68" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="L68" s="138">
-        <v>1.0321</v>
-      </c>
-      <c r="M68" s="128">
-        <v>46197</v>
-      </c>
-      <c r="N68" s="138">
-        <v>0</v>
-      </c>
-      <c r="O68" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="P68" s="138">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="R68" s="138">
-        <v>0.96889999999999998</v>
+      <c r="E68" s="94">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F68" s="137">
+        <v>0.1666</v>
+      </c>
+      <c r="G68" s="127">
+        <v>46266</v>
+      </c>
+      <c r="H68" s="137">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="I68" s="127">
+        <v>46237</v>
+      </c>
+      <c r="J68" s="137">
+        <v>0.16450000000000001</v>
+      </c>
+      <c r="K68" s="127">
+        <v>46204</v>
+      </c>
+      <c r="L68" s="137">
+        <v>0.16339999999999999</v>
+      </c>
+      <c r="M68" s="127">
+        <v>46174</v>
+      </c>
+      <c r="N68" s="137">
+        <v>0.16089999999999999</v>
+      </c>
+      <c r="O68" s="127">
+        <v>46143</v>
+      </c>
+      <c r="P68" s="137">
+        <v>0.16170000000000001</v>
+      </c>
+      <c r="Q68" s="127">
+        <v>46113</v>
+      </c>
+      <c r="R68" s="137">
+        <v>0.16089999999999999</v>
       </c>
       <c r="S68" s="127">
-        <v>46105</v>
-      </c>
-      <c r="T68" s="138">
-        <v>0</v>
-      </c>
-      <c r="U68" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="V68" s="138">
+        <v>46083</v>
+      </c>
+      <c r="T68" s="137">
+        <v>0.16450000000000001</v>
+      </c>
+      <c r="U68" s="127">
+        <v>46055</v>
+      </c>
+      <c r="V68" s="137">
         <v>0</v>
       </c>
       <c r="W68" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="X68" s="138">
-        <v>1.0279</v>
-      </c>
-      <c r="Y68" s="128">
-        <v>46008</v>
-      </c>
-      <c r="Z68" s="96"/>
+      <c r="X68" s="137">
+        <v>0.15989999999999999</v>
+      </c>
+      <c r="Y68" s="127">
+        <v>46009</v>
+      </c>
     </row>
     <row r="69" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>315</v>
-      </c>
-      <c r="B69" s="106" t="s">
-        <v>357</v>
-      </c>
-      <c r="C69" s="105" t="s">
-        <v>291</v>
-      </c>
-      <c r="D69" s="110" t="s">
+        <v>335</v>
+      </c>
+      <c r="B69" t="s">
+        <v>348</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D69" s="92" t="s">
         <v>263</v>
       </c>
-      <c r="E69" s="111">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="F69" s="138">
-        <v>0</v>
-      </c>
-      <c r="G69" s="128">
-        <v>46288</v>
-      </c>
-      <c r="H69" s="138">
-        <v>0</v>
-      </c>
-      <c r="I69" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="J69" s="138">
-        <v>0</v>
-      </c>
-      <c r="K69" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="L69" s="138">
-        <v>0.85189999999999999</v>
-      </c>
-      <c r="M69" s="128">
-        <v>46197</v>
-      </c>
-      <c r="N69" s="138">
-        <v>0</v>
-      </c>
-      <c r="O69" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="P69" s="138">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="R69" s="138">
-        <v>0.37930000000000003</v>
+      <c r="E69" s="94">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F69" s="137">
+        <v>0.1434</v>
+      </c>
+      <c r="G69" s="127">
+        <v>46266</v>
+      </c>
+      <c r="H69" s="137">
+        <v>0.14149999999999999</v>
+      </c>
+      <c r="I69" s="127">
+        <v>46237</v>
+      </c>
+      <c r="J69" s="137">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="K69" s="127">
+        <v>46204</v>
+      </c>
+      <c r="L69" s="137">
+        <v>0.1381</v>
+      </c>
+      <c r="M69" s="127">
+        <v>46174</v>
+      </c>
+      <c r="N69" s="137">
+        <v>0.14230000000000001</v>
+      </c>
+      <c r="O69" s="127">
+        <v>46143</v>
+      </c>
+      <c r="P69" s="137">
+        <v>0.14149999999999999</v>
+      </c>
+      <c r="Q69" s="127">
+        <v>46113</v>
+      </c>
+      <c r="R69" s="137">
+        <v>0.1487</v>
       </c>
       <c r="S69" s="127">
-        <v>46105</v>
-      </c>
-      <c r="T69" s="138">
-        <v>0</v>
-      </c>
-      <c r="U69" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="V69" s="138">
+        <v>46083</v>
+      </c>
+      <c r="T69" s="137">
+        <v>0.13980000000000001</v>
+      </c>
+      <c r="U69" s="127">
+        <v>46055</v>
+      </c>
+      <c r="V69" s="137">
         <v>0</v>
       </c>
       <c r="W69" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="X69" s="138">
-        <v>0.67479999999999996</v>
-      </c>
-      <c r="Y69" s="128">
-        <v>46008</v>
-      </c>
-      <c r="Z69" s="96"/>
+      <c r="X69" s="137">
+        <v>0.14169999999999999</v>
+      </c>
+      <c r="Y69" s="127">
+        <v>46009</v>
+      </c>
     </row>
     <row r="70" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>315</v>
       </c>
       <c r="B70" s="106" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C70" s="105" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="D70" s="110" t="s">
         <v>263</v>
@@ -20539,10 +20557,10 @@
       <c r="E70" s="111">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="F70" s="138">
-        <v>0</v>
-      </c>
-      <c r="G70" s="128">
+      <c r="F70" s="151">
+        <v>0</v>
+      </c>
+      <c r="G70" s="152">
         <v>46288</v>
       </c>
       <c r="H70" s="138">
@@ -20558,7 +20576,7 @@
         <v>85</v>
       </c>
       <c r="L70" s="138">
-        <v>0.98680000000000001</v>
+        <v>1.0321</v>
       </c>
       <c r="M70" s="128">
         <v>46197</v>
@@ -20576,7 +20594,7 @@
         <v>85</v>
       </c>
       <c r="R70" s="138">
-        <v>0.99399999999999999</v>
+        <v>0.96889999999999998</v>
       </c>
       <c r="S70" s="127">
         <v>46105</v>
@@ -20594,7 +20612,7 @@
         <v>85</v>
       </c>
       <c r="X70" s="138">
-        <v>1.6654</v>
+        <v>1.0279</v>
       </c>
       <c r="Y70" s="128">
         <v>46008</v>
@@ -20606,10 +20624,10 @@
         <v>315</v>
       </c>
       <c r="B71" s="106" t="s">
-        <v>353</v>
-      </c>
-      <c r="C71" s="107" t="s">
-        <v>299</v>
+        <v>357</v>
+      </c>
+      <c r="C71" s="105" t="s">
+        <v>291</v>
       </c>
       <c r="D71" s="110" t="s">
         <v>263</v>
@@ -20617,10 +20635,10 @@
       <c r="E71" s="111">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="F71" s="138">
-        <v>0</v>
-      </c>
-      <c r="G71" s="128">
+      <c r="F71" s="151">
+        <v>0</v>
+      </c>
+      <c r="G71" s="152">
         <v>46288</v>
       </c>
       <c r="H71" s="138">
@@ -20636,7 +20654,7 @@
         <v>85</v>
       </c>
       <c r="L71" s="138">
-        <v>0.70540000000000003</v>
+        <v>0.85189999999999999</v>
       </c>
       <c r="M71" s="128">
         <v>46197</v>
@@ -20654,7 +20672,7 @@
         <v>85</v>
       </c>
       <c r="R71" s="138">
-        <v>0.77029999999999998</v>
+        <v>0.37930000000000003</v>
       </c>
       <c r="S71" s="127">
         <v>46105</v>
@@ -20672,32 +20690,33 @@
         <v>85</v>
       </c>
       <c r="X71" s="138">
-        <v>0.81410000000000005</v>
+        <v>0.67479999999999996</v>
       </c>
       <c r="Y71" s="128">
         <v>46008</v>
       </c>
+      <c r="Z71" s="96"/>
     </row>
     <row r="72" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>315</v>
       </c>
       <c r="B72" s="106" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C72" s="105" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D72" s="110" t="s">
         <v>263</v>
       </c>
       <c r="E72" s="111">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="F72" s="138">
-        <v>0</v>
-      </c>
-      <c r="G72" s="128">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="F72" s="151">
+        <v>0</v>
+      </c>
+      <c r="G72" s="152">
         <v>46288</v>
       </c>
       <c r="H72" s="138">
@@ -20713,7 +20732,7 @@
         <v>85</v>
       </c>
       <c r="L72" s="138">
-        <v>0.85540000000000005</v>
+        <v>0.98680000000000001</v>
       </c>
       <c r="M72" s="128">
         <v>46197</v>
@@ -20731,7 +20750,7 @@
         <v>85</v>
       </c>
       <c r="R72" s="138">
-        <v>0.94569999999999999</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="S72" s="127">
         <v>46105</v>
@@ -20749,10 +20768,10 @@
         <v>85</v>
       </c>
       <c r="X72" s="138">
-        <v>0.80049999999999999</v>
+        <v>1.6654</v>
       </c>
       <c r="Y72" s="128">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="Z72" s="96"/>
     </row>
@@ -20761,10 +20780,10 @@
         <v>315</v>
       </c>
       <c r="B73" s="106" t="s">
-        <v>368</v>
-      </c>
-      <c r="C73" s="105" t="s">
-        <v>282</v>
+        <v>353</v>
+      </c>
+      <c r="C73" s="107" t="s">
+        <v>299</v>
       </c>
       <c r="D73" s="110" t="s">
         <v>263</v>
@@ -20772,10 +20791,10 @@
       <c r="E73" s="111">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="F73" s="138">
-        <v>0</v>
-      </c>
-      <c r="G73" s="128">
+      <c r="F73" s="151">
+        <v>0</v>
+      </c>
+      <c r="G73" s="152">
         <v>46288</v>
       </c>
       <c r="H73" s="138">
@@ -20791,7 +20810,7 @@
         <v>85</v>
       </c>
       <c r="L73" s="138">
-        <v>1.2239</v>
+        <v>0.70540000000000003</v>
       </c>
       <c r="M73" s="128">
         <v>46197</v>
@@ -20809,7 +20828,7 @@
         <v>85</v>
       </c>
       <c r="R73" s="138">
-        <v>1.2169000000000001</v>
+        <v>0.77029999999999998</v>
       </c>
       <c r="S73" s="127">
         <v>46105</v>
@@ -20827,33 +20846,32 @@
         <v>85</v>
       </c>
       <c r="X73" s="138">
-        <v>1.2296</v>
+        <v>0.81410000000000005</v>
       </c>
       <c r="Y73" s="128">
         <v>46008</v>
       </c>
-      <c r="Z73" s="96"/>
     </row>
     <row r="74" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>315</v>
       </c>
       <c r="B74" s="106" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C74" s="105" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D74" s="110" t="s">
         <v>263</v>
       </c>
       <c r="E74" s="111">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="F74" s="138">
-        <v>0</v>
-      </c>
-      <c r="G74" s="128">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="F74" s="151">
+        <v>0</v>
+      </c>
+      <c r="G74" s="152">
         <v>46288</v>
       </c>
       <c r="H74" s="138">
@@ -20869,7 +20887,7 @@
         <v>85</v>
       </c>
       <c r="L74" s="138">
-        <v>0.1384</v>
+        <v>0.85540000000000005</v>
       </c>
       <c r="M74" s="128">
         <v>46197</v>
@@ -20887,7 +20905,7 @@
         <v>85</v>
       </c>
       <c r="R74" s="138">
-        <v>9.2975000000000002E-2</v>
+        <v>0.94569999999999999</v>
       </c>
       <c r="S74" s="127">
         <v>46105</v>
@@ -20905,10 +20923,10 @@
         <v>85</v>
       </c>
       <c r="X74" s="138">
-        <v>9.4630000000000006E-2</v>
+        <v>0.80049999999999999</v>
       </c>
       <c r="Y74" s="128">
-        <v>46008</v>
+        <v>46013</v>
       </c>
       <c r="Z74" s="96"/>
     </row>
@@ -20917,10 +20935,10 @@
         <v>315</v>
       </c>
       <c r="B75" s="106" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C75" s="105" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="D75" s="110" t="s">
         <v>263</v>
@@ -20928,10 +20946,10 @@
       <c r="E75" s="111">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="F75" s="138">
-        <v>0</v>
-      </c>
-      <c r="G75" s="128">
+      <c r="F75" s="151">
+        <v>0</v>
+      </c>
+      <c r="G75" s="152">
         <v>46288</v>
       </c>
       <c r="H75" s="138">
@@ -20947,7 +20965,7 @@
         <v>85</v>
       </c>
       <c r="L75" s="138">
-        <v>1.3008999999999999</v>
+        <v>1.2239</v>
       </c>
       <c r="M75" s="128">
         <v>46197</v>
@@ -20965,7 +20983,7 @@
         <v>85</v>
       </c>
       <c r="R75" s="138">
-        <v>1.2768999999999999</v>
+        <v>1.2169000000000001</v>
       </c>
       <c r="S75" s="127">
         <v>46105</v>
@@ -20983,7 +21001,7 @@
         <v>85</v>
       </c>
       <c r="X75" s="138">
-        <v>1.3633</v>
+        <v>1.2296</v>
       </c>
       <c r="Y75" s="128">
         <v>46008</v>
@@ -20995,10 +21013,10 @@
         <v>315</v>
       </c>
       <c r="B76" s="106" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="C76" s="105" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="D76" s="110" t="s">
         <v>263</v>
@@ -21006,10 +21024,10 @@
       <c r="E76" s="111">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="F76" s="138">
-        <v>0</v>
-      </c>
-      <c r="G76" s="128">
+      <c r="F76" s="151">
+        <v>0</v>
+      </c>
+      <c r="G76" s="152">
         <v>46288</v>
       </c>
       <c r="H76" s="138">
@@ -21025,7 +21043,7 @@
         <v>85</v>
       </c>
       <c r="L76" s="138">
-        <v>0.70720000000000005</v>
+        <v>0.1384</v>
       </c>
       <c r="M76" s="128">
         <v>46197</v>
@@ -21043,7 +21061,7 @@
         <v>85</v>
       </c>
       <c r="R76" s="138">
-        <v>0.71919999999999995</v>
+        <v>9.2975000000000002E-2</v>
       </c>
       <c r="S76" s="127">
         <v>46105</v>
@@ -21061,7 +21079,7 @@
         <v>85</v>
       </c>
       <c r="X76" s="138">
-        <v>0.75129999999999997</v>
+        <v>9.4630000000000006E-2</v>
       </c>
       <c r="Y76" s="128">
         <v>46008</v>
@@ -21070,221 +21088,223 @@
     </row>
     <row r="77" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>335</v>
-      </c>
-      <c r="B77" t="s">
-        <v>345</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>237</v>
+        <v>315</v>
+      </c>
+      <c r="B77" s="106" t="s">
+        <v>356</v>
+      </c>
+      <c r="C77" s="105" t="s">
+        <v>311</v>
       </c>
       <c r="D77" s="110" t="s">
-        <v>265</v>
-      </c>
-      <c r="E77" s="94">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="F77" s="137">
-        <v>0.19292999999999999</v>
-      </c>
-      <c r="G77" s="127">
-        <v>46266</v>
-      </c>
-      <c r="H77" s="137">
-        <v>0.20161999999999999</v>
-      </c>
-      <c r="I77" s="127">
-        <v>46237</v>
-      </c>
-      <c r="J77" s="137">
-        <v>0.19264999999999999</v>
-      </c>
-      <c r="K77" s="127">
-        <v>46204</v>
-      </c>
-      <c r="L77" s="137">
-        <v>0.19889999999999999</v>
-      </c>
-      <c r="M77" s="127">
-        <v>46174</v>
-      </c>
-      <c r="N77" s="137">
-        <v>0.18801999999999999</v>
-      </c>
-      <c r="O77" s="127">
-        <v>46143</v>
-      </c>
-      <c r="P77" s="137">
-        <v>0.22111</v>
-      </c>
-      <c r="Q77" s="127">
-        <v>46113</v>
-      </c>
-      <c r="R77" s="137">
-        <v>0.17266000000000001</v>
+        <v>263</v>
+      </c>
+      <c r="E77" s="111">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="F77" s="151">
+        <v>0</v>
+      </c>
+      <c r="G77" s="152">
+        <v>46288</v>
+      </c>
+      <c r="H77" s="138">
+        <v>0</v>
+      </c>
+      <c r="I77" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="J77" s="138">
+        <v>0</v>
+      </c>
+      <c r="K77" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="L77" s="138">
+        <v>1.3008999999999999</v>
+      </c>
+      <c r="M77" s="128">
+        <v>46197</v>
+      </c>
+      <c r="N77" s="138">
+        <v>0</v>
+      </c>
+      <c r="O77" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="P77" s="138">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="R77" s="138">
+        <v>1.2768999999999999</v>
       </c>
       <c r="S77" s="127">
-        <v>46083</v>
-      </c>
-      <c r="T77" s="137">
-        <v>0.20602999999999999</v>
-      </c>
-      <c r="U77" s="127">
-        <v>46055</v>
-      </c>
-      <c r="V77" s="137">
+        <v>46105</v>
+      </c>
+      <c r="T77" s="138">
+        <v>0</v>
+      </c>
+      <c r="U77" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="V77" s="138">
         <v>0</v>
       </c>
       <c r="W77" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="X77" s="137">
-        <v>0.20891000000000001</v>
-      </c>
-      <c r="Y77" s="127">
-        <v>46013</v>
-      </c>
+      <c r="X77" s="138">
+        <v>1.3633</v>
+      </c>
+      <c r="Y77" s="128">
+        <v>46008</v>
+      </c>
+      <c r="Z77" s="96"/>
     </row>
     <row r="78" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>385</v>
-      </c>
-      <c r="B78" t="s">
-        <v>380</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>372</v>
+        <v>315</v>
+      </c>
+      <c r="B78" s="106" t="s">
+        <v>371</v>
+      </c>
+      <c r="C78" s="105" t="s">
+        <v>278</v>
       </c>
       <c r="D78" s="110" t="s">
-        <v>208</v>
-      </c>
-      <c r="E78" s="94">
-        <v>0</v>
-      </c>
-      <c r="F78" s="137">
-        <v>0.22</v>
-      </c>
-      <c r="G78" s="127">
-        <v>46269</v>
-      </c>
-      <c r="H78" s="137">
-        <v>0</v>
-      </c>
-      <c r="I78" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="J78" s="137">
-        <v>0</v>
-      </c>
-      <c r="K78" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="L78" s="137">
-        <v>0.22</v>
-      </c>
-      <c r="M78" s="127">
-        <v>46181</v>
-      </c>
-      <c r="N78" s="137">
-        <v>0</v>
-      </c>
-      <c r="O78" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="P78" s="137">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="R78" s="137">
-        <v>0.21</v>
+        <v>263</v>
+      </c>
+      <c r="E78" s="111">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="F78" s="151">
+        <v>0</v>
+      </c>
+      <c r="G78" s="152">
+        <v>46288</v>
+      </c>
+      <c r="H78" s="138">
+        <v>0</v>
+      </c>
+      <c r="I78" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="J78" s="138">
+        <v>0</v>
+      </c>
+      <c r="K78" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="L78" s="138">
+        <v>0.70720000000000005</v>
+      </c>
+      <c r="M78" s="128">
+        <v>46197</v>
+      </c>
+      <c r="N78" s="138">
+        <v>0</v>
+      </c>
+      <c r="O78" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="P78" s="138">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="R78" s="138">
+        <v>0.71919999999999995</v>
       </c>
       <c r="S78" s="127">
-        <v>46090</v>
-      </c>
-      <c r="T78" s="137">
-        <v>0</v>
-      </c>
-      <c r="U78" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="V78" s="137">
+        <v>46105</v>
+      </c>
+      <c r="T78" s="138">
+        <v>0</v>
+      </c>
+      <c r="U78" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="V78" s="138">
         <v>0</v>
       </c>
       <c r="W78" s="128" t="s">
         <v>85</v>
       </c>
-      <c r="X78" s="137">
-        <v>0.21</v>
-      </c>
-      <c r="Y78" s="127">
-        <v>45999</v>
-      </c>
+      <c r="X78" s="138">
+        <v>0.75129999999999997</v>
+      </c>
+      <c r="Y78" s="128">
+        <v>46008</v>
+      </c>
+      <c r="Z78" s="96"/>
     </row>
     <row r="79" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>385</v>
+        <v>335</v>
       </c>
       <c r="B79" t="s">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>373</v>
+        <v>237</v>
       </c>
       <c r="D79" s="110" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="E79" s="94">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F79" s="137">
-        <v>0.22</v>
+        <v>0.19292999999999999</v>
       </c>
       <c r="G79" s="127">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="H79" s="137">
-        <v>0</v>
-      </c>
-      <c r="I79" s="127" t="s">
-        <v>85</v>
+        <v>0.20161999999999999</v>
+      </c>
+      <c r="I79" s="127">
+        <v>46237</v>
       </c>
       <c r="J79" s="137">
-        <v>0</v>
-      </c>
-      <c r="K79" s="127" t="s">
-        <v>85</v>
+        <v>0.19264999999999999</v>
+      </c>
+      <c r="K79" s="127">
+        <v>46204</v>
       </c>
       <c r="L79" s="137">
-        <v>0.22</v>
+        <v>0.19889999999999999</v>
       </c>
       <c r="M79" s="127">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="N79" s="137">
-        <v>0</v>
-      </c>
-      <c r="O79" s="127" t="s">
-        <v>85</v>
+        <v>0.18801999999999999</v>
+      </c>
+      <c r="O79" s="127">
+        <v>46143</v>
       </c>
       <c r="P79" s="137">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="127" t="s">
-        <v>85</v>
+        <v>0.22111</v>
+      </c>
+      <c r="Q79" s="127">
+        <v>46113</v>
       </c>
       <c r="R79" s="137">
-        <v>0.21</v>
+        <v>0.17266000000000001</v>
       </c>
       <c r="S79" s="127">
-        <v>46090</v>
+        <v>46083</v>
       </c>
       <c r="T79" s="137">
-        <v>0</v>
-      </c>
-      <c r="U79" s="127" t="s">
-        <v>85</v>
+        <v>0.20602999999999999</v>
+      </c>
+      <c r="U79" s="127">
+        <v>46055</v>
       </c>
       <c r="V79" s="137">
         <v>0</v>
@@ -21293,10 +21313,10 @@
         <v>85</v>
       </c>
       <c r="X79" s="137">
-        <v>0.21</v>
+        <v>0.20891000000000001</v>
       </c>
       <c r="Y79" s="127">
-        <v>45999</v>
+        <v>46013</v>
       </c>
     </row>
     <row r="80" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21304,10 +21324,10 @@
         <v>385</v>
       </c>
       <c r="B80" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D80" s="110" t="s">
         <v>208</v>
@@ -21316,10 +21336,10 @@
         <v>0</v>
       </c>
       <c r="F80" s="137">
-        <v>0.28999999999999998</v>
+        <v>0.22</v>
       </c>
       <c r="G80" s="127">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H80" s="137">
         <v>0</v>
@@ -21334,10 +21354,10 @@
         <v>85</v>
       </c>
       <c r="L80" s="137">
-        <v>0</v>
-      </c>
-      <c r="M80" s="127" t="s">
-        <v>85</v>
+        <v>0.22</v>
+      </c>
+      <c r="M80" s="127">
+        <v>46181</v>
       </c>
       <c r="N80" s="137">
         <v>0</v>
@@ -21352,10 +21372,10 @@
         <v>85</v>
       </c>
       <c r="R80" s="137">
-        <v>0.28000000000000003</v>
+        <v>0.21</v>
       </c>
       <c r="S80" s="127">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="T80" s="137">
         <v>0</v>
@@ -21370,10 +21390,10 @@
         <v>85</v>
       </c>
       <c r="X80" s="137">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="127" t="s">
-        <v>85</v>
+        <v>0.21</v>
+      </c>
+      <c r="Y80" s="127">
+        <v>45999</v>
       </c>
     </row>
     <row r="81" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21381,10 +21401,10 @@
         <v>385</v>
       </c>
       <c r="B81" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D81" s="110" t="s">
         <v>208</v>
@@ -21393,10 +21413,10 @@
         <v>0</v>
       </c>
       <c r="F81" s="137">
-        <v>0.28999999999999998</v>
+        <v>0.22</v>
       </c>
       <c r="G81" s="127">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="H81" s="137">
         <v>0</v>
@@ -21411,10 +21431,10 @@
         <v>85</v>
       </c>
       <c r="L81" s="137">
-        <v>0</v>
-      </c>
-      <c r="M81" s="127" t="s">
-        <v>85</v>
+        <v>0.22</v>
+      </c>
+      <c r="M81" s="127">
+        <v>46181</v>
       </c>
       <c r="N81" s="137">
         <v>0</v>
@@ -21429,10 +21449,10 @@
         <v>85</v>
       </c>
       <c r="R81" s="137">
-        <v>0.28000000000000003</v>
+        <v>0.21</v>
       </c>
       <c r="S81" s="127">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="T81" s="137">
         <v>0</v>
@@ -21447,10 +21467,10 @@
         <v>85</v>
       </c>
       <c r="X81" s="137">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="127" t="s">
-        <v>85</v>
+        <v>0.21</v>
+      </c>
+      <c r="Y81" s="127">
+        <v>45999</v>
       </c>
     </row>
     <row r="82" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21458,10 +21478,10 @@
         <v>385</v>
       </c>
       <c r="B82" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D82" s="110" t="s">
         <v>208</v>
@@ -21470,10 +21490,10 @@
         <v>0</v>
       </c>
       <c r="F82" s="137">
-        <v>0.1</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G82" s="127">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="H82" s="137">
         <v>0</v>
@@ -21506,10 +21526,10 @@
         <v>85</v>
       </c>
       <c r="R82" s="137">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="S82" s="127">
-        <v>46092</v>
+        <v>46085</v>
       </c>
       <c r="T82" s="137">
         <v>0</v>
@@ -21535,10 +21555,10 @@
         <v>385</v>
       </c>
       <c r="B83" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D83" s="110" t="s">
         <v>208</v>
@@ -21547,10 +21567,10 @@
         <v>0</v>
       </c>
       <c r="F83" s="137">
-        <v>0.1</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G83" s="127">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="H83" s="137">
         <v>0</v>
@@ -21583,10 +21603,10 @@
         <v>85</v>
       </c>
       <c r="R83" s="137">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="S83" s="127">
-        <v>46092</v>
+        <v>46085</v>
       </c>
       <c r="T83" s="137">
         <v>0</v>
@@ -21612,10 +21632,10 @@
         <v>385</v>
       </c>
       <c r="B84" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D84" s="110" t="s">
         <v>208</v>
@@ -21624,10 +21644,10 @@
         <v>0</v>
       </c>
       <c r="F84" s="137">
-        <v>0</v>
-      </c>
-      <c r="G84" s="127" t="s">
-        <v>85</v>
+        <v>0.1</v>
+      </c>
+      <c r="G84" s="127">
+        <v>46274</v>
       </c>
       <c r="H84" s="137">
         <v>0</v>
@@ -21636,10 +21656,10 @@
         <v>85</v>
       </c>
       <c r="J84" s="137">
-        <v>0.13</v>
-      </c>
-      <c r="K84" s="127">
-        <v>46204</v>
+        <v>0</v>
+      </c>
+      <c r="K84" s="127" t="s">
+        <v>85</v>
       </c>
       <c r="L84" s="137">
         <v>0</v>
@@ -21660,10 +21680,10 @@
         <v>85</v>
       </c>
       <c r="R84" s="137">
-        <v>0</v>
-      </c>
-      <c r="S84" s="127" t="s">
-        <v>85</v>
+        <v>0.1</v>
+      </c>
+      <c r="S84" s="127">
+        <v>46092</v>
       </c>
       <c r="T84" s="137">
         <v>0</v>
@@ -21672,10 +21692,10 @@
         <v>85</v>
       </c>
       <c r="V84" s="137">
-        <v>0.12</v>
-      </c>
-      <c r="W84" s="128">
-        <v>46027</v>
+        <v>0</v>
+      </c>
+      <c r="W84" s="128" t="s">
+        <v>85</v>
       </c>
       <c r="X84" s="137">
         <v>0</v>
@@ -21689,10 +21709,10 @@
         <v>385</v>
       </c>
       <c r="B85" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D85" s="110" t="s">
         <v>208</v>
@@ -21701,10 +21721,10 @@
         <v>0</v>
       </c>
       <c r="F85" s="137">
-        <v>0</v>
-      </c>
-      <c r="G85" s="127" t="s">
-        <v>85</v>
+        <v>0.1</v>
+      </c>
+      <c r="G85" s="127">
+        <v>46274</v>
       </c>
       <c r="H85" s="137">
         <v>0</v>
@@ -21713,10 +21733,10 @@
         <v>85</v>
       </c>
       <c r="J85" s="137">
-        <v>0.13</v>
-      </c>
-      <c r="K85" s="127">
-        <v>46204</v>
+        <v>0</v>
+      </c>
+      <c r="K85" s="127" t="s">
+        <v>85</v>
       </c>
       <c r="L85" s="137">
         <v>0</v>
@@ -21737,10 +21757,10 @@
         <v>85</v>
       </c>
       <c r="R85" s="137">
-        <v>0</v>
-      </c>
-      <c r="S85" s="127" t="s">
-        <v>85</v>
+        <v>0.1</v>
+      </c>
+      <c r="S85" s="127">
+        <v>46092</v>
       </c>
       <c r="T85" s="137">
         <v>0</v>
@@ -21749,10 +21769,10 @@
         <v>85</v>
       </c>
       <c r="V85" s="137">
-        <v>0.12</v>
-      </c>
-      <c r="W85" s="128">
-        <v>46027</v>
+        <v>0</v>
+      </c>
+      <c r="W85" s="128" t="s">
+        <v>85</v>
       </c>
       <c r="X85" s="137">
         <v>0</v>
@@ -21766,10 +21786,10 @@
         <v>385</v>
       </c>
       <c r="B86" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D86" s="110" t="s">
         <v>208</v>
@@ -21790,10 +21810,10 @@
         <v>85</v>
       </c>
       <c r="J86" s="137">
-        <v>0</v>
-      </c>
-      <c r="K86" s="127" t="s">
-        <v>85</v>
+        <v>0.13</v>
+      </c>
+      <c r="K86" s="127">
+        <v>46204</v>
       </c>
       <c r="L86" s="137">
         <v>0</v>
@@ -21826,10 +21846,10 @@
         <v>85</v>
       </c>
       <c r="V86" s="137">
-        <v>0</v>
-      </c>
-      <c r="W86" s="128" t="s">
-        <v>85</v>
+        <v>0.12</v>
+      </c>
+      <c r="W86" s="128">
+        <v>46027</v>
       </c>
       <c r="X86" s="137">
         <v>0</v>
@@ -21843,10 +21863,10 @@
         <v>385</v>
       </c>
       <c r="B87" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="D87" s="110" t="s">
         <v>208</v>
@@ -21867,10 +21887,10 @@
         <v>85</v>
       </c>
       <c r="J87" s="137">
-        <v>0</v>
-      </c>
-      <c r="K87" s="127" t="s">
-        <v>85</v>
+        <v>0.13</v>
+      </c>
+      <c r="K87" s="127">
+        <v>46204</v>
       </c>
       <c r="L87" s="137">
         <v>0</v>
@@ -21903,10 +21923,10 @@
         <v>85</v>
       </c>
       <c r="V87" s="137">
-        <v>0</v>
-      </c>
-      <c r="W87" s="128" t="s">
-        <v>85</v>
+        <v>0.12</v>
+      </c>
+      <c r="W87" s="128">
+        <v>46027</v>
       </c>
       <c r="X87" s="137">
         <v>0</v>
@@ -21917,25 +21937,25 @@
     </row>
     <row r="88" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>315</v>
+        <v>385</v>
       </c>
       <c r="B88" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>261</v>
+        <v>386</v>
       </c>
       <c r="D88" s="110" t="s">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="E88" s="94">
-        <v>6.9999999999999999E-4</v>
+        <v>0</v>
       </c>
       <c r="F88" s="137">
         <v>0</v>
       </c>
-      <c r="G88" s="127">
-        <v>46288</v>
+      <c r="G88" s="127" t="s">
+        <v>85</v>
       </c>
       <c r="H88" s="137">
         <v>0</v>
@@ -21950,10 +21970,10 @@
         <v>85</v>
       </c>
       <c r="L88" s="137">
-        <v>0.16830000000000001</v>
-      </c>
-      <c r="M88" s="127">
-        <v>46197</v>
+        <v>0</v>
+      </c>
+      <c r="M88" s="127" t="s">
+        <v>85</v>
       </c>
       <c r="N88" s="137">
         <v>0</v>
@@ -21968,10 +21988,10 @@
         <v>85</v>
       </c>
       <c r="R88" s="137">
-        <v>0.1147</v>
-      </c>
-      <c r="S88" s="127">
-        <v>46106</v>
+        <v>0</v>
+      </c>
+      <c r="S88" s="127" t="s">
+        <v>85</v>
       </c>
       <c r="T88" s="137">
         <v>0</v>
@@ -21986,158 +22006,282 @@
         <v>85</v>
       </c>
       <c r="X88" s="137">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="Y88" s="127">
-        <v>46001</v>
+        <v>0</v>
+      </c>
+      <c r="Y88" s="127" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="89" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>385</v>
+      </c>
+      <c r="B89" t="s">
+        <v>384</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="D89" s="110" t="s">
+        <v>208</v>
+      </c>
+      <c r="E89" s="94">
+        <v>0</v>
+      </c>
+      <c r="F89" s="137">
+        <v>0</v>
+      </c>
+      <c r="G89" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="H89" s="137">
+        <v>0</v>
+      </c>
+      <c r="I89" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="J89" s="137">
+        <v>0</v>
+      </c>
+      <c r="K89" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="L89" s="137">
+        <v>0</v>
+      </c>
+      <c r="M89" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="N89" s="137">
+        <v>0</v>
+      </c>
+      <c r="O89" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="P89" s="137">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="R89" s="137">
+        <v>0</v>
+      </c>
+      <c r="S89" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="T89" s="137">
+        <v>0</v>
+      </c>
+      <c r="U89" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="V89" s="137">
+        <v>0</v>
+      </c>
+      <c r="W89" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="X89" s="137">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="127" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>315</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B90" t="s">
         <v>354</v>
       </c>
-      <c r="C89" s="14" t="s">
+      <c r="C90" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="D90" s="110" t="s">
+        <v>267</v>
+      </c>
+      <c r="E90" s="94">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="F90" s="137">
+        <v>0</v>
+      </c>
+      <c r="G90" s="127">
+        <v>46288</v>
+      </c>
+      <c r="H90" s="137">
+        <v>0</v>
+      </c>
+      <c r="I90" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="J90" s="137">
+        <v>0</v>
+      </c>
+      <c r="K90" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="L90" s="137">
+        <v>0.16830000000000001</v>
+      </c>
+      <c r="M90" s="127">
+        <v>46197</v>
+      </c>
+      <c r="N90" s="137">
+        <v>0</v>
+      </c>
+      <c r="O90" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="P90" s="137">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="R90" s="137">
+        <v>0.1147</v>
+      </c>
+      <c r="S90" s="127">
+        <v>46106</v>
+      </c>
+      <c r="T90" s="137">
+        <v>0</v>
+      </c>
+      <c r="U90" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="V90" s="137">
+        <v>0</v>
+      </c>
+      <c r="W90" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="X90" s="137">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="Y90" s="127">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>315</v>
+      </c>
+      <c r="B91" t="s">
+        <v>354</v>
+      </c>
+      <c r="C91" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="D89" s="110" t="s">
+      <c r="D91" s="110" t="s">
         <v>273</v>
       </c>
-      <c r="E89" s="94">
+      <c r="E91" s="94">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="F89" s="137">
+      <c r="F91" s="137">
         <v>0.473107</v>
       </c>
-      <c r="G89" s="127">
+      <c r="G91" s="127">
         <v>46280</v>
       </c>
-      <c r="H89" s="137">
-        <v>0</v>
-      </c>
-      <c r="I89" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="J89" s="137">
-        <v>0</v>
-      </c>
-      <c r="K89" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="L89" s="137">
+      <c r="H91" s="137">
+        <v>0</v>
+      </c>
+      <c r="I91" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="J91" s="137">
+        <v>0</v>
+      </c>
+      <c r="K91" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="L91" s="137">
         <v>0.37368899999999999</v>
       </c>
-      <c r="M89" s="127">
+      <c r="M91" s="127">
         <v>46188</v>
       </c>
-      <c r="N89" s="137">
-        <v>0</v>
-      </c>
-      <c r="O89" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="P89" s="137">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="R89" s="137">
+      <c r="N91" s="137">
+        <v>0</v>
+      </c>
+      <c r="O91" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="P91" s="137">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="R91" s="137">
         <v>0.211783</v>
       </c>
-      <c r="S89" s="127">
+      <c r="S91" s="127">
         <v>46098</v>
       </c>
-      <c r="T89" s="137">
-        <v>0</v>
-      </c>
-      <c r="U89" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="V89" s="137">
-        <v>0</v>
-      </c>
-      <c r="W89" s="128" t="s">
-        <v>85</v>
-      </c>
-      <c r="X89" s="137">
+      <c r="T91" s="137">
+        <v>0</v>
+      </c>
+      <c r="U91" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="V91" s="137">
+        <v>0</v>
+      </c>
+      <c r="W91" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="X91" s="137">
         <v>0.695461</v>
       </c>
-      <c r="Y89" s="127">
+      <c r="Y91" s="127">
         <v>46007</v>
       </c>
-    </row>
-    <row r="90" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C90" s="14"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="94"/>
-      <c r="G90" s="127"/>
-      <c r="I90" s="127"/>
-      <c r="K90" s="127"/>
-      <c r="M90" s="127"/>
-      <c r="O90" s="127"/>
-      <c r="Q90" s="127"/>
-      <c r="S90" s="127"/>
-      <c r="U90" s="127"/>
-      <c r="W90" s="127"/>
-      <c r="Y90" s="127"/>
-    </row>
-    <row r="91" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C91" s="14"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="131"/>
-      <c r="G91" s="131"/>
-      <c r="H91" s="131"/>
-      <c r="I91" s="131"/>
-      <c r="J91" s="131"/>
-      <c r="K91" s="131"/>
-      <c r="L91" s="131"/>
-      <c r="M91" s="131"/>
-      <c r="N91" s="131"/>
-      <c r="O91" s="131"/>
-      <c r="P91" s="131"/>
-      <c r="Q91" s="131"/>
-      <c r="R91" s="131"/>
-      <c r="S91" s="131"/>
-      <c r="T91" s="131"/>
-      <c r="U91" s="131"/>
-      <c r="V91" s="131"/>
-      <c r="W91" s="131"/>
-      <c r="X91" s="131"/>
-      <c r="Y91" s="131"/>
     </row>
     <row r="92" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="G92" s="134"/>
-      <c r="I92" s="134"/>
-      <c r="K92" s="134"/>
-      <c r="M92" s="134"/>
-      <c r="O92" s="134"/>
-      <c r="Q92" s="134"/>
-      <c r="S92" s="134"/>
-      <c r="U92" s="134"/>
-      <c r="W92" s="129"/>
-      <c r="Y92" s="134"/>
+      <c r="E92" s="94"/>
+      <c r="G92" s="127"/>
+      <c r="I92" s="127"/>
+      <c r="K92" s="127"/>
+      <c r="M92" s="127"/>
+      <c r="O92" s="127"/>
+      <c r="Q92" s="127"/>
+      <c r="S92" s="127"/>
+      <c r="U92" s="127"/>
+      <c r="W92" s="127"/>
+      <c r="Y92" s="127"/>
     </row>
     <row r="93" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
       <c r="E93" s="14"/>
-      <c r="G93" s="134"/>
-      <c r="I93" s="134"/>
-      <c r="K93" s="134"/>
-      <c r="M93" s="134"/>
-      <c r="O93" s="134"/>
-      <c r="Q93" s="134"/>
-      <c r="S93" s="134"/>
-      <c r="U93" s="134"/>
-      <c r="W93" s="129"/>
-      <c r="Y93" s="134"/>
+      <c r="F93" s="131"/>
+      <c r="G93" s="131"/>
+      <c r="H93" s="131"/>
+      <c r="I93" s="131"/>
+      <c r="J93" s="131"/>
+      <c r="K93" s="131"/>
+      <c r="L93" s="131"/>
+      <c r="M93" s="131"/>
+      <c r="N93" s="131"/>
+      <c r="O93" s="131"/>
+      <c r="P93" s="131"/>
+      <c r="Q93" s="131"/>
+      <c r="R93" s="131"/>
+      <c r="S93" s="131"/>
+      <c r="T93" s="131"/>
+      <c r="U93" s="131"/>
+      <c r="V93" s="131"/>
+      <c r="W93" s="131"/>
+      <c r="X93" s="131"/>
+      <c r="Y93" s="131"/>
     </row>
     <row r="94" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C94" s="14"/>
@@ -22157,32 +22301,32 @@
     <row r="95" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
-      <c r="E95" s="94"/>
-      <c r="G95" s="135"/>
-      <c r="I95" s="135"/>
-      <c r="K95" s="135"/>
-      <c r="M95" s="135"/>
-      <c r="O95" s="135"/>
-      <c r="Q95" s="135"/>
-      <c r="S95" s="135"/>
-      <c r="U95" s="135"/>
-      <c r="W95" s="130"/>
-      <c r="Y95" s="135"/>
+      <c r="E95" s="14"/>
+      <c r="G95" s="134"/>
+      <c r="I95" s="134"/>
+      <c r="K95" s="134"/>
+      <c r="M95" s="134"/>
+      <c r="O95" s="134"/>
+      <c r="Q95" s="134"/>
+      <c r="S95" s="134"/>
+      <c r="U95" s="134"/>
+      <c r="W95" s="129"/>
+      <c r="Y95" s="134"/>
     </row>
     <row r="96" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
-      <c r="E96" s="94"/>
-      <c r="G96" s="135"/>
-      <c r="I96" s="135"/>
-      <c r="K96" s="135"/>
-      <c r="M96" s="135"/>
-      <c r="O96" s="135"/>
-      <c r="Q96" s="135"/>
-      <c r="S96" s="135"/>
-      <c r="U96" s="135"/>
-      <c r="W96" s="130"/>
-      <c r="Y96" s="135"/>
+      <c r="E96" s="14"/>
+      <c r="G96" s="134"/>
+      <c r="I96" s="134"/>
+      <c r="K96" s="134"/>
+      <c r="M96" s="134"/>
+      <c r="O96" s="134"/>
+      <c r="Q96" s="134"/>
+      <c r="S96" s="134"/>
+      <c r="U96" s="134"/>
+      <c r="W96" s="129"/>
+      <c r="Y96" s="134"/>
     </row>
     <row r="97" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C97" s="14"/>
@@ -22263,31 +22407,31 @@
       <c r="C102" s="14"/>
       <c r="D102" s="14"/>
       <c r="E102" s="94"/>
-      <c r="G102" s="109"/>
-      <c r="I102" s="109"/>
-      <c r="K102" s="109"/>
-      <c r="M102" s="109"/>
-      <c r="O102" s="109"/>
-      <c r="Q102" s="109"/>
-      <c r="S102" s="109"/>
-      <c r="U102" s="109"/>
+      <c r="G102" s="135"/>
+      <c r="I102" s="135"/>
+      <c r="K102" s="135"/>
+      <c r="M102" s="135"/>
+      <c r="O102" s="135"/>
+      <c r="Q102" s="135"/>
+      <c r="S102" s="135"/>
+      <c r="U102" s="135"/>
       <c r="W102" s="130"/>
-      <c r="Y102" s="109"/>
+      <c r="Y102" s="135"/>
     </row>
     <row r="103" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
       <c r="E103" s="94"/>
-      <c r="G103" s="109"/>
-      <c r="I103" s="109"/>
-      <c r="K103" s="109"/>
-      <c r="M103" s="109"/>
-      <c r="O103" s="109"/>
-      <c r="Q103" s="109"/>
-      <c r="S103" s="109"/>
-      <c r="U103" s="109"/>
+      <c r="G103" s="135"/>
+      <c r="I103" s="135"/>
+      <c r="K103" s="135"/>
+      <c r="M103" s="135"/>
+      <c r="O103" s="135"/>
+      <c r="Q103" s="135"/>
+      <c r="S103" s="135"/>
+      <c r="U103" s="135"/>
       <c r="W103" s="130"/>
-      <c r="Y103" s="109"/>
+      <c r="Y103" s="135"/>
     </row>
     <row r="104" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C104" s="14"/>
@@ -22496,7 +22640,7 @@
       <c r="Q117" s="109"/>
       <c r="S117" s="109"/>
       <c r="U117" s="109"/>
-      <c r="W117" s="97"/>
+      <c r="W117" s="130"/>
       <c r="Y117" s="109"/>
     </row>
     <row r="118" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22511,7 +22655,7 @@
       <c r="Q118" s="109"/>
       <c r="S118" s="109"/>
       <c r="U118" s="109"/>
-      <c r="W118" s="97"/>
+      <c r="W118" s="130"/>
       <c r="Y118" s="109"/>
     </row>
     <row r="119" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22683,31 +22827,31 @@
       <c r="C130" s="14"/>
       <c r="D130" s="14"/>
       <c r="E130" s="94"/>
-      <c r="G130" s="133"/>
-      <c r="I130" s="133"/>
-      <c r="K130" s="133"/>
-      <c r="M130" s="133"/>
-      <c r="O130" s="133"/>
-      <c r="Q130" s="133"/>
-      <c r="S130" s="133"/>
-      <c r="U130" s="133"/>
+      <c r="G130" s="109"/>
+      <c r="I130" s="109"/>
+      <c r="K130" s="109"/>
+      <c r="M130" s="109"/>
+      <c r="O130" s="109"/>
+      <c r="Q130" s="109"/>
+      <c r="S130" s="109"/>
+      <c r="U130" s="109"/>
       <c r="W130" s="97"/>
-      <c r="Y130" s="133"/>
+      <c r="Y130" s="109"/>
     </row>
     <row r="131" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
       <c r="E131" s="94"/>
-      <c r="G131" s="133"/>
-      <c r="I131" s="133"/>
-      <c r="K131" s="133"/>
-      <c r="M131" s="133"/>
-      <c r="O131" s="133"/>
-      <c r="Q131" s="133"/>
-      <c r="S131" s="133"/>
-      <c r="U131" s="133"/>
+      <c r="G131" s="109"/>
+      <c r="I131" s="109"/>
+      <c r="K131" s="109"/>
+      <c r="M131" s="109"/>
+      <c r="O131" s="109"/>
+      <c r="Q131" s="109"/>
+      <c r="S131" s="109"/>
+      <c r="U131" s="109"/>
       <c r="W131" s="97"/>
-      <c r="Y131" s="133"/>
+      <c r="Y131" s="109"/>
     </row>
     <row r="132" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C132" s="14"/>
@@ -26280,17 +26424,47 @@
       <c r="Y369" s="133"/>
     </row>
     <row r="370" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C370" s="14"/>
+      <c r="D370" s="14"/>
       <c r="E370" s="94"/>
-      <c r="G370" s="136"/>
-      <c r="I370" s="136"/>
-      <c r="K370" s="136"/>
-      <c r="M370" s="136"/>
-      <c r="O370" s="136"/>
-      <c r="Q370" s="136"/>
-      <c r="S370" s="136"/>
-      <c r="U370" s="136"/>
-      <c r="W370" s="95"/>
-      <c r="Y370" s="136"/>
+      <c r="G370" s="133"/>
+      <c r="I370" s="133"/>
+      <c r="K370" s="133"/>
+      <c r="M370" s="133"/>
+      <c r="O370" s="133"/>
+      <c r="Q370" s="133"/>
+      <c r="S370" s="133"/>
+      <c r="U370" s="133"/>
+      <c r="W370" s="97"/>
+      <c r="Y370" s="133"/>
+    </row>
+    <row r="371" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C371" s="14"/>
+      <c r="D371" s="14"/>
+      <c r="E371" s="94"/>
+      <c r="G371" s="133"/>
+      <c r="I371" s="133"/>
+      <c r="K371" s="133"/>
+      <c r="M371" s="133"/>
+      <c r="O371" s="133"/>
+      <c r="Q371" s="133"/>
+      <c r="S371" s="133"/>
+      <c r="U371" s="133"/>
+      <c r="W371" s="97"/>
+      <c r="Y371" s="133"/>
+    </row>
+    <row r="372" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E372" s="94"/>
+      <c r="G372" s="136"/>
+      <c r="I372" s="136"/>
+      <c r="K372" s="136"/>
+      <c r="M372" s="136"/>
+      <c r="O372" s="136"/>
+      <c r="Q372" s="136"/>
+      <c r="S372" s="136"/>
+      <c r="U372" s="136"/>
+      <c r="W372" s="95"/>
+      <c r="Y372" s="136"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -26386,7 +26560,7 @@
       </c>
       <c r="D5" s="100" t="str">
         <f ca="1">_xlfn.CONCAT("ETF_",D15,".csv")</f>
-        <v>ETF_2026-09-17.csv</v>
+        <v>ETF_2026-09-19.csv</v>
       </c>
       <c r="E5" s="86"/>
     </row>
@@ -26515,7 +26689,7 @@
     <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D15" s="104" t="str">
         <f t="shared" ref="D15" ca="1" si="0">TEXT(TODAY(),"yyyy-mm-dd")</f>
-        <v>2026-09-17</v>
+        <v>2026-09-19</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">

--- a/spreadsheets/2026 Fin Inst Database.xlsx
+++ b/spreadsheets/2026 Fin Inst Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-projects\trading\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9969346F-F2DC-4709-A128-0FE88F2A1F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B02D46-F1FD-409B-9FB2-1F173DAA7D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30120" yWindow="675" windowWidth="16035" windowHeight="12225" tabRatio="763" activeTab="2" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
+    <workbookView xWindow="32145" yWindow="1515" windowWidth="21720" windowHeight="12225" tabRatio="763" activeTab="2" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="31" r:id="rId1"/>
@@ -38,55 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-  <valueMetadata count="2">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-    <bk>
-      <rc t="2" v="1"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3543" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="509">
   <si>
     <t>comm_type</t>
   </si>
@@ -1613,96 +1566,6 @@
   </si>
   <si>
     <t>div 2026-10 ex-date</t>
-  </si>
-  <si>
-    <t>Symbol</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>$0.106159 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.078196 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.084227 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.092812 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.088281 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.082614 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.082315 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.100791 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.105460 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.107003 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.073372 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.099260 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.117704 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.126519 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.145673 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.138868 (BlackRock)</t>
-  </si>
-  <si>
-    <t>Not yet showing Oct. 1 on iShares (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.058608 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.056044 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.055342 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.054768 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.055815 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.052463 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.069236 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.068937 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.066775 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.059066 (BlackRock)</t>
-  </si>
-  <si>
-    <t>$0.065558 (BlackRock)</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +1857,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2389,14 +2252,6 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2405,107 +2260,6 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="94">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2648,12 +2402,88 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.000000_);_(&quot;$&quot;* \(#,##0.000000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2668,395 +2498,10 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="Aptos Narrow"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="174" formatCode="0.0000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.000000_);_(&quot;$&quot;* \(#,##0.000000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3926,11 +3371,31 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.000000_);_(&quot;$&quot;* \(#,##0.000000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3945,11 +3410,32 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3964,16 +3450,17 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -3983,12 +3470,313 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.000000_);_(&quot;$&quot;* \(#,##0.000000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4003,11 +3791,68 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color auto="1"/>
-        <name val="Arial"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="174" formatCode="0.0000000"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4022,10 +3867,20 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="Arial"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4040,106 +3895,36 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
-  <rv s="0">
-    <v>7</v>
-    <v>8</v>
-    <v>0</v>
-    <v>1</v>
-  </rv>
-  <rv s="1">
-    <v>8</v>
-    <v>1</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
-  <s t="_error">
-    <k n="colOffset" t="i"/>
-    <k n="errorType" t="i"/>
-    <k n="rwOffset" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="propagated" t="b"/>
-  </s>
-</rvStructures>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}" name="static_data_table" displayName="static_data_table" ref="A1:P188" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86" headerRowCellStyle="Comma" dataCellStyle="Comma">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}" name="static_data_table" displayName="static_data_table" ref="A1:P188" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65" headerRowCellStyle="Comma" dataCellStyle="Comma">
   <autoFilter ref="A1:P188" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P188">
     <sortCondition ref="B1:B188"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="19" xr3:uid="{1221CC04-A25D-42E0-9BD3-B46333797DBE}" name="vpn" dataDxfId="85" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{BED55A9A-3E28-4A17-AA02-2381DB89A658}" name="grouping" dataDxfId="84" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{F9B08B7F-16AE-460B-BDFB-B2726D177E92}" name="subgroup" dataDxfId="83" dataCellStyle="Comma"/>
-    <tableColumn id="1" xr3:uid="{8C59AB6B-6EBF-48B8-9D8A-4E9EFB96C425}" name="my_prod_type" dataDxfId="82"/>
-    <tableColumn id="18" xr3:uid="{D3CEE51C-FF16-474C-AC93-30CEB3E7D375}" name="my_fi_name" dataDxfId="81" dataCellStyle="Comma"/>
-    <tableColumn id="22" xr3:uid="{51F924B8-25BB-4080-AD58-7509A60E27B0}" name="my_pf_name" dataDxfId="80"/>
-    <tableColumn id="2" xr3:uid="{A13A7736-F17C-4146-B643-6EF65FC4B25C}" name="pf_locator" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{211C7B2F-2849-4B0F-B281-BF0424C5B57F}" name="top_currency" dataDxfId="78" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{46C5F41D-D64D-4F76-9E5D-390D6FE03BE6}" name="base_currency" dataDxfId="77" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{E2441BE5-ABB7-40CB-848F-02508F05A37C}" name="comm_type" dataDxfId="76" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{16FCE019-989B-4467-A8B9-96A8E58B2A2A}" name="comm_maker" dataDxfId="75" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{0E805949-D535-4626-85EB-FA3727E7DAF4}" name="comm_taker" dataDxfId="74" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{5709324A-7C63-43F4-AF59-F119177A7972}" name="comm_misc" dataDxfId="73" dataCellStyle="Comma"/>
-    <tableColumn id="8" xr3:uid="{32E47B88-05FD-48EE-97A0-59BC78476043}" name="comm_update" dataDxfId="72" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{B6578BCD-793E-47C9-99CF-D01D02E8D922}" name="mkt_data_stream" dataDxfId="71" dataCellStyle="Comma"/>
-    <tableColumn id="13" xr3:uid="{F138DC7A-FBFD-4726-8F8E-B333700760C4}" name="exclusion" dataDxfId="70" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{1221CC04-A25D-42E0-9BD3-B46333797DBE}" name="vpn" dataDxfId="64" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{BED55A9A-3E28-4A17-AA02-2381DB89A658}" name="grouping" dataDxfId="63" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{F9B08B7F-16AE-460B-BDFB-B2726D177E92}" name="subgroup" dataDxfId="62" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{8C59AB6B-6EBF-48B8-9D8A-4E9EFB96C425}" name="my_prod_type" dataDxfId="61"/>
+    <tableColumn id="18" xr3:uid="{D3CEE51C-FF16-474C-AC93-30CEB3E7D375}" name="my_fi_name" dataDxfId="60" dataCellStyle="Comma"/>
+    <tableColumn id="22" xr3:uid="{51F924B8-25BB-4080-AD58-7509A60E27B0}" name="my_pf_name" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{A13A7736-F17C-4146-B643-6EF65FC4B25C}" name="pf_locator" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{211C7B2F-2849-4B0F-B281-BF0424C5B57F}" name="top_currency" dataDxfId="57" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{46C5F41D-D64D-4F76-9E5D-390D6FE03BE6}" name="base_currency" dataDxfId="56" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{E2441BE5-ABB7-40CB-848F-02508F05A37C}" name="comm_type" dataDxfId="55" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{16FCE019-989B-4467-A8B9-96A8E58B2A2A}" name="comm_maker" dataDxfId="54" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{0E805949-D535-4626-85EB-FA3727E7DAF4}" name="comm_taker" dataDxfId="53" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{5709324A-7C63-43F4-AF59-F119177A7972}" name="comm_misc" dataDxfId="52" dataCellStyle="Comma"/>
+    <tableColumn id="8" xr3:uid="{32E47B88-05FD-48EE-97A0-59BC78476043}" name="comm_update" dataDxfId="51" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{B6578BCD-793E-47C9-99CF-D01D02E8D922}" name="mkt_data_stream" dataDxfId="50" dataCellStyle="Comma"/>
+    <tableColumn id="13" xr3:uid="{F138DC7A-FBFD-4726-8F8E-B333700760C4}" name="exclusion" dataDxfId="49" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}" name="btc_to_do" displayName="btc_to_do" ref="A193:AA246" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}" name="btc_to_do" displayName="btc_to_do" ref="A193:AA246" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <autoFilter ref="A193:AA246" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}">
     <filterColumn colId="1">
       <filters>
@@ -4148,33 +3933,33 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{73FD62E2-E8FE-4C00-9C3C-F3122EB55D0D}" name="Column1" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{F8F856BF-80BD-4398-8276-448953D1A283}" name="Column2" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{859FF76C-0D7F-496C-B885-2DE680F3F916}" name="Column7" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{EFE5B159-5688-4C13-A02D-A6C704275E2E}" name="Column4" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{69D00D15-DF82-46C9-9945-107A85371A6F}" name="Column5" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{F10DE59E-3B92-4DD0-8A04-FAE76E9F8BB9}" name="Column6" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{2D949549-0F5C-4A89-B8F7-72304B9A24F1}" name="Column8" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{C42826CE-029E-4945-8434-CBC9F4DAA57F}" name="Column9" dataDxfId="60" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{F0789B57-A27F-47CD-94AE-4F6B71344DB9}" name="Column92" dataDxfId="59" dataCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{84F8B5AD-93FB-4C3E-8E09-FB358E10FC62}" name="Column93" dataDxfId="58" dataCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{DA8CB162-5C11-45A4-93E0-E0C45C3ED3D0}" name="Column94" dataDxfId="57" dataCellStyle="Comma"/>
-    <tableColumn id="27" xr3:uid="{100A9F62-6915-49BB-B014-4D0BC03BB553}" name="Column95" dataDxfId="56" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{5B60D48A-2B91-4E81-AD9D-2709C1335F32}" name="Column10" dataDxfId="55" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{E1B16D3B-DEA4-44A7-8DE4-CA3F41D77B2B}" name="Column11" dataDxfId="54" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{793817C6-38BE-49BA-A9A6-4F96D87310D9}" name="Column12" dataDxfId="53" dataCellStyle="Comma"/>
-    <tableColumn id="15" xr3:uid="{2AFA675A-D2B0-476D-A865-BB72634DC6DA}" name="Column15" dataDxfId="52"/>
-    <tableColumn id="16" xr3:uid="{B5249436-7148-4EBF-B8E6-5226AA101320}" name="Column16" dataDxfId="51" dataCellStyle="Currency"/>
-    <tableColumn id="17" xr3:uid="{22140E2C-B2EC-4771-8D39-0E8FE9F80B88}" name="Column17" dataDxfId="50"/>
-    <tableColumn id="18" xr3:uid="{AC423A03-E794-4524-9C7D-D02B01892118}" name="Column18" dataDxfId="49" dataCellStyle="Comma"/>
-    <tableColumn id="19" xr3:uid="{F73A917A-F13B-4BB9-8524-E34E6050878C}" name="Column19" dataDxfId="48" dataCellStyle="Comma"/>
-    <tableColumn id="20" xr3:uid="{4A9B484B-EBD7-41D1-8470-161DB87D7FB2}" name="Column20" dataDxfId="47" dataCellStyle="Comma"/>
-    <tableColumn id="21" xr3:uid="{D03D1805-69BB-4D67-B61E-961F2E625E81}" name="Column21" dataDxfId="46"/>
-    <tableColumn id="22" xr3:uid="{66E8E4D1-FF14-404F-8354-025C93AED5CB}" name="Column22" dataDxfId="45"/>
-    <tableColumn id="23" xr3:uid="{9540F131-1C8F-4F4F-8796-92F1AFD57E03}" name="Column23" dataDxfId="44"/>
-    <tableColumn id="24" xr3:uid="{B7156378-CEA1-4808-9801-4E93C755FE92}" name="Column24" dataDxfId="43"/>
-    <tableColumn id="25" xr3:uid="{6908C233-AA1B-4818-BF8F-36FC13C53D09}" name="Column25" dataDxfId="42"/>
-    <tableColumn id="26" xr3:uid="{104781D6-1EEE-4947-A424-3CE3DCADF4CF}" name="Column26" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{73FD62E2-E8FE-4C00-9C3C-F3122EB55D0D}" name="Column1" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{F8F856BF-80BD-4398-8276-448953D1A283}" name="Column2" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{859FF76C-0D7F-496C-B885-2DE680F3F916}" name="Column7" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{EFE5B159-5688-4C13-A02D-A6C704275E2E}" name="Column4" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{69D00D15-DF82-46C9-9945-107A85371A6F}" name="Column5" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{F10DE59E-3B92-4DD0-8A04-FAE76E9F8BB9}" name="Column6" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{2D949549-0F5C-4A89-B8F7-72304B9A24F1}" name="Column8" dataDxfId="40"/>
+    <tableColumn id="9" xr3:uid="{C42826CE-029E-4945-8434-CBC9F4DAA57F}" name="Column9" dataDxfId="39" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{F0789B57-A27F-47CD-94AE-4F6B71344DB9}" name="Column92" dataDxfId="38" dataCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{84F8B5AD-93FB-4C3E-8E09-FB358E10FC62}" name="Column93" dataDxfId="37" dataCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{DA8CB162-5C11-45A4-93E0-E0C45C3ED3D0}" name="Column94" dataDxfId="36" dataCellStyle="Comma"/>
+    <tableColumn id="27" xr3:uid="{100A9F62-6915-49BB-B014-4D0BC03BB553}" name="Column95" dataDxfId="35" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{5B60D48A-2B91-4E81-AD9D-2709C1335F32}" name="Column10" dataDxfId="34" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{E1B16D3B-DEA4-44A7-8DE4-CA3F41D77B2B}" name="Column11" dataDxfId="33" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{793817C6-38BE-49BA-A9A6-4F96D87310D9}" name="Column12" dataDxfId="32" dataCellStyle="Comma"/>
+    <tableColumn id="15" xr3:uid="{2AFA675A-D2B0-476D-A865-BB72634DC6DA}" name="Column15" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{B5249436-7148-4EBF-B8E6-5226AA101320}" name="Column16" dataDxfId="30" dataCellStyle="Currency"/>
+    <tableColumn id="17" xr3:uid="{22140E2C-B2EC-4771-8D39-0E8FE9F80B88}" name="Column17" dataDxfId="29"/>
+    <tableColumn id="18" xr3:uid="{AC423A03-E794-4524-9C7D-D02B01892118}" name="Column18" dataDxfId="28" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{F73A917A-F13B-4BB9-8524-E34E6050878C}" name="Column19" dataDxfId="27" dataCellStyle="Comma"/>
+    <tableColumn id="20" xr3:uid="{4A9B484B-EBD7-41D1-8470-161DB87D7FB2}" name="Column20" dataDxfId="26" dataCellStyle="Comma"/>
+    <tableColumn id="21" xr3:uid="{D03D1805-69BB-4D67-B61E-961F2E625E81}" name="Column21" dataDxfId="25"/>
+    <tableColumn id="22" xr3:uid="{66E8E4D1-FF14-404F-8354-025C93AED5CB}" name="Column22" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{9540F131-1C8F-4F4F-8796-92F1AFD57E03}" name="Column23" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{B7156378-CEA1-4808-9801-4E93C755FE92}" name="Column24" dataDxfId="22"/>
+    <tableColumn id="25" xr3:uid="{6908C233-AA1B-4818-BF8F-36FC13C53D09}" name="Column25" dataDxfId="21"/>
+    <tableColumn id="26" xr3:uid="{104781D6-1EEE-4947-A424-3CE3DCADF4CF}" name="Column26" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4187,47 +3972,47 @@
     <sortCondition ref="G1:G165"/>
   </sortState>
   <tableColumns count="28">
-    <tableColumn id="8" xr3:uid="{8CAFE9A2-351C-491C-8F0E-A191FB5F62F1}" name="grouping" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{8CAFE9A2-351C-491C-8F0E-A191FB5F62F1}" name="grouping" dataDxfId="93"/>
     <tableColumn id="7" xr3:uid="{05D8AE13-6024-4F28-BE04-4F5644C5B73A}" name="subgroup"/>
-    <tableColumn id="1" xr3:uid="{AFA57C80-2B2F-4727-B322-33373A15C9AE}" name="symbol" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{26F4ADAE-9F47-4523-899C-9F45673EC02E}" name="etf family" dataDxfId="1" dataCellStyle="Comma"/>
-    <tableColumn id="2" xr3:uid="{8D355E55-9FB0-4524-AED7-63AB9F6D6462}" name="etf fee" dataDxfId="2" dataCellStyle="Percent"/>
-    <tableColumn id="10" xr3:uid="{970A7118-A815-4E0B-AD6C-48FAB15A53E2}" name="div 2026-10" dataDxfId="0" dataCellStyle="Currency"/>
-    <tableColumn id="28" xr3:uid="{092D8B8C-6C96-4D08-B83C-1ACFDEDD9F8C}" name="div 2026-10 ex-date" dataDxfId="4" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{FCA124B1-94D2-4B56-BB90-0F7311223FEE}" name="div 2026-09" dataDxfId="39" dataCellStyle="Currency"/>
-    <tableColumn id="16" xr3:uid="{BFBF1D57-673D-4449-B2FA-6EED3331C484}" name="div 2026-09 ex-date" dataDxfId="38" dataCellStyle="Percent"/>
-    <tableColumn id="13" xr3:uid="{F669470C-F245-4562-8E25-5953F248B91F}" name="div 2026-08" dataDxfId="37" dataCellStyle="Currency"/>
-    <tableColumn id="23" xr3:uid="{9D2DF049-DA5F-4A77-8D33-ABB58A4438DC}" name="div 2026-08 ex-date" dataDxfId="36" dataCellStyle="Percent"/>
-    <tableColumn id="11" xr3:uid="{BBCBF25D-DDD4-4D61-8E1E-077BE62554AC}" name="div 2026-07" dataDxfId="35" dataCellStyle="Currency"/>
-    <tableColumn id="22" xr3:uid="{9B510A38-BDAA-4C83-A0BA-CBA8258D1B5A}" name="div 2026-07 ex-date" dataDxfId="34" dataCellStyle="Percent"/>
-    <tableColumn id="14" xr3:uid="{D76D35EB-1AB6-4DE5-8C1C-3111406F2F72}" name="div 2026-06" dataDxfId="33" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{2101D0BE-AB56-44C4-AFF7-91BBB1013C9C}" name="div 2026-06 ex-date" dataDxfId="32" dataCellStyle="Percent"/>
-    <tableColumn id="21" xr3:uid="{82A49A8D-4D68-4D59-B5F9-F90A5262424F}" name="div 2026-05" dataDxfId="31" dataCellStyle="Currency"/>
-    <tableColumn id="24" xr3:uid="{2182D668-9AC5-4102-8F80-1187AFD225B7}" name="div 2026-05 ex-date" dataDxfId="30" dataCellStyle="Percent"/>
-    <tableColumn id="20" xr3:uid="{852173F6-72F7-4C68-BCA3-F7246A86D135}" name="div 2026-04" dataDxfId="29" dataCellStyle="Currency"/>
-    <tableColumn id="25" xr3:uid="{B8A617CB-C02A-4BAC-8397-105FB69C924D}" name="div 2026-04 ex-date" dataDxfId="28" dataCellStyle="Percent"/>
-    <tableColumn id="12" xr3:uid="{9BD4CA41-7A1D-40D5-86AC-FF1C5FE693FF}" name="div 2026-03" dataDxfId="27" dataCellStyle="Currency"/>
-    <tableColumn id="15" xr3:uid="{EE81E628-1DED-4A9A-B38F-77C889074F27}" name="div 2026-03 ex-date" dataDxfId="26" dataCellStyle="Percent"/>
-    <tableColumn id="19" xr3:uid="{3AD8B9FD-8C84-4949-A894-23543B2F48F6}" name="div 2026-02" dataDxfId="25" dataCellStyle="Currency"/>
-    <tableColumn id="26" xr3:uid="{B1AEFFE4-8EA5-4C45-A401-AE133D518FD2}" name="div 2026-02 ex-date" dataDxfId="24" dataCellStyle="Percent"/>
-    <tableColumn id="17" xr3:uid="{A1681DB9-E7FD-4AAD-BF01-80B2684F4CDF}" name="div 2026-01" dataDxfId="23" dataCellStyle="Currency"/>
-    <tableColumn id="27" xr3:uid="{576627EC-6EAC-4067-956A-DF67926726DC}" name="div 2026-01 ex-date" dataDxfId="22" dataCellStyle="Percent"/>
-    <tableColumn id="5" xr3:uid="{6C9795AF-4493-4D80-8BB1-FF32A4E90439}" name=" div 2025-12" dataDxfId="21" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{D716E943-B958-4884-BE63-A9B80B433F62}" name="div 2025-12 ex-date" dataDxfId="20" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{9FCCF7D4-0FBF-4FEE-86E1-9320D1C3E195}" name="comment" dataDxfId="19" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{AFA57C80-2B2F-4727-B322-33373A15C9AE}" name="symbol" dataDxfId="92"/>
+    <tableColumn id="18" xr3:uid="{26F4ADAE-9F47-4523-899C-9F45673EC02E}" name="etf family" dataDxfId="91" dataCellStyle="Comma"/>
+    <tableColumn id="2" xr3:uid="{8D355E55-9FB0-4524-AED7-63AB9F6D6462}" name="etf fee" dataDxfId="90" dataCellStyle="Percent"/>
+    <tableColumn id="10" xr3:uid="{970A7118-A815-4E0B-AD6C-48FAB15A53E2}" name="div 2026-10" dataDxfId="89" dataCellStyle="Currency"/>
+    <tableColumn id="28" xr3:uid="{092D8B8C-6C96-4D08-B83C-1ACFDEDD9F8C}" name="div 2026-10 ex-date" dataDxfId="88" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{FCA124B1-94D2-4B56-BB90-0F7311223FEE}" name="div 2026-09" dataDxfId="87" dataCellStyle="Currency"/>
+    <tableColumn id="16" xr3:uid="{BFBF1D57-673D-4449-B2FA-6EED3331C484}" name="div 2026-09 ex-date" dataDxfId="86" dataCellStyle="Percent"/>
+    <tableColumn id="13" xr3:uid="{F669470C-F245-4562-8E25-5953F248B91F}" name="div 2026-08" dataDxfId="85" dataCellStyle="Currency"/>
+    <tableColumn id="23" xr3:uid="{9D2DF049-DA5F-4A77-8D33-ABB58A4438DC}" name="div 2026-08 ex-date" dataDxfId="84" dataCellStyle="Percent"/>
+    <tableColumn id="11" xr3:uid="{BBCBF25D-DDD4-4D61-8E1E-077BE62554AC}" name="div 2026-07" dataDxfId="83" dataCellStyle="Currency"/>
+    <tableColumn id="22" xr3:uid="{9B510A38-BDAA-4C83-A0BA-CBA8258D1B5A}" name="div 2026-07 ex-date" dataDxfId="82" dataCellStyle="Percent"/>
+    <tableColumn id="14" xr3:uid="{D76D35EB-1AB6-4DE5-8C1C-3111406F2F72}" name="div 2026-06" dataDxfId="81" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{2101D0BE-AB56-44C4-AFF7-91BBB1013C9C}" name="div 2026-06 ex-date" dataDxfId="80" dataCellStyle="Percent"/>
+    <tableColumn id="21" xr3:uid="{82A49A8D-4D68-4D59-B5F9-F90A5262424F}" name="div 2026-05" dataDxfId="79" dataCellStyle="Currency"/>
+    <tableColumn id="24" xr3:uid="{2182D668-9AC5-4102-8F80-1187AFD225B7}" name="div 2026-05 ex-date" dataDxfId="78" dataCellStyle="Percent"/>
+    <tableColumn id="20" xr3:uid="{852173F6-72F7-4C68-BCA3-F7246A86D135}" name="div 2026-04" dataDxfId="77" dataCellStyle="Currency"/>
+    <tableColumn id="25" xr3:uid="{B8A617CB-C02A-4BAC-8397-105FB69C924D}" name="div 2026-04 ex-date" dataDxfId="76" dataCellStyle="Percent"/>
+    <tableColumn id="12" xr3:uid="{9BD4CA41-7A1D-40D5-86AC-FF1C5FE693FF}" name="div 2026-03" dataDxfId="75" dataCellStyle="Currency"/>
+    <tableColumn id="15" xr3:uid="{EE81E628-1DED-4A9A-B38F-77C889074F27}" name="div 2026-03 ex-date" dataDxfId="74" dataCellStyle="Percent"/>
+    <tableColumn id="19" xr3:uid="{3AD8B9FD-8C84-4949-A894-23543B2F48F6}" name="div 2026-02" dataDxfId="73" dataCellStyle="Currency"/>
+    <tableColumn id="26" xr3:uid="{B1AEFFE4-8EA5-4C45-A401-AE133D518FD2}" name="div 2026-02 ex-date" dataDxfId="72" dataCellStyle="Percent"/>
+    <tableColumn id="17" xr3:uid="{A1681DB9-E7FD-4AAD-BF01-80B2684F4CDF}" name="div 2026-01" dataDxfId="71" dataCellStyle="Currency"/>
+    <tableColumn id="27" xr3:uid="{576627EC-6EAC-4067-956A-DF67926726DC}" name="div 2026-01 ex-date" dataDxfId="70" dataCellStyle="Percent"/>
+    <tableColumn id="5" xr3:uid="{6C9795AF-4493-4D80-8BB1-FF32A4E90439}" name=" div 2025-12" dataDxfId="69" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{D716E943-B958-4884-BE63-A9B80B433F62}" name="div 2025-12 ex-date" dataDxfId="68" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{9FCCF7D4-0FBF-4FEE-86E1-9320D1C3E195}" name="comment" dataDxfId="67" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}" name="mkt_data_streaming_inputs" displayName="mkt_data_streaming_inputs" ref="A1:D13" totalsRowShown="0" headerRowDxfId="93" dataDxfId="92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}" name="mkt_data_streaming_inputs" displayName="mkt_data_streaming_inputs" ref="A1:D13" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:D13" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1B4EEA70-C71C-4CEF-9887-9E40B33F8AAC}" name="Keys" dataDxfId="91"/>
-    <tableColumn id="2" xr3:uid="{5215E933-000B-4891-AE18-89796F5A216B}" name="Crypto" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{A4E0A8E0-4334-4FB9-95BD-3E9FE4AB471E}" name="Stat_Arb_Group" dataDxfId="89"/>
-    <tableColumn id="5" xr3:uid="{16DC4587-9A67-4643-BE5B-698CEC2360C4}" name="BTC_ETF" dataDxfId="88"/>
+    <tableColumn id="1" xr3:uid="{1B4EEA70-C71C-4CEF-9887-9E40B33F8AAC}" name="Keys" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{5215E933-000B-4891-AE18-89796F5A216B}" name="Crypto" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{A4E0A8E0-4334-4FB9-95BD-3E9FE4AB471E}" name="Stat_Arb_Group" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{16DC4587-9A67-4643-BE5B-698CEC2360C4}" name="BTC_ETF" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16805,61 +16590,61 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A2:B2 A2:A57 C2:C57 B3:B57 A58:C58 B59:C73 A59:A188">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F188 E189:E192 C199:D199 P199:X199 C203:D203 M203 H239:L239">
-    <cfRule type="cellIs" dxfId="16" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="26" operator="equal">
       <formula>"usdt"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F193:F246 Y193:Z246">
-    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="18" operator="equal">
       <formula>"USDC"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="19" operator="equal">
       <formula>"usdt"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G220">
-    <cfRule type="cellIs" dxfId="13" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="22" operator="equal">
       <formula>"usdt"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G239:G240">
-    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="20" operator="equal">
       <formula>"usdt"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I42 H46:I50 K46:L50">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"import"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:L17">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"import"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O188">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O239">
-    <cfRule type="cellIs" dxfId="7" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="16" operator="equal">
       <formula>"usdt"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA203">
-    <cfRule type="cellIs" dxfId="6" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="23" operator="equal">
       <formula>"usdt"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17004,7 +16789,7 @@
       <c r="C2" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="D2" s="150" t="s">
+      <c r="D2" t="s">
         <v>266</v>
       </c>
       <c r="E2" s="92">
@@ -17087,7 +16872,7 @@
       <c r="C3" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="D3" s="150" t="s">
+      <c r="D3" t="s">
         <v>273</v>
       </c>
       <c r="E3" s="92">
@@ -17170,7 +16955,7 @@
       <c r="C4" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="150" t="s">
+      <c r="D4" t="s">
         <v>273</v>
       </c>
       <c r="E4" s="92">
@@ -17253,7 +17038,7 @@
       <c r="C5" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="D5" s="150" t="s">
+      <c r="D5" t="s">
         <v>273</v>
       </c>
       <c r="E5" s="92">
@@ -17336,7 +17121,7 @@
       <c r="C6" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D6" s="150" t="s">
+      <c r="D6" t="s">
         <v>273</v>
       </c>
       <c r="E6" s="92">
@@ -17419,7 +17204,7 @@
       <c r="C7" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="D7" s="150" t="s">
+      <c r="D7" t="s">
         <v>273</v>
       </c>
       <c r="E7" s="92">
@@ -17502,7 +17287,7 @@
       <c r="C8" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="D8" s="150" t="s">
+      <c r="D8" t="s">
         <v>273</v>
       </c>
       <c r="E8" s="92">
@@ -17585,7 +17370,7 @@
       <c r="C9" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="D9" s="150" t="s">
+      <c r="D9" t="s">
         <v>273</v>
       </c>
       <c r="E9" s="92">
@@ -17668,7 +17453,7 @@
       <c r="C10" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="D10" s="150" t="s">
+      <c r="D10" t="s">
         <v>273</v>
       </c>
       <c r="E10" s="92">
@@ -17751,7 +17536,7 @@
       <c r="C11" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="D11" s="150" t="s">
+      <c r="D11" t="s">
         <v>273</v>
       </c>
       <c r="E11" s="92">
@@ -17834,7 +17619,7 @@
       <c r="C12" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="D12" s="150" t="s">
+      <c r="D12" t="s">
         <v>273</v>
       </c>
       <c r="E12" s="92">
@@ -17917,7 +17702,7 @@
       <c r="C13" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="150" t="s">
+      <c r="D13" t="s">
         <v>273</v>
       </c>
       <c r="E13" s="92">
@@ -18000,7 +17785,7 @@
       <c r="C14" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="D14" s="150" t="s">
+      <c r="D14" t="s">
         <v>273</v>
       </c>
       <c r="E14" s="92">
@@ -18083,7 +17868,7 @@
       <c r="C15" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="D15" s="150" t="s">
+      <c r="D15" t="s">
         <v>273</v>
       </c>
       <c r="E15" s="92">
@@ -18166,7 +17951,7 @@
       <c r="C16" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="D16" s="150" t="s">
+      <c r="D16" t="s">
         <v>273</v>
       </c>
       <c r="E16" s="92">
@@ -20659,7 +20444,7 @@
       <c r="C45" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="D45" s="150" t="s">
+      <c r="D45" t="s">
         <v>208</v>
       </c>
       <c r="E45" s="92">
@@ -20742,7 +20527,7 @@
       <c r="C46" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="D46" s="150" t="s">
+      <c r="D46" t="s">
         <v>208</v>
       </c>
       <c r="E46" s="92">
@@ -20825,13 +20610,15 @@
       <c r="C47" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="D47" s="150" t="s">
+      <c r="D47" t="s">
         <v>264</v>
       </c>
       <c r="E47" s="106">
         <v>2E-3</v>
       </c>
-      <c r="F47" s="152"/>
+      <c r="F47" s="128">
+        <v>0.4</v>
+      </c>
       <c r="G47" s="123">
         <v>46296</v>
       </c>
@@ -20906,7 +20693,7 @@
       <c r="C48" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="D48" s="150" t="s">
+      <c r="D48" t="s">
         <v>267</v>
       </c>
       <c r="E48" s="92">
@@ -20989,7 +20776,7 @@
       <c r="C49" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="D49" s="150" t="s">
+      <c r="D49" t="s">
         <v>267</v>
       </c>
       <c r="E49" s="92">
@@ -21072,7 +20859,7 @@
       <c r="C50" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="D50" s="150" t="s">
+      <c r="D50" t="s">
         <v>267</v>
       </c>
       <c r="E50" s="92">
@@ -21155,7 +20942,7 @@
       <c r="C51" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="D51" s="150" t="s">
+      <c r="D51" t="s">
         <v>274</v>
       </c>
       <c r="E51" s="92">
@@ -21238,7 +21025,7 @@
       <c r="C52" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="D52" s="150" t="s">
+      <c r="D52" t="s">
         <v>274</v>
       </c>
       <c r="E52" s="92">
@@ -21321,7 +21108,7 @@
       <c r="C53" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="D53" s="150" t="s">
+      <c r="D53" t="s">
         <v>274</v>
       </c>
       <c r="E53" s="92">
@@ -21404,7 +21191,7 @@
       <c r="C54" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="D54" s="150" t="s">
+      <c r="D54" t="s">
         <v>274</v>
       </c>
       <c r="E54" s="92">
@@ -21487,7 +21274,7 @@
       <c r="C55" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="D55" s="150" t="s">
+      <c r="D55" t="s">
         <v>274</v>
       </c>
       <c r="E55" s="92">
@@ -21570,7 +21357,7 @@
       <c r="C56" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="D56" s="150" t="s">
+      <c r="D56" t="s">
         <v>274</v>
       </c>
       <c r="E56" s="92">
@@ -21653,7 +21440,7 @@
       <c r="C57" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="D57" s="150" t="s">
+      <c r="D57" t="s">
         <v>274</v>
       </c>
       <c r="E57" s="92">
@@ -21736,7 +21523,7 @@
       <c r="C58" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="D58" s="150" t="s">
+      <c r="D58" t="s">
         <v>274</v>
       </c>
       <c r="E58" s="92">
@@ -21819,7 +21606,7 @@
       <c r="C59" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="D59" s="150" t="s">
+      <c r="D59" t="s">
         <v>274</v>
       </c>
       <c r="E59" s="92">
@@ -21902,7 +21689,7 @@
       <c r="C60" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="D60" s="150" t="s">
+      <c r="D60" t="s">
         <v>274</v>
       </c>
       <c r="E60" s="92">
@@ -21985,7 +21772,7 @@
       <c r="C61" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="D61" s="150" t="s">
+      <c r="D61" t="s">
         <v>262</v>
       </c>
       <c r="E61" s="92">
@@ -22068,7 +21855,7 @@
       <c r="C62" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="D62" s="150" t="s">
+      <c r="D62" t="s">
         <v>263</v>
       </c>
       <c r="E62" s="92">
@@ -22151,7 +21938,7 @@
       <c r="C63" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="D63" s="150" t="s">
+      <c r="D63" t="s">
         <v>263</v>
       </c>
       <c r="E63" s="92">
@@ -22234,7 +22021,7 @@
       <c r="C64" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="D64" s="150" t="s">
+      <c r="D64" t="s">
         <v>263</v>
       </c>
       <c r="E64" s="92">
@@ -22317,7 +22104,7 @@
       <c r="C65" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="D65" s="150" t="s">
+      <c r="D65" t="s">
         <v>263</v>
       </c>
       <c r="E65" s="92">
@@ -22400,7 +22187,7 @@
       <c r="C66" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="D66" s="150" t="s">
+      <c r="D66" t="s">
         <v>263</v>
       </c>
       <c r="E66" s="92">
@@ -22483,7 +22270,7 @@
       <c r="C67" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="D67" s="150" t="s">
+      <c r="D67" t="s">
         <v>263</v>
       </c>
       <c r="E67" s="92">
@@ -22566,7 +22353,7 @@
       <c r="C68" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="D68" s="150" t="s">
+      <c r="D68" t="s">
         <v>263</v>
       </c>
       <c r="E68" s="92">
@@ -22649,7 +22436,7 @@
       <c r="C69" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="D69" s="150" t="s">
+      <c r="D69" t="s">
         <v>263</v>
       </c>
       <c r="E69" s="92">
@@ -22732,7 +22519,7 @@
       <c r="C70" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="D70" s="150" t="s">
+      <c r="D70" t="s">
         <v>263</v>
       </c>
       <c r="E70" s="92">
@@ -22815,7 +22602,7 @@
       <c r="C71" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="D71" s="150" t="s">
+      <c r="D71" t="s">
         <v>265</v>
       </c>
       <c r="E71" s="92">
@@ -22898,7 +22685,7 @@
       <c r="C72" s="103" t="s">
         <v>275</v>
       </c>
-      <c r="D72" s="151" t="s">
+      <c r="D72" s="104" t="s">
         <v>272</v>
       </c>
       <c r="E72" s="107">
@@ -22982,7 +22769,7 @@
       <c r="C73" s="103" t="s">
         <v>284</v>
       </c>
-      <c r="D73" s="151" t="s">
+      <c r="D73" s="104" t="s">
         <v>272</v>
       </c>
       <c r="E73" s="107">
@@ -23066,7 +22853,7 @@
       <c r="C74" s="103" t="s">
         <v>292</v>
       </c>
-      <c r="D74" s="151" t="s">
+      <c r="D74" s="104" t="s">
         <v>272</v>
       </c>
       <c r="E74" s="107">
@@ -23150,7 +22937,7 @@
       <c r="C75" s="103" t="s">
         <v>296</v>
       </c>
-      <c r="D75" s="151" t="s">
+      <c r="D75" s="104" t="s">
         <v>272</v>
       </c>
       <c r="E75" s="107">
@@ -23234,7 +23021,7 @@
       <c r="C76" s="103" t="s">
         <v>288</v>
       </c>
-      <c r="D76" s="151" t="s">
+      <c r="D76" s="104" t="s">
         <v>272</v>
       </c>
       <c r="E76" s="107">
@@ -23318,7 +23105,7 @@
       <c r="C77" s="103" t="s">
         <v>300</v>
       </c>
-      <c r="D77" s="151" t="s">
+      <c r="D77" s="104" t="s">
         <v>272</v>
       </c>
       <c r="E77" s="107">
@@ -23402,7 +23189,7 @@
       <c r="C78" s="103" t="s">
         <v>279</v>
       </c>
-      <c r="D78" s="151" t="s">
+      <c r="D78" s="104" t="s">
         <v>272</v>
       </c>
       <c r="E78" s="107">
@@ -23486,7 +23273,7 @@
       <c r="C79" s="103" t="s">
         <v>304</v>
       </c>
-      <c r="D79" s="151" t="s">
+      <c r="D79" s="104" t="s">
         <v>272</v>
       </c>
       <c r="E79" s="107">
@@ -23570,7 +23357,7 @@
       <c r="C80" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="D80" s="151" t="s">
+      <c r="D80" s="104" t="s">
         <v>272</v>
       </c>
       <c r="E80" s="107">
@@ -23654,7 +23441,7 @@
       <c r="C81" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="D81" s="150" t="s">
+      <c r="D81" t="s">
         <v>397</v>
       </c>
       <c r="E81" s="140">
@@ -26146,7 +25933,7 @@
       <c r="C110" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="D110" s="150" t="s">
+      <c r="D110" t="s">
         <v>273</v>
       </c>
       <c r="E110" s="107">
@@ -26230,7 +26017,7 @@
       <c r="C111" s="103" t="s">
         <v>309</v>
       </c>
-      <c r="D111" s="151" t="s">
+      <c r="D111" s="104" t="s">
         <v>273</v>
       </c>
       <c r="E111" s="107">
@@ -26314,7 +26101,7 @@
       <c r="C112" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="D112" s="150" t="s">
+      <c r="D112" t="s">
         <v>273</v>
       </c>
       <c r="E112" s="107">
@@ -26398,7 +26185,7 @@
       <c r="C113" s="103" t="s">
         <v>276</v>
       </c>
-      <c r="D113" s="151" t="s">
+      <c r="D113" s="104" t="s">
         <v>273</v>
       </c>
       <c r="E113" s="107">
@@ -26482,7 +26269,7 @@
       <c r="C114" s="103" t="s">
         <v>285</v>
       </c>
-      <c r="D114" s="151" t="s">
+      <c r="D114" s="104" t="s">
         <v>273</v>
       </c>
       <c r="E114" s="107">
@@ -26566,7 +26353,7 @@
       <c r="C115" s="103" t="s">
         <v>289</v>
       </c>
-      <c r="D115" s="151" t="s">
+      <c r="D115" s="104" t="s">
         <v>273</v>
       </c>
       <c r="E115" s="107">
@@ -26650,7 +26437,7 @@
       <c r="C116" s="103" t="s">
         <v>293</v>
       </c>
-      <c r="D116" s="151" t="s">
+      <c r="D116" s="104" t="s">
         <v>273</v>
       </c>
       <c r="E116" s="107">
@@ -26734,7 +26521,7 @@
       <c r="C117" s="103" t="s">
         <v>297</v>
       </c>
-      <c r="D117" s="151" t="s">
+      <c r="D117" s="104" t="s">
         <v>273</v>
       </c>
       <c r="E117" s="107">
@@ -26818,7 +26605,7 @@
       <c r="C118" s="103" t="s">
         <v>280</v>
       </c>
-      <c r="D118" s="151" t="s">
+      <c r="D118" s="104" t="s">
         <v>273</v>
       </c>
       <c r="E118" s="107">
@@ -26902,7 +26689,7 @@
       <c r="C119" s="103" t="s">
         <v>301</v>
       </c>
-      <c r="D119" s="151" t="s">
+      <c r="D119" s="104" t="s">
         <v>273</v>
       </c>
       <c r="E119" s="107">
@@ -26986,7 +26773,7 @@
       <c r="C120" s="103" t="s">
         <v>305</v>
       </c>
-      <c r="D120" s="151" t="s">
+      <c r="D120" s="104" t="s">
         <v>273</v>
       </c>
       <c r="E120" s="107">
@@ -27070,7 +26857,7 @@
       <c r="C121" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="D121" s="150" t="s">
+      <c r="D121" t="s">
         <v>273</v>
       </c>
       <c r="E121" s="92">
@@ -27154,7 +26941,7 @@
       <c r="C122" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="D122" s="150" t="s">
+      <c r="D122" t="s">
         <v>273</v>
       </c>
       <c r="E122" s="92">
@@ -27237,7 +27024,7 @@
       <c r="C123" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="D123" s="150" t="s">
+      <c r="D123" t="s">
         <v>208</v>
       </c>
       <c r="E123" s="92">
@@ -27320,7 +27107,7 @@
       <c r="C124" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="D124" s="150" t="s">
+      <c r="D124" t="s">
         <v>208</v>
       </c>
       <c r="E124" s="92">
@@ -27403,7 +27190,7 @@
       <c r="C125" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="D125" s="150" t="s">
+      <c r="D125" t="s">
         <v>208</v>
       </c>
       <c r="E125" s="92">
@@ -27487,7 +27274,7 @@
       <c r="C126" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="D126" s="150" t="s">
+      <c r="D126" t="s">
         <v>208</v>
       </c>
       <c r="E126" s="92">
@@ -27571,7 +27358,7 @@
       <c r="C127" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="D127" s="150" t="s">
+      <c r="D127" t="s">
         <v>208</v>
       </c>
       <c r="E127" s="92">
@@ -27654,7 +27441,7 @@
       <c r="C128" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="D128" s="150" t="s">
+      <c r="D128" t="s">
         <v>208</v>
       </c>
       <c r="E128" s="92">
@@ -27737,7 +27524,7 @@
       <c r="C129" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="D129" s="150" t="s">
+      <c r="D129" t="s">
         <v>208</v>
       </c>
       <c r="E129" s="92">
@@ -27820,7 +27607,7 @@
       <c r="C130" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="D130" s="150" t="s">
+      <c r="D130" t="s">
         <v>208</v>
       </c>
       <c r="E130" s="92">
@@ -27903,7 +27690,7 @@
       <c r="C131" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="D131" s="150" t="s">
+      <c r="D131" t="s">
         <v>208</v>
       </c>
       <c r="E131" s="92">
@@ -27987,7 +27774,7 @@
       <c r="C132" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="D132" s="150" t="s">
+      <c r="D132" t="s">
         <v>208</v>
       </c>
       <c r="E132" s="92">
@@ -28071,7 +27858,7 @@
       <c r="C133" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="D133" s="150" t="s">
+      <c r="D133" t="s">
         <v>208</v>
       </c>
       <c r="E133" s="92">
@@ -28154,7 +27941,7 @@
       <c r="C134" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="D134" s="150" t="s">
+      <c r="D134" t="s">
         <v>208</v>
       </c>
       <c r="E134" s="92">
@@ -28237,7 +28024,7 @@
       <c r="C135" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="D135" s="150" t="s">
+      <c r="D135" t="s">
         <v>208</v>
       </c>
       <c r="E135" s="92">
@@ -28321,7 +28108,7 @@
       <c r="C136" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="D136" s="150" t="s">
+      <c r="D136" t="s">
         <v>208</v>
       </c>
       <c r="E136" s="92">
@@ -28405,7 +28192,7 @@
       <c r="C137" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="D137" s="150" t="s">
+      <c r="D137" t="s">
         <v>208</v>
       </c>
       <c r="E137" s="92">
@@ -28489,7 +28276,7 @@
       <c r="C138" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="D138" s="150" t="s">
+      <c r="D138" t="s">
         <v>208</v>
       </c>
       <c r="E138" s="92">
@@ -28573,7 +28360,7 @@
       <c r="C139" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D139" s="150" t="s">
+      <c r="D139" t="s">
         <v>208</v>
       </c>
       <c r="E139" s="92">
@@ -28656,7 +28443,7 @@
       <c r="C140" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="D140" s="150" t="s">
+      <c r="D140" t="s">
         <v>208</v>
       </c>
       <c r="E140" s="92">
@@ -28739,7 +28526,7 @@
       <c r="C141" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="D141" s="150" t="s">
+      <c r="D141" t="s">
         <v>208</v>
       </c>
       <c r="E141" s="92">
@@ -28823,7 +28610,7 @@
       <c r="C142" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="D142" s="150" t="s">
+      <c r="D142" t="s">
         <v>208</v>
       </c>
       <c r="E142" s="92">
@@ -28907,7 +28694,7 @@
       <c r="C143" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="D143" s="150" t="s">
+      <c r="D143" t="s">
         <v>267</v>
       </c>
       <c r="E143" s="92">
@@ -28990,7 +28777,7 @@
       <c r="C144" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="D144" s="150" t="s">
+      <c r="D144" t="s">
         <v>274</v>
       </c>
       <c r="E144" s="140">
@@ -29074,7 +28861,7 @@
       <c r="C145" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="D145" s="150" t="s">
+      <c r="D145" t="s">
         <v>274</v>
       </c>
       <c r="E145" s="140">
@@ -29158,7 +28945,7 @@
       <c r="C146" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="D146" s="150" t="s">
+      <c r="D146" t="s">
         <v>274</v>
       </c>
       <c r="E146" s="92">
@@ -29242,7 +29029,7 @@
       <c r="C147" s="103" t="s">
         <v>286</v>
       </c>
-      <c r="D147" s="151" t="s">
+      <c r="D147" s="104" t="s">
         <v>274</v>
       </c>
       <c r="E147" s="107">
@@ -29326,7 +29113,7 @@
       <c r="C148" s="103" t="s">
         <v>290</v>
       </c>
-      <c r="D148" s="151" t="s">
+      <c r="D148" s="104" t="s">
         <v>274</v>
       </c>
       <c r="E148" s="107">
@@ -29410,7 +29197,7 @@
       <c r="C149" s="103" t="s">
         <v>298</v>
       </c>
-      <c r="D149" s="151" t="s">
+      <c r="D149" s="104" t="s">
         <v>274</v>
       </c>
       <c r="E149" s="107">
@@ -29494,7 +29281,7 @@
       <c r="C150" s="103" t="s">
         <v>306</v>
       </c>
-      <c r="D150" s="151" t="s">
+      <c r="D150" s="104" t="s">
         <v>274</v>
       </c>
       <c r="E150" s="107">
@@ -29578,7 +29365,7 @@
       <c r="C151" s="103" t="s">
         <v>281</v>
       </c>
-      <c r="D151" s="151" t="s">
+      <c r="D151" s="104" t="s">
         <v>274</v>
       </c>
       <c r="E151" s="107">
@@ -29662,7 +29449,7 @@
       <c r="C152" s="103" t="s">
         <v>302</v>
       </c>
-      <c r="D152" s="151" t="s">
+      <c r="D152" s="104" t="s">
         <v>274</v>
       </c>
       <c r="E152" s="107">
@@ -29746,7 +29533,7 @@
       <c r="C153" s="103" t="s">
         <v>310</v>
       </c>
-      <c r="D153" s="151" t="s">
+      <c r="D153" s="104" t="s">
         <v>274</v>
       </c>
       <c r="E153" s="107">
@@ -29830,7 +29617,7 @@
       <c r="C154" s="103" t="s">
         <v>294</v>
       </c>
-      <c r="D154" s="151" t="s">
+      <c r="D154" s="104" t="s">
         <v>274</v>
       </c>
       <c r="E154" s="107">
@@ -29914,7 +29701,7 @@
       <c r="C155" s="103" t="s">
         <v>277</v>
       </c>
-      <c r="D155" s="151" t="s">
+      <c r="D155" s="104" t="s">
         <v>274</v>
       </c>
       <c r="E155" s="107">
@@ -29998,7 +29785,7 @@
       <c r="C156" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="D156" s="150" t="s">
+      <c r="D156" t="s">
         <v>393</v>
       </c>
       <c r="E156" s="92">
@@ -30082,7 +29869,7 @@
       <c r="C157" s="103" t="s">
         <v>278</v>
       </c>
-      <c r="D157" s="151" t="s">
+      <c r="D157" s="104" t="s">
         <v>263</v>
       </c>
       <c r="E157" s="107">
@@ -30166,7 +29953,7 @@
       <c r="C158" s="103" t="s">
         <v>282</v>
       </c>
-      <c r="D158" s="151" t="s">
+      <c r="D158" s="104" t="s">
         <v>263</v>
       </c>
       <c r="E158" s="107">
@@ -30250,7 +30037,7 @@
       <c r="C159" s="103" t="s">
         <v>287</v>
       </c>
-      <c r="D159" s="151" t="s">
+      <c r="D159" s="104" t="s">
         <v>263</v>
       </c>
       <c r="E159" s="107">
@@ -30334,7 +30121,7 @@
       <c r="C160" s="103" t="s">
         <v>291</v>
       </c>
-      <c r="D160" s="151" t="s">
+      <c r="D160" s="104" t="s">
         <v>263</v>
       </c>
       <c r="E160" s="107">
@@ -30418,7 +30205,7 @@
       <c r="C161" s="103" t="s">
         <v>307</v>
       </c>
-      <c r="D161" s="151" t="s">
+      <c r="D161" s="104" t="s">
         <v>263</v>
       </c>
       <c r="E161" s="107">
@@ -30502,7 +30289,7 @@
       <c r="C162" s="103" t="s">
         <v>295</v>
       </c>
-      <c r="D162" s="151" t="s">
+      <c r="D162" s="104" t="s">
         <v>263</v>
       </c>
       <c r="E162" s="107">
@@ -30586,7 +30373,7 @@
       <c r="C163" s="105" t="s">
         <v>299</v>
       </c>
-      <c r="D163" s="151" t="s">
+      <c r="D163" s="104" t="s">
         <v>263</v>
       </c>
       <c r="E163" s="107">
@@ -30669,7 +30456,7 @@
       <c r="C164" s="103" t="s">
         <v>303</v>
       </c>
-      <c r="D164" s="151" t="s">
+      <c r="D164" s="104" t="s">
         <v>263</v>
       </c>
       <c r="E164" s="107">
@@ -30753,7 +30540,7 @@
       <c r="C165" s="103" t="s">
         <v>311</v>
       </c>
-      <c r="D165" s="151" t="s">
+      <c r="D165" s="104" t="s">
         <v>263</v>
       </c>
       <c r="E165" s="107">
@@ -30914,12 +30701,8 @@
     </row>
     <row r="171" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C171" s="14"/>
-      <c r="D171" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="E171" s="92" t="s">
-        <v>510</v>
-      </c>
+      <c r="D171" s="14"/>
+      <c r="E171" s="92"/>
       <c r="F171" s="92"/>
       <c r="G171" s="92"/>
       <c r="I171" s="126"/>
@@ -30934,28 +30717,12 @@
       <c r="AA171" s="126"/>
     </row>
     <row r="172" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C172" s="14" t="b">
-        <f>D172=C17</f>
-        <v>1</v>
-      </c>
-      <c r="D172" s="14" t="s">
-        <v>441</v>
-      </c>
-      <c r="E172" s="92" t="s">
-        <v>511</v>
-      </c>
+      <c r="C172" s="14"/>
+      <c r="D172" s="14"/>
+      <c r="E172" s="92"/>
       <c r="F172" s="92"/>
-      <c r="G172" s="92" t="str" cm="1">
-        <f t="array" ref="G172:H172">_xlfn.TEXTSPLIT(E172," ")</f>
-        <v>$0.106159</v>
-      </c>
-      <c r="H172" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I172" s="153">
-        <f>VALUE(G172)</f>
-        <v>0.106159</v>
-      </c>
+      <c r="G172" s="92"/>
+      <c r="I172" s="126"/>
       <c r="K172" s="126"/>
       <c r="M172" s="126"/>
       <c r="O172" s="126"/>
@@ -30967,28 +30734,12 @@
       <c r="AA172" s="126"/>
     </row>
     <row r="173" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C173" s="14" t="b">
-        <f t="shared" ref="C173:C199" si="0">D173=C18</f>
-        <v>1</v>
-      </c>
-      <c r="D173" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="E173" s="92" t="s">
-        <v>512</v>
-      </c>
+      <c r="C173" s="14"/>
+      <c r="D173" s="14"/>
+      <c r="E173" s="92"/>
       <c r="F173" s="92"/>
-      <c r="G173" s="92" t="str" cm="1">
-        <f t="array" ref="G173:H173">_xlfn.TEXTSPLIT(E173," ")</f>
-        <v>$0.078196</v>
-      </c>
-      <c r="H173" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I173" s="153">
-        <f t="shared" ref="I173:I199" si="1">VALUE(G173)</f>
-        <v>7.8196000000000002E-2</v>
-      </c>
+      <c r="G173" s="92"/>
+      <c r="I173" s="126"/>
       <c r="K173" s="126"/>
       <c r="M173" s="126"/>
       <c r="O173" s="126"/>
@@ -31000,28 +30751,12 @@
       <c r="AA173" s="126"/>
     </row>
     <row r="174" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C174" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D174" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="E174" s="92" t="s">
-        <v>513</v>
-      </c>
+      <c r="C174" s="14"/>
+      <c r="D174" s="14"/>
+      <c r="E174" s="92"/>
       <c r="F174" s="92"/>
-      <c r="G174" s="92" t="str" cm="1">
-        <f t="array" ref="G174:H174">_xlfn.TEXTSPLIT(E174," ")</f>
-        <v>$0.084227</v>
-      </c>
-      <c r="H174" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I174" s="153">
-        <f t="shared" si="1"/>
-        <v>8.4226999999999996E-2</v>
-      </c>
+      <c r="G174" s="92"/>
+      <c r="I174" s="126"/>
       <c r="K174" s="126"/>
       <c r="M174" s="126"/>
       <c r="O174" s="126"/>
@@ -31033,28 +30768,12 @@
       <c r="AA174" s="126"/>
     </row>
     <row r="175" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C175" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D175" s="14" t="s">
-        <v>427</v>
-      </c>
-      <c r="E175" s="92" t="s">
-        <v>514</v>
-      </c>
+      <c r="C175" s="14"/>
+      <c r="D175" s="14"/>
+      <c r="E175" s="92"/>
       <c r="F175" s="92"/>
-      <c r="G175" s="92" t="str" cm="1">
-        <f t="array" ref="G175:H175">_xlfn.TEXTSPLIT(E175," ")</f>
-        <v>$0.092812</v>
-      </c>
-      <c r="H175" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I175" s="153">
-        <f t="shared" si="1"/>
-        <v>9.2812000000000006E-2</v>
-      </c>
+      <c r="G175" s="92"/>
+      <c r="I175" s="126"/>
       <c r="K175" s="126"/>
       <c r="M175" s="126"/>
       <c r="O175" s="126"/>
@@ -31066,28 +30785,12 @@
       <c r="AA175" s="126"/>
     </row>
     <row r="176" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C176" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D176" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="E176" s="92" t="s">
-        <v>515</v>
-      </c>
+      <c r="C176" s="14"/>
+      <c r="D176" s="14"/>
+      <c r="E176" s="92"/>
       <c r="F176" s="92"/>
-      <c r="G176" s="92" t="str" cm="1">
-        <f t="array" ref="G176:H176">_xlfn.TEXTSPLIT(E176," ")</f>
-        <v>$0.088281</v>
-      </c>
-      <c r="H176" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I176" s="153">
-        <f t="shared" si="1"/>
-        <v>8.8280999999999998E-2</v>
-      </c>
+      <c r="G176" s="92"/>
+      <c r="I176" s="126"/>
       <c r="K176" s="126"/>
       <c r="M176" s="126"/>
       <c r="O176" s="126"/>
@@ -31099,28 +30802,12 @@
       <c r="AA176" s="126"/>
     </row>
     <row r="177" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C177" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D177" s="14" t="s">
-        <v>431</v>
-      </c>
-      <c r="E177" s="92" t="s">
-        <v>516</v>
-      </c>
+      <c r="C177" s="14"/>
+      <c r="D177" s="14"/>
+      <c r="E177" s="92"/>
       <c r="F177" s="92"/>
-      <c r="G177" s="92" t="str" cm="1">
-        <f t="array" ref="G177:H177">_xlfn.TEXTSPLIT(E177," ")</f>
-        <v>$0.082614</v>
-      </c>
-      <c r="H177" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I177" s="153">
-        <f t="shared" si="1"/>
-        <v>8.2614000000000007E-2</v>
-      </c>
+      <c r="G177" s="92"/>
+      <c r="I177" s="126"/>
       <c r="K177" s="126"/>
       <c r="M177" s="126"/>
       <c r="O177" s="126"/>
@@ -31132,28 +30819,12 @@
       <c r="AA177" s="126"/>
     </row>
     <row r="178" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C178" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D178" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="E178" s="92" t="s">
-        <v>517</v>
-      </c>
+      <c r="C178" s="14"/>
+      <c r="D178" s="14"/>
+      <c r="E178" s="92"/>
       <c r="F178" s="92"/>
-      <c r="G178" s="92" t="str" cm="1">
-        <f t="array" ref="G178:H178">_xlfn.TEXTSPLIT(E178," ")</f>
-        <v>$0.082315</v>
-      </c>
-      <c r="H178" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I178" s="153">
-        <f t="shared" si="1"/>
-        <v>8.2314999999999999E-2</v>
-      </c>
+      <c r="G178" s="92"/>
+      <c r="I178" s="126"/>
       <c r="K178" s="126"/>
       <c r="M178" s="126"/>
       <c r="O178" s="126"/>
@@ -31165,28 +30836,12 @@
       <c r="AA178" s="126"/>
     </row>
     <row r="179" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C179" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D179" s="14" t="s">
-        <v>435</v>
-      </c>
-      <c r="E179" s="92" t="s">
-        <v>518</v>
-      </c>
+      <c r="C179" s="14"/>
+      <c r="D179" s="14"/>
+      <c r="E179" s="92"/>
       <c r="F179" s="92"/>
-      <c r="G179" s="92" t="str" cm="1">
-        <f t="array" ref="G179:H179">_xlfn.TEXTSPLIT(E179," ")</f>
-        <v>$0.100791</v>
-      </c>
-      <c r="H179" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I179" s="153">
-        <f t="shared" si="1"/>
-        <v>0.10079100000000001</v>
-      </c>
+      <c r="G179" s="92"/>
+      <c r="I179" s="126"/>
       <c r="K179" s="126"/>
       <c r="M179" s="126"/>
       <c r="O179" s="126"/>
@@ -31198,28 +30853,12 @@
       <c r="AA179" s="126"/>
     </row>
     <row r="180" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C180" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D180" s="14" t="s">
-        <v>437</v>
-      </c>
-      <c r="E180" s="92" t="s">
-        <v>519</v>
-      </c>
+      <c r="C180" s="14"/>
+      <c r="D180" s="14"/>
+      <c r="E180" s="92"/>
       <c r="F180" s="92"/>
-      <c r="G180" s="92" t="str" cm="1">
-        <f t="array" ref="G180:H180">_xlfn.TEXTSPLIT(E180," ")</f>
-        <v>$0.105460</v>
-      </c>
-      <c r="H180" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I180" s="153">
-        <f t="shared" si="1"/>
-        <v>0.10546</v>
-      </c>
+      <c r="G180" s="92"/>
+      <c r="I180" s="126"/>
       <c r="K180" s="126"/>
       <c r="M180" s="126"/>
       <c r="O180" s="126"/>
@@ -31231,28 +30870,12 @@
       <c r="AA180" s="126"/>
     </row>
     <row r="181" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C181" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D181" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="E181" s="92" t="s">
-        <v>520</v>
-      </c>
+      <c r="C181" s="14"/>
+      <c r="D181" s="14"/>
+      <c r="E181" s="92"/>
       <c r="F181" s="92"/>
-      <c r="G181" s="92" t="str" cm="1">
-        <f t="array" ref="G181:H181">_xlfn.TEXTSPLIT(E181," ")</f>
-        <v>$0.107003</v>
-      </c>
-      <c r="H181" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I181" s="153">
-        <f t="shared" si="1"/>
-        <v>0.107003</v>
-      </c>
+      <c r="G181" s="92"/>
+      <c r="I181" s="126"/>
       <c r="K181" s="126"/>
       <c r="M181" s="126"/>
       <c r="O181" s="126"/>
@@ -31264,28 +30887,12 @@
       <c r="AA181" s="126"/>
     </row>
     <row r="182" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C182" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D182" s="14" t="s">
-        <v>454</v>
-      </c>
-      <c r="E182" s="92" t="s">
-        <v>521</v>
-      </c>
+      <c r="C182" s="14"/>
+      <c r="D182" s="14"/>
+      <c r="E182" s="92"/>
       <c r="F182" s="92"/>
-      <c r="G182" s="92" t="str" cm="1">
-        <f t="array" ref="G182:H182">_xlfn.TEXTSPLIT(E182," ")</f>
-        <v>$0.073372</v>
-      </c>
-      <c r="H182" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I182" s="153">
-        <f t="shared" si="1"/>
-        <v>7.3372000000000007E-2</v>
-      </c>
+      <c r="G182" s="92"/>
+      <c r="I182" s="126"/>
       <c r="K182" s="126"/>
       <c r="M182" s="126"/>
       <c r="O182" s="126"/>
@@ -31297,28 +30904,12 @@
       <c r="AA182" s="126"/>
     </row>
     <row r="183" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C183" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D183" s="14" t="s">
-        <v>456</v>
-      </c>
-      <c r="E183" s="92" t="s">
-        <v>522</v>
-      </c>
+      <c r="C183" s="14"/>
+      <c r="D183" s="14"/>
+      <c r="E183" s="92"/>
       <c r="F183" s="92"/>
-      <c r="G183" s="92" t="str" cm="1">
-        <f t="array" ref="G183:H183">_xlfn.TEXTSPLIT(E183," ")</f>
-        <v>$0.099260</v>
-      </c>
-      <c r="H183" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I183" s="153">
-        <f t="shared" si="1"/>
-        <v>9.9260000000000001E-2</v>
-      </c>
+      <c r="G183" s="92"/>
+      <c r="I183" s="126"/>
       <c r="K183" s="126"/>
       <c r="M183" s="126"/>
       <c r="O183" s="126"/>
@@ -31330,28 +30921,12 @@
       <c r="AA183" s="126"/>
     </row>
     <row r="184" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C184" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D184" s="14" t="s">
-        <v>458</v>
-      </c>
-      <c r="E184" s="92" t="s">
-        <v>523</v>
-      </c>
+      <c r="C184" s="14"/>
+      <c r="D184" s="14"/>
+      <c r="E184" s="92"/>
       <c r="F184" s="92"/>
-      <c r="G184" s="92" t="str" cm="1">
-        <f t="array" ref="G184:H184">_xlfn.TEXTSPLIT(E184," ")</f>
-        <v>$0.117704</v>
-      </c>
-      <c r="H184" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I184" s="153">
-        <f t="shared" si="1"/>
-        <v>0.117704</v>
-      </c>
+      <c r="G184" s="92"/>
+      <c r="I184" s="126"/>
       <c r="K184" s="126"/>
       <c r="M184" s="126"/>
       <c r="O184" s="126"/>
@@ -31363,28 +30938,12 @@
       <c r="AA184" s="126"/>
     </row>
     <row r="185" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C185" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D185" s="14" t="s">
-        <v>460</v>
-      </c>
-      <c r="E185" s="92" t="s">
-        <v>524</v>
-      </c>
+      <c r="C185" s="14"/>
+      <c r="D185" s="14"/>
+      <c r="E185" s="92"/>
       <c r="F185" s="92"/>
-      <c r="G185" s="92" t="str" cm="1">
-        <f t="array" ref="G185:H185">_xlfn.TEXTSPLIT(E185," ")</f>
-        <v>$0.126519</v>
-      </c>
-      <c r="H185" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I185" s="153">
-        <f t="shared" si="1"/>
-        <v>0.12651899999999999</v>
-      </c>
+      <c r="G185" s="92"/>
+      <c r="I185" s="126"/>
       <c r="K185" s="126"/>
       <c r="M185" s="126"/>
       <c r="O185" s="126"/>
@@ -31396,28 +30955,12 @@
       <c r="AA185" s="126"/>
     </row>
     <row r="186" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C186" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D186" s="14" t="s">
-        <v>462</v>
-      </c>
-      <c r="E186" s="92" t="s">
-        <v>525</v>
-      </c>
+      <c r="C186" s="14"/>
+      <c r="D186" s="14"/>
+      <c r="E186" s="92"/>
       <c r="F186" s="92"/>
-      <c r="G186" s="92" t="str" cm="1">
-        <f t="array" ref="G186:H186">_xlfn.TEXTSPLIT(E186," ")</f>
-        <v>$0.145673</v>
-      </c>
-      <c r="H186" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I186" s="153">
-        <f t="shared" si="1"/>
-        <v>0.145673</v>
-      </c>
+      <c r="G186" s="92"/>
+      <c r="I186" s="126"/>
       <c r="K186" s="126"/>
       <c r="M186" s="126"/>
       <c r="O186" s="126"/>
@@ -31429,28 +30972,12 @@
       <c r="AA186" s="126"/>
     </row>
     <row r="187" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C187" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D187" s="14" t="s">
-        <v>464</v>
-      </c>
-      <c r="E187" s="92" t="s">
-        <v>526</v>
-      </c>
+      <c r="C187" s="14"/>
+      <c r="D187" s="14"/>
+      <c r="E187" s="92"/>
       <c r="F187" s="92"/>
-      <c r="G187" s="92" t="str" cm="1">
-        <f t="array" ref="G187:H187">_xlfn.TEXTSPLIT(E187," ")</f>
-        <v>$0.138868</v>
-      </c>
-      <c r="H187" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I187" s="153">
-        <f t="shared" si="1"/>
-        <v>0.13886799999999999</v>
-      </c>
+      <c r="G187" s="92"/>
+      <c r="I187" s="126"/>
       <c r="K187" s="126"/>
       <c r="M187" s="126"/>
       <c r="O187" s="126"/>
@@ -31462,25 +30989,12 @@
       <c r="AA187" s="126"/>
     </row>
     <row r="188" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C188" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D188" s="14" t="s">
-        <v>466</v>
-      </c>
-      <c r="E188" s="92" t="s">
-        <v>527</v>
-      </c>
+      <c r="C188" s="14"/>
+      <c r="D188" s="14"/>
+      <c r="E188" s="92"/>
       <c r="F188" s="92"/>
-      <c r="G188" s="92" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="G188" ca="1">_xlfn.TEXTSPLIT(E188," ")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I188" s="153" t="e" vm="2">
-        <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="G188" s="92"/>
+      <c r="I188" s="126"/>
       <c r="K188" s="126"/>
       <c r="M188" s="126"/>
       <c r="O188" s="126"/>
@@ -31492,28 +31006,12 @@
       <c r="AA188" s="126"/>
     </row>
     <row r="189" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C189" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D189" s="14" t="s">
-        <v>468</v>
-      </c>
-      <c r="E189" s="92" t="s">
-        <v>528</v>
-      </c>
+      <c r="C189" s="14"/>
+      <c r="D189" s="14"/>
+      <c r="E189" s="92"/>
       <c r="F189" s="92"/>
-      <c r="G189" s="92" t="str" cm="1">
-        <f t="array" ref="G189:H189">_xlfn.TEXTSPLIT(E189," ")</f>
-        <v>$0.058608</v>
-      </c>
-      <c r="H189" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I189" s="153">
-        <f t="shared" si="1"/>
-        <v>5.8608E-2</v>
-      </c>
+      <c r="G189" s="92"/>
+      <c r="I189" s="126"/>
       <c r="K189" s="126"/>
       <c r="M189" s="126"/>
       <c r="O189" s="126"/>
@@ -31525,28 +31023,12 @@
       <c r="AA189" s="126"/>
     </row>
     <row r="190" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C190" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D190" s="14" t="s">
-        <v>470</v>
-      </c>
-      <c r="E190" s="92" t="s">
-        <v>529</v>
-      </c>
+      <c r="C190" s="14"/>
+      <c r="D190" s="14"/>
+      <c r="E190" s="92"/>
       <c r="F190" s="92"/>
-      <c r="G190" s="92" t="str" cm="1">
-        <f t="array" ref="G190:H190">_xlfn.TEXTSPLIT(E190," ")</f>
-        <v>$0.056044</v>
-      </c>
-      <c r="H190" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I190" s="153">
-        <f t="shared" si="1"/>
-        <v>5.6043999999999997E-2</v>
-      </c>
+      <c r="G190" s="92"/>
+      <c r="I190" s="126"/>
       <c r="K190" s="126"/>
       <c r="M190" s="126"/>
       <c r="O190" s="126"/>
@@ -31558,28 +31040,12 @@
       <c r="AA190" s="126"/>
     </row>
     <row r="191" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C191" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D191" s="14" t="s">
-        <v>472</v>
-      </c>
-      <c r="E191" s="92" t="s">
-        <v>530</v>
-      </c>
+      <c r="C191" s="14"/>
+      <c r="D191" s="14"/>
+      <c r="E191" s="92"/>
       <c r="F191" s="92"/>
-      <c r="G191" s="92" t="str" cm="1">
-        <f t="array" ref="G191:H191">_xlfn.TEXTSPLIT(E191," ")</f>
-        <v>$0.055342</v>
-      </c>
-      <c r="H191" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I191" s="153">
-        <f t="shared" si="1"/>
-        <v>5.5342000000000002E-2</v>
-      </c>
+      <c r="G191" s="92"/>
+      <c r="I191" s="126"/>
       <c r="K191" s="126"/>
       <c r="M191" s="126"/>
       <c r="O191" s="126"/>
@@ -31591,28 +31057,12 @@
       <c r="AA191" s="126"/>
     </row>
     <row r="192" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C192" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D192" s="14" t="s">
-        <v>474</v>
-      </c>
-      <c r="E192" s="92" t="s">
-        <v>531</v>
-      </c>
+      <c r="C192" s="14"/>
+      <c r="D192" s="14"/>
+      <c r="E192" s="92"/>
       <c r="F192" s="92"/>
-      <c r="G192" s="92" t="str" cm="1">
-        <f t="array" ref="G192:H192">_xlfn.TEXTSPLIT(E192," ")</f>
-        <v>$0.054768</v>
-      </c>
-      <c r="H192" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I192" s="153">
-        <f t="shared" si="1"/>
-        <v>5.4767999999999997E-2</v>
-      </c>
+      <c r="G192" s="92"/>
+      <c r="I192" s="126"/>
       <c r="K192" s="126"/>
       <c r="M192" s="126"/>
       <c r="O192" s="126"/>
@@ -31624,28 +31074,12 @@
       <c r="AA192" s="126"/>
     </row>
     <row r="193" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C193" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D193" s="14" t="s">
-        <v>476</v>
-      </c>
-      <c r="E193" s="92" t="s">
-        <v>532</v>
-      </c>
+      <c r="C193" s="14"/>
+      <c r="D193" s="14"/>
+      <c r="E193" s="92"/>
       <c r="F193" s="92"/>
-      <c r="G193" s="92" t="str" cm="1">
-        <f t="array" ref="G193:H193">_xlfn.TEXTSPLIT(E193," ")</f>
-        <v>$0.055815</v>
-      </c>
-      <c r="H193" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I193" s="153">
-        <f t="shared" si="1"/>
-        <v>5.5814999999999997E-2</v>
-      </c>
+      <c r="G193" s="92"/>
+      <c r="I193" s="126"/>
       <c r="K193" s="126"/>
       <c r="M193" s="126"/>
       <c r="O193" s="126"/>
@@ -31657,28 +31091,12 @@
       <c r="AA193" s="126"/>
     </row>
     <row r="194" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C194" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D194" s="14" t="s">
-        <v>478</v>
-      </c>
-      <c r="E194" s="92" t="s">
-        <v>533</v>
-      </c>
+      <c r="C194" s="14"/>
+      <c r="D194" s="14"/>
+      <c r="E194" s="92"/>
       <c r="F194" s="92"/>
-      <c r="G194" s="92" t="str" cm="1">
-        <f t="array" ref="G194:H194">_xlfn.TEXTSPLIT(E194," ")</f>
-        <v>$0.052463</v>
-      </c>
-      <c r="H194" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I194" s="153">
-        <f t="shared" si="1"/>
-        <v>5.2463000000000003E-2</v>
-      </c>
+      <c r="G194" s="92"/>
+      <c r="I194" s="126"/>
       <c r="K194" s="126"/>
       <c r="M194" s="126"/>
       <c r="O194" s="126"/>
@@ -31690,28 +31108,12 @@
       <c r="AA194" s="126"/>
     </row>
     <row r="195" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C195" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D195" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E195" s="92" t="s">
-        <v>534</v>
-      </c>
+      <c r="C195" s="14"/>
+      <c r="D195" s="14"/>
+      <c r="E195" s="92"/>
       <c r="F195" s="92"/>
-      <c r="G195" s="92" t="str" cm="1">
-        <f t="array" ref="G195:H195">_xlfn.TEXTSPLIT(E195," ")</f>
-        <v>$0.069236</v>
-      </c>
-      <c r="H195" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I195" s="153">
-        <f t="shared" si="1"/>
-        <v>6.9236000000000006E-2</v>
-      </c>
+      <c r="G195" s="92"/>
+      <c r="I195" s="126"/>
       <c r="K195" s="126"/>
       <c r="M195" s="126"/>
       <c r="O195" s="126"/>
@@ -31723,28 +31125,12 @@
       <c r="AA195" s="126"/>
     </row>
     <row r="196" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C196" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D196" s="14" t="s">
-        <v>482</v>
-      </c>
-      <c r="E196" s="92" t="s">
-        <v>535</v>
-      </c>
+      <c r="C196" s="14"/>
+      <c r="D196" s="14"/>
+      <c r="E196" s="92"/>
       <c r="F196" s="92"/>
-      <c r="G196" s="92" t="str" cm="1">
-        <f t="array" ref="G196:H196">_xlfn.TEXTSPLIT(E196," ")</f>
-        <v>$0.068937</v>
-      </c>
-      <c r="H196" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I196" s="153">
-        <f t="shared" si="1"/>
-        <v>6.8936999999999998E-2</v>
-      </c>
+      <c r="G196" s="92"/>
+      <c r="I196" s="126"/>
       <c r="K196" s="126"/>
       <c r="M196" s="126"/>
       <c r="O196" s="126"/>
@@ -31756,28 +31142,12 @@
       <c r="AA196" s="126"/>
     </row>
     <row r="197" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C197" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D197" s="14" t="s">
-        <v>484</v>
-      </c>
-      <c r="E197" s="92" t="s">
-        <v>536</v>
-      </c>
+      <c r="C197" s="14"/>
+      <c r="D197" s="14"/>
+      <c r="E197" s="92"/>
       <c r="F197" s="92"/>
-      <c r="G197" s="92" t="str" cm="1">
-        <f t="array" ref="G197:H197">_xlfn.TEXTSPLIT(E197," ")</f>
-        <v>$0.066775</v>
-      </c>
-      <c r="H197" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I197" s="153">
-        <f t="shared" si="1"/>
-        <v>6.6775000000000001E-2</v>
-      </c>
+      <c r="G197" s="92"/>
+      <c r="I197" s="126"/>
       <c r="K197" s="126"/>
       <c r="M197" s="126"/>
       <c r="O197" s="126"/>
@@ -31789,28 +31159,12 @@
       <c r="AA197" s="126"/>
     </row>
     <row r="198" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C198" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D198" s="14" t="s">
-        <v>486</v>
-      </c>
-      <c r="E198" s="92" t="s">
-        <v>537</v>
-      </c>
+      <c r="C198" s="14"/>
+      <c r="D198" s="14"/>
+      <c r="E198" s="92"/>
       <c r="F198" s="92"/>
-      <c r="G198" s="92" t="str" cm="1">
-        <f t="array" ref="G198:H198">_xlfn.TEXTSPLIT(E198," ")</f>
-        <v>$0.059066</v>
-      </c>
-      <c r="H198" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I198" s="153">
-        <f t="shared" si="1"/>
-        <v>5.9066E-2</v>
-      </c>
+      <c r="G198" s="92"/>
+      <c r="I198" s="126"/>
       <c r="K198" s="126"/>
       <c r="M198" s="126"/>
       <c r="O198" s="126"/>
@@ -31822,28 +31176,12 @@
       <c r="AA198" s="126"/>
     </row>
     <row r="199" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C199" s="14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D199" s="14" t="s">
-        <v>488</v>
-      </c>
-      <c r="E199" s="92" t="s">
-        <v>538</v>
-      </c>
+      <c r="C199" s="14"/>
+      <c r="D199" s="14"/>
+      <c r="E199" s="92"/>
       <c r="F199" s="92"/>
-      <c r="G199" s="92" t="str" cm="1">
-        <f t="array" ref="G199:H199">_xlfn.TEXTSPLIT(E199," ")</f>
-        <v>$0.065558</v>
-      </c>
-      <c r="H199" s="123" t="str">
-        <v>(BlackRock)</v>
-      </c>
-      <c r="I199" s="153">
-        <f t="shared" si="1"/>
-        <v>6.5558000000000005E-2</v>
-      </c>
+      <c r="G199" s="92"/>
+      <c r="I199" s="126"/>
       <c r="K199" s="126"/>
       <c r="M199" s="126"/>
       <c r="O199" s="126"/>
@@ -34989,7 +34327,7 @@
       </c>
       <c r="D5" s="98" t="str">
         <f ca="1">_xlfn.CONCAT("ETF_",D15,".csv")</f>
-        <v>ETF_2026-10-01.csv</v>
+        <v>ETF_2026-10-02.csv</v>
       </c>
       <c r="E5" s="85"/>
     </row>
@@ -35118,7 +34456,7 @@
     <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D15" s="102" t="str">
         <f t="shared" ref="D15" ca="1" si="0">TEXT(TODAY(),"yyyy-mm-dd")</f>
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -35139,7 +34477,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B2:D2">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/spreadsheets/2026 Fin Inst Database.xlsx
+++ b/spreadsheets/2026 Fin Inst Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-projects\trading\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B02D46-F1FD-409B-9FB2-1F173DAA7D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBDACD3-C872-4451-94EF-07CCB320DDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32145" yWindow="1515" windowWidth="21720" windowHeight="12225" tabRatio="763" activeTab="2" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="763" activeTab="3" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="31" r:id="rId1"/>

--- a/spreadsheets/2026 Fin Inst Database.xlsx
+++ b/spreadsheets/2026 Fin Inst Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-projects\trading\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE0BDB1-B309-472A-85E7-D18F59108BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875545AC-9E87-4D0E-86F5-4D22B6E7D11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1455" yWindow="1725" windowWidth="26145" windowHeight="12885" tabRatio="763" firstSheet="2" activeTab="2" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
+    <workbookView xWindow="28830" yWindow="375" windowWidth="28635" windowHeight="14850" tabRatio="763" activeTab="2" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="31" r:id="rId1"/>
@@ -2441,7 +2441,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
-  <dxfs count="115">
+  <dxfs count="113">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2559,26 +2559,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4770,133 +4750,133 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}" name="crypto_inputs" displayName="crypto_inputs" ref="A1:R73" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" headerRowCellStyle="Comma" dataCellStyle="Comma">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}" name="crypto_inputs" displayName="crypto_inputs" ref="A1:R73" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67" headerRowCellStyle="Comma" dataCellStyle="Comma">
   <autoFilter ref="A1:R73" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R73">
     <sortCondition descending="1" ref="A1:A73"/>
   </sortState>
   <tableColumns count="18">
-    <tableColumn id="14" xr3:uid="{AE9F6681-044C-49F1-A049-ABF4F62D16D5}" name="mkt_data_stream" dataDxfId="68" dataCellStyle="Comma"/>
-    <tableColumn id="18" xr3:uid="{D3CEE51C-FF16-474C-AC93-30CEB3E7D375}" name="my_fi_name" dataDxfId="67" dataCellStyle="Comma"/>
-    <tableColumn id="13" xr3:uid="{F138DC7A-FBFD-4726-8F8E-B333700760C4}" name="disqualifying note" dataDxfId="66" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{BED55A9A-3E28-4A17-AA02-2381DB89A658}" name="category1" dataDxfId="65" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{F9B08B7F-16AE-460B-BDFB-B2726D177E92}" name="category2" dataDxfId="64" dataCellStyle="Comma"/>
-    <tableColumn id="15" xr3:uid="{8E202CEB-E8E6-47CA-932D-C16AE5D50E53}" name="etf family" dataDxfId="63" dataCellStyle="Comma"/>
-    <tableColumn id="16" xr3:uid="{2F5F5933-5123-4CD9-B4C1-D1312F01E4DE}" name="etf fee" dataDxfId="62" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{211C7B2F-2849-4B0F-B281-BF0424C5B57F}" name="top_currency" dataDxfId="61" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{46C5F41D-D64D-4F76-9E5D-390D6FE03BE6}" name="base_currency" dataDxfId="60" dataCellStyle="Comma"/>
-    <tableColumn id="2" xr3:uid="{A13A7736-F17C-4146-B643-6EF65FC4B25C}" name="pf_locator" dataDxfId="59" dataCellStyle="Comma"/>
-    <tableColumn id="1" xr3:uid="{8C59AB6B-6EBF-48B8-9D8A-4E9EFB96C425}" name="my_prod_type" dataDxfId="58"/>
-    <tableColumn id="22" xr3:uid="{51F924B8-25BB-4080-AD58-7509A60E27B0}" name="my_pf_name" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{E2441BE5-ABB7-40CB-848F-02508F05A37C}" name="comm_type" dataDxfId="56" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{16FCE019-989B-4467-A8B9-96A8E58B2A2A}" name="comm_maker" dataDxfId="55" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{0E805949-D535-4626-85EB-FA3727E7DAF4}" name="comm_taker" dataDxfId="54" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{5709324A-7C63-43F4-AF59-F119177A7972}" name="comm_misc" dataDxfId="53" dataCellStyle="Comma"/>
-    <tableColumn id="8" xr3:uid="{32E47B88-05FD-48EE-97A0-59BC78476043}" name="comm_update" dataDxfId="52" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{B6578BCD-793E-47C9-99CF-D01D02E8D922}" name="vpn" dataDxfId="51" dataCellStyle="Comma"/>
+    <tableColumn id="14" xr3:uid="{AE9F6681-044C-49F1-A049-ABF4F62D16D5}" name="mkt_data_stream" dataDxfId="66" dataCellStyle="Comma"/>
+    <tableColumn id="18" xr3:uid="{D3CEE51C-FF16-474C-AC93-30CEB3E7D375}" name="my_fi_name" dataDxfId="65" dataCellStyle="Comma"/>
+    <tableColumn id="13" xr3:uid="{F138DC7A-FBFD-4726-8F8E-B333700760C4}" name="disqualifying note" dataDxfId="64" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{BED55A9A-3E28-4A17-AA02-2381DB89A658}" name="category1" dataDxfId="63" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{F9B08B7F-16AE-460B-BDFB-B2726D177E92}" name="category2" dataDxfId="62" dataCellStyle="Comma"/>
+    <tableColumn id="15" xr3:uid="{8E202CEB-E8E6-47CA-932D-C16AE5D50E53}" name="etf family" dataDxfId="61" dataCellStyle="Comma"/>
+    <tableColumn id="16" xr3:uid="{2F5F5933-5123-4CD9-B4C1-D1312F01E4DE}" name="etf fee" dataDxfId="60" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{211C7B2F-2849-4B0F-B281-BF0424C5B57F}" name="top_currency" dataDxfId="59" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{46C5F41D-D64D-4F76-9E5D-390D6FE03BE6}" name="base_currency" dataDxfId="58" dataCellStyle="Comma"/>
+    <tableColumn id="2" xr3:uid="{A13A7736-F17C-4146-B643-6EF65FC4B25C}" name="pf_locator" dataDxfId="57" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{8C59AB6B-6EBF-48B8-9D8A-4E9EFB96C425}" name="my_prod_type" dataDxfId="56"/>
+    <tableColumn id="22" xr3:uid="{51F924B8-25BB-4080-AD58-7509A60E27B0}" name="my_pf_name" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{E2441BE5-ABB7-40CB-848F-02508F05A37C}" name="comm_type" dataDxfId="54" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{16FCE019-989B-4467-A8B9-96A8E58B2A2A}" name="comm_maker" dataDxfId="53" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{0E805949-D535-4626-85EB-FA3727E7DAF4}" name="comm_taker" dataDxfId="52" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{5709324A-7C63-43F4-AF59-F119177A7972}" name="comm_misc" dataDxfId="51" dataCellStyle="Comma"/>
+    <tableColumn id="8" xr3:uid="{32E47B88-05FD-48EE-97A0-59BC78476043}" name="comm_update" dataDxfId="50" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{B6578BCD-793E-47C9-99CF-D01D02E8D922}" name="vpn" dataDxfId="49" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA181052-8538-4BDE-9B79-99824A5039A6}" name="equity_inputs" displayName="equity_inputs" ref="A1:AP226" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113" headerRowCellStyle="Comma" dataCellStyle="Comma">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA181052-8538-4BDE-9B79-99824A5039A6}" name="equity_inputs" displayName="equity_inputs" ref="A1:AP226" totalsRowShown="0" headerRowDxfId="112" dataDxfId="111" headerRowCellStyle="Comma" dataCellStyle="Comma">
   <autoFilter ref="A1:AP226" xr:uid="{AA181052-8538-4BDE-9B79-99824A5039A6}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AP226">
     <sortCondition ref="B1:B226"/>
   </sortState>
   <tableColumns count="42">
-    <tableColumn id="14" xr3:uid="{B9E7859D-283F-459F-B5FC-7492060346EF}" name="mkt_data_stream" dataDxfId="112" dataCellStyle="Comma"/>
-    <tableColumn id="18" xr3:uid="{C158D3E6-44D8-4136-9E49-87057A5E2D35}" name="my_fi_name" dataDxfId="111" dataCellStyle="Comma"/>
-    <tableColumn id="13" xr3:uid="{B8FA96DB-A591-405B-89D4-88C2C843AF49}" name="disqualifying note" dataDxfId="110" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{FD21DD83-85C2-47FF-90F4-C97678F2BCB4}" name="category1" dataDxfId="109" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{05EFBA4D-5176-4DB3-955F-729F5A712AD1}" name="category2" dataDxfId="108" dataCellStyle="Comma"/>
-    <tableColumn id="40" xr3:uid="{E0FE2CE5-2695-4415-9029-E809758DF847}" name="category3" dataDxfId="107" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{8AE22F3D-E74C-49C3-8AE8-D4ABD4B8D678}" name="etf family" dataDxfId="106" dataCellStyle="Comma"/>
-    <tableColumn id="15" xr3:uid="{1D7AB539-4D0B-4D52-A49F-627A35F16C26}" name="etf fee" dataDxfId="105" dataCellStyle="Percent"/>
-    <tableColumn id="16" xr3:uid="{99EF2196-0837-4539-9D7D-AB5E4FAA5F25}" name=" div 2025-12" dataDxfId="104" dataCellStyle="Comma"/>
-    <tableColumn id="17" xr3:uid="{FD063936-E2C7-4A15-8018-26DAFCD0347D}" name="div 2025-12 ex-date" dataDxfId="103" dataCellStyle="Comma"/>
-    <tableColumn id="19" xr3:uid="{6B5D6F46-DC89-4DD2-A8F5-ED89E53527A2}" name="div 2026-01" dataDxfId="102" dataCellStyle="Comma"/>
-    <tableColumn id="20" xr3:uid="{B077032E-9078-4BBD-AF52-AC1E68990BC9}" name="div 2026-01 ex-date" dataDxfId="101" dataCellStyle="Comma"/>
-    <tableColumn id="21" xr3:uid="{6105DC40-7BE1-4897-BDBE-71FD0688583C}" name="div 2026-02" dataDxfId="100" dataCellStyle="Comma"/>
-    <tableColumn id="23" xr3:uid="{C121E1DA-7970-452E-B3CE-3284BEDE696F}" name="div 2026-02 ex-date" dataDxfId="99" dataCellStyle="Comma"/>
-    <tableColumn id="24" xr3:uid="{524041E5-BF0C-47EB-B8A5-17DDE0D7066F}" name="div 2026-03" dataDxfId="98" dataCellStyle="Comma"/>
-    <tableColumn id="25" xr3:uid="{4950AEC5-E1D9-4076-9D30-8C37C620CD2C}" name="div 2026-03 ex-date" dataDxfId="97" dataCellStyle="Comma"/>
-    <tableColumn id="26" xr3:uid="{D0B52289-D738-4ED0-BE6A-4EB4651A6C5B}" name="div 2026-04" dataDxfId="96" dataCellStyle="Comma"/>
-    <tableColumn id="27" xr3:uid="{7DAD3645-A5C6-4D8F-B115-7A3687B1A7A8}" name="div 2026-04 ex-date" dataDxfId="95" dataCellStyle="Comma"/>
-    <tableColumn id="28" xr3:uid="{0D42A8E5-743F-488A-9E4B-ECD2E0CA3E0A}" name="div 2026-05" dataDxfId="94" dataCellStyle="Comma"/>
-    <tableColumn id="29" xr3:uid="{0B1995D5-836A-4006-A48D-0307C155F430}" name="div 2026-05 ex-date" dataDxfId="93" dataCellStyle="Comma"/>
-    <tableColumn id="30" xr3:uid="{E3032677-FBA3-435F-A667-7F3002D08E55}" name="div 2026-06" dataDxfId="92" dataCellStyle="Comma"/>
-    <tableColumn id="31" xr3:uid="{25AC86CB-8EDE-4A8E-A5B8-D301C311152E}" name="div 2026-06 ex-date" dataDxfId="91" dataCellStyle="Comma"/>
-    <tableColumn id="32" xr3:uid="{02694708-4881-4FA3-A0D9-A4DF987903E6}" name="div 2026-07" dataDxfId="90" dataCellStyle="Comma"/>
-    <tableColumn id="33" xr3:uid="{6CB7666A-1ABA-4CEC-9D28-E20E17F388B3}" name="div 2026-07 ex-date" dataDxfId="89" dataCellStyle="Comma"/>
-    <tableColumn id="34" xr3:uid="{D1241C91-DA69-430C-863D-07C2DA4C1ECB}" name="div 2026-08" dataDxfId="88" dataCellStyle="Comma"/>
-    <tableColumn id="35" xr3:uid="{EA945934-4FA4-457A-ABA9-51C3C213977F}" name="div 2026-08 ex-date" dataDxfId="87" dataCellStyle="Comma"/>
-    <tableColumn id="36" xr3:uid="{B8829B43-BDF7-4C79-8DB8-23EBB56C8AC7}" name="div 2026-09" dataDxfId="86" dataCellStyle="Comma"/>
-    <tableColumn id="37" xr3:uid="{0B635EC3-A961-44D4-8EAB-D8944F97733A}" name="div 2026-09 ex-date" dataDxfId="85" dataCellStyle="Comma"/>
-    <tableColumn id="38" xr3:uid="{86B81DCA-FD5B-4E43-BC04-EE6E3924D052}" name="div 2026-10" dataDxfId="84" dataCellStyle="Comma"/>
-    <tableColumn id="39" xr3:uid="{E54B6B2D-95E9-4A59-8884-CAA967E71657}" name="div 2026-10 ex-date" dataDxfId="83" dataCellStyle="Comma"/>
-    <tableColumn id="44" xr3:uid="{7ACE1DC9-8F16-4A8C-A1D7-6CA2219773E8}" name="div 2026-11" dataDxfId="82" dataCellStyle="Comma"/>
-    <tableColumn id="45" xr3:uid="{D455B03D-CF37-44D2-9E4A-3D3EE75118EA}" name="div 2026-11 ex-date" dataDxfId="81" dataCellStyle="Comma"/>
-    <tableColumn id="42" xr3:uid="{31937B88-09E8-450C-AB75-AC01630E0023}" name="div 2026-12" dataDxfId="80" dataCellStyle="Comma"/>
-    <tableColumn id="43" xr3:uid="{3EBCF0B3-0917-4FA4-A0A5-459B70FF847E}" name="div 2026-12 ex-date" dataDxfId="79" dataCellStyle="Comma"/>
-    <tableColumn id="2" xr3:uid="{E09F1F43-E8B1-4493-93DC-B4B241E28DE4}" name="pf_locator" dataDxfId="78" dataCellStyle="Comma"/>
-    <tableColumn id="1" xr3:uid="{2B9B859C-AA9C-4472-8098-F421DF695AA8}" name="my_prod_type" dataDxfId="77" dataCellStyle="Comma"/>
-    <tableColumn id="22" xr3:uid="{550B25BC-F5B5-4458-8819-9754046A90AD}" name="my_pf_name" dataDxfId="76" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{32F67A3B-8384-4F3D-84AE-70CD50E8F9E6}" name="comm_type" dataDxfId="75" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{FF3F76FB-0A9F-4EBF-8240-3AF9FE706046}" name="comm_maker" dataDxfId="74" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{1983D463-B14C-4E51-819C-221E1856FFE2}" name="comm_taker" dataDxfId="73" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{779401E1-B251-4A89-B0B0-DA63C83ED06B}" name="comm_misc" dataDxfId="72" dataCellStyle="Comma"/>
-    <tableColumn id="8" xr3:uid="{4FF98E47-C097-4074-8F6F-71B6D6D3E6F9}" name="comm_update" dataDxfId="71" dataCellStyle="Comma"/>
+    <tableColumn id="14" xr3:uid="{B9E7859D-283F-459F-B5FC-7492060346EF}" name="mkt_data_stream" dataDxfId="110" dataCellStyle="Comma"/>
+    <tableColumn id="18" xr3:uid="{C158D3E6-44D8-4136-9E49-87057A5E2D35}" name="my_fi_name" dataDxfId="109" dataCellStyle="Comma"/>
+    <tableColumn id="13" xr3:uid="{B8FA96DB-A591-405B-89D4-88C2C843AF49}" name="disqualifying note" dataDxfId="108" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{FD21DD83-85C2-47FF-90F4-C97678F2BCB4}" name="category1" dataDxfId="107" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{05EFBA4D-5176-4DB3-955F-729F5A712AD1}" name="category2" dataDxfId="106" dataCellStyle="Comma"/>
+    <tableColumn id="40" xr3:uid="{E0FE2CE5-2695-4415-9029-E809758DF847}" name="category3" dataDxfId="105" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{8AE22F3D-E74C-49C3-8AE8-D4ABD4B8D678}" name="etf family" dataDxfId="104" dataCellStyle="Comma"/>
+    <tableColumn id="15" xr3:uid="{1D7AB539-4D0B-4D52-A49F-627A35F16C26}" name="etf fee" dataDxfId="103" dataCellStyle="Percent"/>
+    <tableColumn id="16" xr3:uid="{99EF2196-0837-4539-9D7D-AB5E4FAA5F25}" name=" div 2025-12" dataDxfId="102" dataCellStyle="Comma"/>
+    <tableColumn id="17" xr3:uid="{FD063936-E2C7-4A15-8018-26DAFCD0347D}" name="div 2025-12 ex-date" dataDxfId="101" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{6B5D6F46-DC89-4DD2-A8F5-ED89E53527A2}" name="div 2026-01" dataDxfId="100" dataCellStyle="Comma"/>
+    <tableColumn id="20" xr3:uid="{B077032E-9078-4BBD-AF52-AC1E68990BC9}" name="div 2026-01 ex-date" dataDxfId="99" dataCellStyle="Comma"/>
+    <tableColumn id="21" xr3:uid="{6105DC40-7BE1-4897-BDBE-71FD0688583C}" name="div 2026-02" dataDxfId="98" dataCellStyle="Comma"/>
+    <tableColumn id="23" xr3:uid="{C121E1DA-7970-452E-B3CE-3284BEDE696F}" name="div 2026-02 ex-date" dataDxfId="97" dataCellStyle="Comma"/>
+    <tableColumn id="24" xr3:uid="{524041E5-BF0C-47EB-B8A5-17DDE0D7066F}" name="div 2026-03" dataDxfId="96" dataCellStyle="Comma"/>
+    <tableColumn id="25" xr3:uid="{4950AEC5-E1D9-4076-9D30-8C37C620CD2C}" name="div 2026-03 ex-date" dataDxfId="95" dataCellStyle="Comma"/>
+    <tableColumn id="26" xr3:uid="{D0B52289-D738-4ED0-BE6A-4EB4651A6C5B}" name="div 2026-04" dataDxfId="94" dataCellStyle="Comma"/>
+    <tableColumn id="27" xr3:uid="{7DAD3645-A5C6-4D8F-B115-7A3687B1A7A8}" name="div 2026-04 ex-date" dataDxfId="93" dataCellStyle="Comma"/>
+    <tableColumn id="28" xr3:uid="{0D42A8E5-743F-488A-9E4B-ECD2E0CA3E0A}" name="div 2026-05" dataDxfId="92" dataCellStyle="Comma"/>
+    <tableColumn id="29" xr3:uid="{0B1995D5-836A-4006-A48D-0307C155F430}" name="div 2026-05 ex-date" dataDxfId="91" dataCellStyle="Comma"/>
+    <tableColumn id="30" xr3:uid="{E3032677-FBA3-435F-A667-7F3002D08E55}" name="div 2026-06" dataDxfId="90" dataCellStyle="Comma"/>
+    <tableColumn id="31" xr3:uid="{25AC86CB-8EDE-4A8E-A5B8-D301C311152E}" name="div 2026-06 ex-date" dataDxfId="89" dataCellStyle="Comma"/>
+    <tableColumn id="32" xr3:uid="{02694708-4881-4FA3-A0D9-A4DF987903E6}" name="div 2026-07" dataDxfId="88" dataCellStyle="Comma"/>
+    <tableColumn id="33" xr3:uid="{6CB7666A-1ABA-4CEC-9D28-E20E17F388B3}" name="div 2026-07 ex-date" dataDxfId="87" dataCellStyle="Comma"/>
+    <tableColumn id="34" xr3:uid="{D1241C91-DA69-430C-863D-07C2DA4C1ECB}" name="div 2026-08" dataDxfId="86" dataCellStyle="Comma"/>
+    <tableColumn id="35" xr3:uid="{EA945934-4FA4-457A-ABA9-51C3C213977F}" name="div 2026-08 ex-date" dataDxfId="85" dataCellStyle="Comma"/>
+    <tableColumn id="36" xr3:uid="{B8829B43-BDF7-4C79-8DB8-23EBB56C8AC7}" name="div 2026-09" dataDxfId="84" dataCellStyle="Comma"/>
+    <tableColumn id="37" xr3:uid="{0B635EC3-A961-44D4-8EAB-D8944F97733A}" name="div 2026-09 ex-date" dataDxfId="83" dataCellStyle="Comma"/>
+    <tableColumn id="38" xr3:uid="{86B81DCA-FD5B-4E43-BC04-EE6E3924D052}" name="div 2026-10" dataDxfId="82" dataCellStyle="Comma"/>
+    <tableColumn id="39" xr3:uid="{E54B6B2D-95E9-4A59-8884-CAA967E71657}" name="div 2026-10 ex-date" dataDxfId="81" dataCellStyle="Comma"/>
+    <tableColumn id="44" xr3:uid="{7ACE1DC9-8F16-4A8C-A1D7-6CA2219773E8}" name="div 2026-11" dataDxfId="80" dataCellStyle="Comma"/>
+    <tableColumn id="45" xr3:uid="{D455B03D-CF37-44D2-9E4A-3D3EE75118EA}" name="div 2026-11 ex-date" dataDxfId="79" dataCellStyle="Comma"/>
+    <tableColumn id="42" xr3:uid="{31937B88-09E8-450C-AB75-AC01630E0023}" name="div 2026-12" dataDxfId="78" dataCellStyle="Comma"/>
+    <tableColumn id="43" xr3:uid="{3EBCF0B3-0917-4FA4-A0A5-459B70FF847E}" name="div 2026-12 ex-date" dataDxfId="77" dataCellStyle="Comma"/>
+    <tableColumn id="2" xr3:uid="{E09F1F43-E8B1-4493-93DC-B4B241E28DE4}" name="pf_locator" dataDxfId="76" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{2B9B859C-AA9C-4472-8098-F421DF695AA8}" name="my_prod_type" dataDxfId="75" dataCellStyle="Comma"/>
+    <tableColumn id="22" xr3:uid="{550B25BC-F5B5-4458-8819-9754046A90AD}" name="my_pf_name" dataDxfId="74" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{32F67A3B-8384-4F3D-84AE-70CD50E8F9E6}" name="comm_type" dataDxfId="73" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{FF3F76FB-0A9F-4EBF-8240-3AF9FE706046}" name="comm_maker" dataDxfId="72" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{1983D463-B14C-4E51-819C-221E1856FFE2}" name="comm_taker" dataDxfId="71" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{779401E1-B251-4A89-B0B0-DA63C83ED06B}" name="comm_misc" dataDxfId="70" dataCellStyle="Comma"/>
+    <tableColumn id="8" xr3:uid="{4FF98E47-C097-4074-8F6F-71B6D6D3E6F9}" name="comm_update" dataDxfId="69" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}" name="mkt_data_streaming_inputs" displayName="mkt_data_streaming_inputs" ref="A1:D13" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}" name="mkt_data_streaming_inputs" displayName="mkt_data_streaming_inputs" ref="A1:D13" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <autoFilter ref="A1:D13" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1B4EEA70-C71C-4CEF-9887-9E40B33F8AAC}" name="Keys" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{5215E933-000B-4891-AE18-89796F5A216B}" name="Crypto" dataDxfId="47"/>
-    <tableColumn id="4" xr3:uid="{A4E0A8E0-4334-4FB9-95BD-3E9FE4AB471E}" name="Stat_Arb_Group" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{16DC4587-9A67-4643-BE5B-698CEC2360C4}" name="BTC_ETF" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{1B4EEA70-C71C-4CEF-9887-9E40B33F8AAC}" name="Keys" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{5215E933-000B-4891-AE18-89796F5A216B}" name="Crypto" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{A4E0A8E0-4334-4FB9-95BD-3E9FE4AB471E}" name="Stat_Arb_Group" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{16DC4587-9A67-4643-BE5B-698CEC2360C4}" name="BTC_ETF" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}" name="btc_to_do" displayName="btc_to_do" ref="A1:AA54" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}" name="btc_to_do" displayName="btc_to_do" ref="A1:AA54" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="A1:AA54" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{73FD62E2-E8FE-4C00-9C3C-F3122EB55D0D}" name="Column1" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{F8F856BF-80BD-4398-8276-448953D1A283}" name="Column2" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{859FF76C-0D7F-496C-B885-2DE680F3F916}" name="Column7" dataDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{EFE5B159-5688-4C13-A02D-A6C704275E2E}" name="Column4" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{69D00D15-DF82-46C9-9945-107A85371A6F}" name="Column5" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{F10DE59E-3B92-4DD0-8A04-FAE76E9F8BB9}" name="Column6" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{2D949549-0F5C-4A89-B8F7-72304B9A24F1}" name="Column8" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{C42826CE-029E-4945-8434-CBC9F4DAA57F}" name="Column9" dataDxfId="35" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{F0789B57-A27F-47CD-94AE-4F6B71344DB9}" name="Column92" dataDxfId="34" dataCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{84F8B5AD-93FB-4C3E-8E09-FB358E10FC62}" name="Column93" dataDxfId="33" dataCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{DA8CB162-5C11-45A4-93E0-E0C45C3ED3D0}" name="Column94" dataDxfId="32" dataCellStyle="Comma"/>
-    <tableColumn id="27" xr3:uid="{100A9F62-6915-49BB-B014-4D0BC03BB553}" name="Column95" dataDxfId="31" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{5B60D48A-2B91-4E81-AD9D-2709C1335F32}" name="Column10" dataDxfId="30" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{E1B16D3B-DEA4-44A7-8DE4-CA3F41D77B2B}" name="Column11" dataDxfId="29" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{793817C6-38BE-49BA-A9A6-4F96D87310D9}" name="Column12" dataDxfId="28" dataCellStyle="Comma"/>
-    <tableColumn id="15" xr3:uid="{2AFA675A-D2B0-476D-A865-BB72634DC6DA}" name="Column15" dataDxfId="27"/>
-    <tableColumn id="16" xr3:uid="{B5249436-7148-4EBF-B8E6-5226AA101320}" name="Column16" dataDxfId="26" dataCellStyle="Currency"/>
-    <tableColumn id="17" xr3:uid="{22140E2C-B2EC-4771-8D39-0E8FE9F80B88}" name="Column17" dataDxfId="25"/>
-    <tableColumn id="18" xr3:uid="{AC423A03-E794-4524-9C7D-D02B01892118}" name="Column18" dataDxfId="24" dataCellStyle="Comma"/>
-    <tableColumn id="19" xr3:uid="{F73A917A-F13B-4BB9-8524-E34E6050878C}" name="Column19" dataDxfId="23" dataCellStyle="Comma"/>
-    <tableColumn id="20" xr3:uid="{4A9B484B-EBD7-41D1-8470-161DB87D7FB2}" name="Column20" dataDxfId="22" dataCellStyle="Comma"/>
-    <tableColumn id="21" xr3:uid="{D03D1805-69BB-4D67-B61E-961F2E625E81}" name="Column21" dataDxfId="21"/>
-    <tableColumn id="22" xr3:uid="{66E8E4D1-FF14-404F-8354-025C93AED5CB}" name="Column22" dataDxfId="20"/>
-    <tableColumn id="23" xr3:uid="{9540F131-1C8F-4F4F-8796-92F1AFD57E03}" name="Column23" dataDxfId="19"/>
-    <tableColumn id="24" xr3:uid="{B7156378-CEA1-4808-9801-4E93C755FE92}" name="Column24" dataDxfId="18"/>
-    <tableColumn id="25" xr3:uid="{6908C233-AA1B-4818-BF8F-36FC13C53D09}" name="Column25" dataDxfId="17"/>
-    <tableColumn id="26" xr3:uid="{104781D6-1EEE-4947-A424-3CE3DCADF4CF}" name="Column26" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{73FD62E2-E8FE-4C00-9C3C-F3122EB55D0D}" name="Column1" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{F8F856BF-80BD-4398-8276-448953D1A283}" name="Column2" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{859FF76C-0D7F-496C-B885-2DE680F3F916}" name="Column7" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{EFE5B159-5688-4C13-A02D-A6C704275E2E}" name="Column4" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{69D00D15-DF82-46C9-9945-107A85371A6F}" name="Column5" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{F10DE59E-3B92-4DD0-8A04-FAE76E9F8BB9}" name="Column6" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{2D949549-0F5C-4A89-B8F7-72304B9A24F1}" name="Column8" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{C42826CE-029E-4945-8434-CBC9F4DAA57F}" name="Column9" dataDxfId="33" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{F0789B57-A27F-47CD-94AE-4F6B71344DB9}" name="Column92" dataDxfId="32" dataCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{84F8B5AD-93FB-4C3E-8E09-FB358E10FC62}" name="Column93" dataDxfId="31" dataCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{DA8CB162-5C11-45A4-93E0-E0C45C3ED3D0}" name="Column94" dataDxfId="30" dataCellStyle="Comma"/>
+    <tableColumn id="27" xr3:uid="{100A9F62-6915-49BB-B014-4D0BC03BB553}" name="Column95" dataDxfId="29" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{5B60D48A-2B91-4E81-AD9D-2709C1335F32}" name="Column10" dataDxfId="28" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{E1B16D3B-DEA4-44A7-8DE4-CA3F41D77B2B}" name="Column11" dataDxfId="27" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{793817C6-38BE-49BA-A9A6-4F96D87310D9}" name="Column12" dataDxfId="26" dataCellStyle="Comma"/>
+    <tableColumn id="15" xr3:uid="{2AFA675A-D2B0-476D-A865-BB72634DC6DA}" name="Column15" dataDxfId="25"/>
+    <tableColumn id="16" xr3:uid="{B5249436-7148-4EBF-B8E6-5226AA101320}" name="Column16" dataDxfId="24" dataCellStyle="Currency"/>
+    <tableColumn id="17" xr3:uid="{22140E2C-B2EC-4771-8D39-0E8FE9F80B88}" name="Column17" dataDxfId="23"/>
+    <tableColumn id="18" xr3:uid="{AC423A03-E794-4524-9C7D-D02B01892118}" name="Column18" dataDxfId="22" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{F73A917A-F13B-4BB9-8524-E34E6050878C}" name="Column19" dataDxfId="21" dataCellStyle="Comma"/>
+    <tableColumn id="20" xr3:uid="{4A9B484B-EBD7-41D1-8470-161DB87D7FB2}" name="Column20" dataDxfId="20" dataCellStyle="Comma"/>
+    <tableColumn id="21" xr3:uid="{D03D1805-69BB-4D67-B61E-961F2E625E81}" name="Column21" dataDxfId="19"/>
+    <tableColumn id="22" xr3:uid="{66E8E4D1-FF14-404F-8354-025C93AED5CB}" name="Column22" dataDxfId="18"/>
+    <tableColumn id="23" xr3:uid="{9540F131-1C8F-4F4F-8796-92F1AFD57E03}" name="Column23" dataDxfId="17"/>
+    <tableColumn id="24" xr3:uid="{B7156378-CEA1-4808-9801-4E93C755FE92}" name="Column24" dataDxfId="16"/>
+    <tableColumn id="25" xr3:uid="{6908C233-AA1B-4818-BF8F-36FC13C53D09}" name="Column25" dataDxfId="15"/>
+    <tableColumn id="26" xr3:uid="{104781D6-1EEE-4947-A424-3CE3DCADF4CF}" name="Column26" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5998,12 +5978,12 @@
       <c r="S11" s="3"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:30" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4" t="s">
@@ -6021,7 +6001,7 @@
         <v>18</v>
       </c>
       <c r="J12" s="2">
-        <v>907006410</v>
+        <v>876880607</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>3</v>
@@ -6048,14 +6028,17 @@
         <v>0</v>
       </c>
       <c r="S12" s="3"/>
-      <c r="Z12" s="2"/>
-    </row>
-    <row r="13" spans="1:30" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U12" s="2"/>
+      <c r="W12" s="23"/>
+      <c r="X12" s="2"/>
+      <c r="Z12" s="3"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>301</v>
+        <v>183</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="4" t="s">
@@ -6073,7 +6056,7 @@
         <v>18</v>
       </c>
       <c r="J13" s="2">
-        <v>918675705</v>
+        <v>887699043</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>3</v>
@@ -6100,14 +6083,17 @@
         <v>0</v>
       </c>
       <c r="S13" s="3"/>
-      <c r="Z13" s="2"/>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="U13" s="2"/>
+      <c r="W13" s="23"/>
+      <c r="X13" s="2"/>
+      <c r="Z13" s="3"/>
+    </row>
+    <row r="14" spans="1:30" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="4" t="s">
@@ -6124,8 +6110,8 @@
       <c r="I14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="2">
-        <v>817976209</v>
+      <c r="J14" s="72">
+        <v>751356958</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>3</v>
@@ -6152,17 +6138,14 @@
         <v>0</v>
       </c>
       <c r="S14" s="3"/>
-      <c r="U14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="Z14" s="2"/>
+    </row>
+    <row r="15" spans="1:30" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>182</v>
+        <v>258</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="4" t="s">
@@ -6180,7 +6163,7 @@
         <v>18</v>
       </c>
       <c r="J15" s="2">
-        <v>876880607</v>
+        <v>907006410</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>3</v>
@@ -6207,17 +6190,14 @@
         <v>0</v>
       </c>
       <c r="S15" s="3"/>
-      <c r="U15" s="2"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="2"/>
-      <c r="Z15" s="3"/>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="Z15" s="2"/>
+    </row>
+    <row r="16" spans="1:30" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>183</v>
+        <v>301</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="4" t="s">
@@ -6235,7 +6215,7 @@
         <v>18</v>
       </c>
       <c r="J16" s="2">
-        <v>887699043</v>
+        <v>918675705</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>3</v>
@@ -6262,17 +6242,14 @@
         <v>0</v>
       </c>
       <c r="S16" s="3"/>
-      <c r="U16" s="2"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="2"/>
-      <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="1:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z16" s="2"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="4" t="s">
@@ -6289,8 +6266,8 @@
       <c r="I17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="72">
-        <v>751356958</v>
+      <c r="J17" s="2">
+        <v>817976209</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>3</v>
@@ -6317,14 +6294,17 @@
         <v>0</v>
       </c>
       <c r="S17" s="3"/>
-      <c r="Z17" s="2"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="U17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B18" s="67" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="66" t="s">
@@ -6342,7 +6322,7 @@
         <v>18</v>
       </c>
       <c r="J18" s="67">
-        <v>907006434</v>
+        <v>876880626</v>
       </c>
       <c r="K18" s="67" t="s">
         <v>3</v>
@@ -6374,12 +6354,12 @@
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="66" t="s">
@@ -6397,7 +6377,7 @@
         <v>18</v>
       </c>
       <c r="J19" s="67">
-        <v>918675725</v>
+        <v>887699064</v>
       </c>
       <c r="K19" s="67" t="s">
         <v>3</v>
@@ -6429,12 +6409,12 @@
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B20" s="67" t="s">
-        <v>376</v>
+        <v>189</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="66" t="s">
@@ -6451,8 +6431,8 @@
       <c r="I20" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="67">
-        <v>817976231</v>
+      <c r="J20" s="73">
+        <v>751357003</v>
       </c>
       <c r="K20" s="67" t="s">
         <v>3</v>
@@ -6484,12 +6464,12 @@
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B21" s="67" t="s">
-        <v>187</v>
+        <v>304</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="66" t="s">
@@ -6507,7 +6487,7 @@
         <v>18</v>
       </c>
       <c r="J21" s="67">
-        <v>876880626</v>
+        <v>907006434</v>
       </c>
       <c r="K21" s="67" t="s">
         <v>3</v>
@@ -6539,12 +6519,12 @@
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B22" s="67" t="s">
-        <v>188</v>
+        <v>305</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="66" t="s">
@@ -6562,7 +6542,7 @@
         <v>18</v>
       </c>
       <c r="J22" s="67">
-        <v>887699064</v>
+        <v>918675725</v>
       </c>
       <c r="K22" s="67" t="s">
         <v>3</v>
@@ -6594,12 +6574,12 @@
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="97" t="b">
         <v>1</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>189</v>
+        <v>376</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="66" t="s">
@@ -6616,8 +6596,8 @@
       <c r="I23" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="73">
-        <v>751357003</v>
+      <c r="J23" s="67">
+        <v>817976231</v>
       </c>
       <c r="K23" s="67" t="s">
         <v>3</v>
@@ -6649,7 +6629,7 @@
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="97" t="b">
         <v>1</v>
       </c>
@@ -6704,7 +6684,7 @@
       <c r="X24" s="2"/>
       <c r="Y24" s="2"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="97" t="b">
         <v>0</v>
       </c>
@@ -6757,7 +6737,7 @@
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="97" t="b">
         <v>0</v>
       </c>
@@ -6810,7 +6790,7 @@
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="97" t="b">
         <v>0</v>
       </c>
@@ -6863,7 +6843,7 @@
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="97" t="b">
         <v>0</v>
       </c>
@@ -6918,7 +6898,7 @@
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="97" t="b">
         <v>0</v>
       </c>
@@ -6973,7 +6953,7 @@
       <c r="X29" s="2"/>
       <c r="Y29" s="2"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="97" t="b">
         <v>0</v>
       </c>
@@ -7028,7 +7008,7 @@
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="97" t="b">
         <v>0</v>
       </c>
@@ -7081,7 +7061,7 @@
       <c r="X31" s="2"/>
       <c r="Y31" s="2"/>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="97" t="b">
         <v>0</v>
       </c>
@@ -9242,19 +9222,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A73">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:A73 R2:R73">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R73">
-    <cfRule type="cellIs" dxfId="13" priority="17" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36929,7 +36901,7 @@
       </c>
       <c r="D5" s="84" t="str">
         <f ca="1">_xlfn.CONCAT("ETF_",D15,".csv")</f>
-        <v>ETF_2026-10-25.csv</v>
+        <v>ETF_2026-10-27.csv</v>
       </c>
       <c r="E5" s="77"/>
     </row>
@@ -37058,7 +37030,7 @@
     <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D15" s="88" t="str">
         <f t="shared" ref="D15" ca="1" si="0">TEXT(TODAY(),"yyyy-mm-dd")</f>
-        <v>2026-10-25</v>
+        <v>2026-10-27</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -38100,7 +38072,7 @@
       </c>
       <c r="D20" s="2">
         <f>crypto_inputs[[#This Row],[pf_locator]]</f>
-        <v>817976231</v>
+        <v>751357003</v>
       </c>
       <c r="E20" s="32" t="s">
         <v>18</v>
